--- a/artfynd/A 41672-2024 artfynd.xlsx
+++ b/artfynd/A 41672-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120067935</v>
+        <v>120069457</v>
       </c>
       <c r="B2" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>746381</v>
+        <v>746379</v>
       </c>
       <c r="R2" t="n">
-        <v>7152596</v>
+        <v>7152575</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120069457</v>
+        <v>120067935</v>
       </c>
       <c r="B3" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>746379</v>
+        <v>746381</v>
       </c>
       <c r="R3" t="n">
-        <v>7152575</v>
+        <v>7152596</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120068255</v>
+        <v>120066896</v>
       </c>
       <c r="B12" t="n">
-        <v>91840</v>
+        <v>91863</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,25 +1807,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>746352</v>
+        <v>746537</v>
       </c>
       <c r="R12" t="n">
-        <v>7152686</v>
+        <v>7152456</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120066896</v>
+        <v>120068255</v>
       </c>
       <c r="B13" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,25 +1919,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>746537</v>
+        <v>746352</v>
       </c>
       <c r="R13" t="n">
-        <v>7152456</v>
+        <v>7152686</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -3361,6 +3361,6242 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120079797</v>
+      </c>
+      <c r="B26" t="n">
+        <v>89633</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>746432</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7152509</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120086266</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91863</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>746429</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7152625</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120094849</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>746531</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7152454</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120094897</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>746482</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7152467</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120086294</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>746310</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7152670</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120080346</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>746461</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7152458</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120080348</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>746505</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7152451</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120080336</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>746545</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7152464</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120080295</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57463</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>746385</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7152570</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120094922</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91884</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>746442</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7152565</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120086297</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>746473</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7152499</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120086246</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91884</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>746475</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7152487</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120086298</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>746527</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7152434</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120094959</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>746300</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7152654</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>120094869</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>746522</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7152453</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>120079812</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>746540</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7152434</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>120086276</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>746304</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7152657</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>120094901</v>
+      </c>
+      <c r="B43" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>746487</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7152494</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>120080341</v>
+      </c>
+      <c r="B44" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>746384</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7152544</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>120080345</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>746459</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7152465</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>120086269</v>
+      </c>
+      <c r="B46" t="n">
+        <v>88153</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>4962</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Mjölsvärting</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Lyophyllum semitale</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Fr. : Fr.) Kühner</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>746365</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7152575</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Inte ihålig men övriga karaktärer stämde.</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>120086280</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>746527</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7152434</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>120094855</v>
+      </c>
+      <c r="B48" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>746547</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7152471</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>120086263</v>
+      </c>
+      <c r="B49" t="n">
+        <v>92030</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>746450</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7152549</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>120086274</v>
+      </c>
+      <c r="B50" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>746478</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7152496</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>120080306</v>
+      </c>
+      <c r="B51" t="n">
+        <v>91884</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>746490</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7152502</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>120080319</v>
+      </c>
+      <c r="B52" t="n">
+        <v>92030</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>746477</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7152502</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På kolad tallstubbe</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL52" t="inlineStr">
+        <is>
+          <t>Kolad tallstubbe</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Kolad tallstubbe</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>120080342</v>
+      </c>
+      <c r="B53" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>746478</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7152487</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>120086228</v>
+      </c>
+      <c r="B54" t="n">
+        <v>74638</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>746357</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7152581</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>120079802</v>
+      </c>
+      <c r="B55" t="n">
+        <v>91884</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>746495</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7152470</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>120086238</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57463</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>746509</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7152434</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Två</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>120086275</v>
+      </c>
+      <c r="B57" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>746370</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7152601</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>120094932</v>
+      </c>
+      <c r="B58" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>746414</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7152584</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>120094907</v>
+      </c>
+      <c r="B59" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>746484</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7152510</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>120080307</v>
+      </c>
+      <c r="B60" t="n">
+        <v>91884</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>746426</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7152510</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>120086245</v>
+      </c>
+      <c r="B61" t="n">
+        <v>91884</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>746365</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7152575</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>120086277</v>
+      </c>
+      <c r="B62" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>746302</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7152670</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>120086295</v>
+      </c>
+      <c r="B63" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>746365</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7152695</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>120086296</v>
+      </c>
+      <c r="B64" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>746425</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7152621</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>120094916</v>
+      </c>
+      <c r="B65" t="n">
+        <v>91884</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>746490</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7152513</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>120086230</v>
+      </c>
+      <c r="B66" t="n">
+        <v>90527</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>746412</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7152564</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>120094939</v>
+      </c>
+      <c r="B67" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>746413</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7152616</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>120094951</v>
+      </c>
+      <c r="B68" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>746357</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7152686</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>120086291</v>
+      </c>
+      <c r="B69" t="n">
+        <v>90807</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>65</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Fläckporing</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Anthoporia albobrunnea</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>746502</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7152478</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>120086278</v>
+      </c>
+      <c r="B70" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>746365</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7152695</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>120086272</v>
+      </c>
+      <c r="B71" t="n">
+        <v>74624</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>306</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Kornig nållav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Chaenotheca chlorella</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>746357</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7152581</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>120080349</v>
+      </c>
+      <c r="B72" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>746540</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7152444</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>120080337</v>
+      </c>
+      <c r="B73" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>746488</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7152500</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>120086259</v>
+      </c>
+      <c r="B74" t="n">
+        <v>91832</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>746394</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7152581</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>120086265</v>
+      </c>
+      <c r="B75" t="n">
+        <v>78263</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>746353</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7152592</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>120079805</v>
+      </c>
+      <c r="B76" t="n">
+        <v>92030</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>746437</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7152508</v>
+      </c>
+      <c r="S76" t="n">
+        <v>15</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>120079813</v>
+      </c>
+      <c r="B77" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>746517</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7152485</v>
+      </c>
+      <c r="S77" t="n">
+        <v>15</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>120080338</v>
+      </c>
+      <c r="B78" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>746455</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7152561</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>120079809</v>
+      </c>
+      <c r="B79" t="n">
+        <v>90712</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>746368</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7152599</v>
+      </c>
+      <c r="S79" t="n">
+        <v>15</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>120080326</v>
+      </c>
+      <c r="B80" t="n">
+        <v>89230</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>1596</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Jättemusseron</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Tricholoma colossus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>746543</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7152437</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>120080340</v>
+      </c>
+      <c r="B81" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>746398</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7152548</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>120080343</v>
+      </c>
+      <c r="B82" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>746467</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7152466</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>120086279</v>
+      </c>
+      <c r="B83" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>746397</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7152654</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>120094945</v>
+      </c>
+      <c r="B84" t="n">
+        <v>91884</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>746417</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7152628</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>120094886</v>
+      </c>
+      <c r="B85" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Vintjärnskammen, Vb</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>746500</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7152466</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41672-2024 artfynd.xlsx
+++ b/artfynd/A 41672-2024 artfynd.xlsx
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120068331</v>
+        <v>120067262</v>
       </c>
       <c r="B4" t="n">
         <v>91840</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>746318</v>
+        <v>746520</v>
       </c>
       <c r="R4" t="n">
-        <v>7152701</v>
+        <v>7152494</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120067262</v>
+        <v>120068331</v>
       </c>
       <c r="B5" t="n">
         <v>91840</v>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>746520</v>
+        <v>746318</v>
       </c>
       <c r="R5" t="n">
-        <v>7152494</v>
+        <v>7152701</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120068133</v>
+        <v>120067430</v>
       </c>
       <c r="B6" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>746333</v>
+        <v>746505</v>
       </c>
       <c r="R6" t="n">
-        <v>7152647</v>
+        <v>7152499</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120068460</v>
+        <v>120068133</v>
       </c>
       <c r="B7" t="n">
         <v>91840</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>746312</v>
+        <v>746333</v>
       </c>
       <c r="R7" t="n">
-        <v>7152709</v>
+        <v>7152647</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120067430</v>
+        <v>120068460</v>
       </c>
       <c r="B8" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>746505</v>
+        <v>746312</v>
       </c>
       <c r="R8" t="n">
-        <v>7152499</v>
+        <v>7152709</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -3465,10 +3465,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120086266</v>
+        <v>120094849</v>
       </c>
       <c r="B27" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3477,38 +3477,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>746429</v>
+        <v>746531</v>
       </c>
       <c r="R27" t="n">
-        <v>7152625</v>
+        <v>7152454</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3549,6 +3552,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3567,7 +3571,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120094849</v>
+        <v>120094897</v>
       </c>
       <c r="B28" t="n">
         <v>91840</v>
@@ -3610,10 +3614,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>746531</v>
+        <v>746482</v>
       </c>
       <c r="R28" t="n">
-        <v>7152454</v>
+        <v>7152467</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3673,10 +3677,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120094897</v>
+        <v>120086266</v>
       </c>
       <c r="B29" t="n">
-        <v>91840</v>
+        <v>91863</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3685,41 +3689,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>746482</v>
+        <v>746429</v>
       </c>
       <c r="R29" t="n">
-        <v>7152467</v>
+        <v>7152625</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3760,7 +3761,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4403,7 +4403,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120086297</v>
+        <v>120094959</v>
       </c>
       <c r="B36" t="n">
         <v>91840</v>
@@ -4437,16 +4437,19 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>746473</v>
+        <v>746300</v>
       </c>
       <c r="R36" t="n">
-        <v>7152499</v>
+        <v>7152654</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4487,6 +4490,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4505,10 +4509,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120086246</v>
+        <v>120094869</v>
       </c>
       <c r="B37" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4517,38 +4521,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>746475</v>
+        <v>746522</v>
       </c>
       <c r="R37" t="n">
-        <v>7152487</v>
+        <v>7152453</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4589,6 +4596,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4607,7 +4615,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120086298</v>
+        <v>120086297</v>
       </c>
       <c r="B38" t="n">
         <v>91840</v>
@@ -4647,10 +4655,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>746527</v>
+        <v>746473</v>
       </c>
       <c r="R38" t="n">
-        <v>7152434</v>
+        <v>7152499</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4709,10 +4717,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120094959</v>
+        <v>120086246</v>
       </c>
       <c r="B39" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4721,41 +4729,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>746300</v>
+        <v>746475</v>
       </c>
       <c r="R39" t="n">
-        <v>7152654</v>
+        <v>7152487</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4796,7 +4801,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4815,7 +4819,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120094869</v>
+        <v>120086298</v>
       </c>
       <c r="B40" t="n">
         <v>91840</v>
@@ -4849,19 +4853,16 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>746522</v>
+        <v>746527</v>
       </c>
       <c r="R40" t="n">
-        <v>7152453</v>
+        <v>7152434</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4902,7 +4903,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4921,7 +4921,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120079812</v>
+        <v>120094901</v>
       </c>
       <c r="B41" t="n">
         <v>91840</v>
@@ -4955,19 +4955,22 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>746540</v>
+        <v>746487</v>
       </c>
       <c r="R41" t="n">
-        <v>7152434</v>
+        <v>7152494</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5012,22 +5015,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120086276</v>
+        <v>120079812</v>
       </c>
       <c r="B42" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5036,25 +5039,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5064,13 +5067,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>746304</v>
+        <v>746540</v>
       </c>
       <c r="R42" t="n">
-        <v>7152657</v>
+        <v>7152434</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5108,28 +5111,29 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120094901</v>
+        <v>120086276</v>
       </c>
       <c r="B43" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5138,41 +5142,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>746487</v>
+        <v>746304</v>
       </c>
       <c r="R43" t="n">
-        <v>7152494</v>
+        <v>7152657</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5213,7 +5214,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5547,10 +5547,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120086280</v>
+        <v>120094855</v>
       </c>
       <c r="B47" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5559,38 +5559,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>746527</v>
+        <v>746547</v>
       </c>
       <c r="R47" t="n">
-        <v>7152434</v>
+        <v>7152471</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5631,6 +5634,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5649,10 +5653,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120094855</v>
+        <v>120086280</v>
       </c>
       <c r="B48" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5661,41 +5665,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>746547</v>
+        <v>746527</v>
       </c>
       <c r="R48" t="n">
-        <v>7152471</v>
+        <v>7152434</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5736,7 +5737,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -7747,7 +7747,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120094951</v>
+        <v>120080349</v>
       </c>
       <c r="B68" t="n">
         <v>91840</v>
@@ -7781,19 +7781,16 @@
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>746357</v>
+        <v>746540</v>
       </c>
       <c r="R68" t="n">
-        <v>7152686</v>
+        <v>7152444</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7834,29 +7831,28 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120086291</v>
+        <v>120080337</v>
       </c>
       <c r="B69" t="n">
-        <v>90807</v>
+        <v>91840</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7865,25 +7861,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7893,10 +7889,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>746502</v>
+        <v>746488</v>
       </c>
       <c r="R69" t="n">
-        <v>7152478</v>
+        <v>7152500</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7943,22 +7939,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120086278</v>
+        <v>120094951</v>
       </c>
       <c r="B70" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7967,38 +7963,41 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>746365</v>
+        <v>746357</v>
       </c>
       <c r="R70" t="n">
-        <v>7152695</v>
+        <v>7152686</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8039,6 +8038,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8057,10 +8057,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120086272</v>
+        <v>120086291</v>
       </c>
       <c r="B71" t="n">
-        <v>74624</v>
+        <v>90807</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8069,25 +8069,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>306</v>
+        <v>65</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8097,10 +8097,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>746357</v>
+        <v>746502</v>
       </c>
       <c r="R71" t="n">
-        <v>7152581</v>
+        <v>7152478</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8159,10 +8159,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120080349</v>
+        <v>120086278</v>
       </c>
       <c r="B72" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8171,25 +8171,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8199,10 +8199,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>746540</v>
+        <v>746365</v>
       </c>
       <c r="R72" t="n">
-        <v>7152444</v>
+        <v>7152695</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8249,22 +8249,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120080337</v>
+        <v>120086272</v>
       </c>
       <c r="B73" t="n">
-        <v>91840</v>
+        <v>74624</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8277,21 +8277,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8301,10 +8301,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>746488</v>
+        <v>746357</v>
       </c>
       <c r="R73" t="n">
-        <v>7152500</v>
+        <v>7152581</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8351,12 +8351,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8771,10 +8771,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120080338</v>
+        <v>120079809</v>
       </c>
       <c r="B78" t="n">
-        <v>91840</v>
+        <v>90712</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8783,41 +8783,44 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>746455</v>
+        <v>746368</v>
       </c>
       <c r="R78" t="n">
-        <v>7152561</v>
+        <v>7152599</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8855,28 +8858,29 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120079809</v>
+        <v>120080338</v>
       </c>
       <c r="B79" t="n">
-        <v>90712</v>
+        <v>91840</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8885,44 +8889,41 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>746368</v>
+        <v>746455</v>
       </c>
       <c r="R79" t="n">
-        <v>7152599</v>
+        <v>7152561</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8960,19 +8961,18 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>

--- a/artfynd/A 41672-2024 artfynd.xlsx
+++ b/artfynd/A 41672-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120069457</v>
+        <v>120068460</v>
       </c>
       <c r="B2" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>746379</v>
+        <v>746312</v>
       </c>
       <c r="R2" t="n">
-        <v>7152575</v>
+        <v>7152709</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120067935</v>
+        <v>120068300</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>91863</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>746381</v>
+        <v>746336</v>
       </c>
       <c r="R3" t="n">
-        <v>7152596</v>
+        <v>7152676</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120067262</v>
+        <v>120067430</v>
       </c>
       <c r="B4" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>746520</v>
+        <v>746505</v>
       </c>
       <c r="R4" t="n">
-        <v>7152494</v>
+        <v>7152499</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120068331</v>
+        <v>120067262</v>
       </c>
       <c r="B5" t="n">
         <v>91840</v>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>746318</v>
+        <v>746520</v>
       </c>
       <c r="R5" t="n">
-        <v>7152701</v>
+        <v>7152494</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120067430</v>
+        <v>120067979</v>
       </c>
       <c r="B6" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>746505</v>
+        <v>746392</v>
       </c>
       <c r="R6" t="n">
-        <v>7152499</v>
+        <v>7152615</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120068133</v>
+        <v>120068365</v>
       </c>
       <c r="B7" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>746333</v>
+        <v>746323</v>
       </c>
       <c r="R7" t="n">
-        <v>7152647</v>
+        <v>7152700</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120068460</v>
+        <v>120068602</v>
       </c>
       <c r="B8" t="n">
-        <v>91840</v>
+        <v>79636</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>746312</v>
+        <v>746307</v>
       </c>
       <c r="R8" t="n">
-        <v>7152709</v>
+        <v>7152647</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120067137</v>
+        <v>120068383</v>
       </c>
       <c r="B9" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,25 +1471,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>746520</v>
+        <v>746313</v>
       </c>
       <c r="R9" t="n">
-        <v>7152487</v>
+        <v>7152706</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120068602</v>
+        <v>120069608</v>
       </c>
       <c r="B10" t="n">
-        <v>79636</v>
+        <v>91832</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,25 +1583,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>746307</v>
+        <v>746422</v>
       </c>
       <c r="R10" t="n">
-        <v>7152647</v>
+        <v>7152546</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120068300</v>
+        <v>120069348</v>
       </c>
       <c r="B11" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,25 +1695,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>746336</v>
+        <v>746382</v>
       </c>
       <c r="R11" t="n">
-        <v>7152676</v>
+        <v>7152570</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120066896</v>
+        <v>120067137</v>
       </c>
       <c r="B12" t="n">
-        <v>91863</v>
+        <v>91834</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>746537</v>
+        <v>746520</v>
       </c>
       <c r="R12" t="n">
-        <v>7152456</v>
+        <v>7152487</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120068255</v>
+        <v>120067885</v>
       </c>
       <c r="B13" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,25 +1919,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>746352</v>
+        <v>746399</v>
       </c>
       <c r="R13" t="n">
-        <v>7152686</v>
+        <v>7152617</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120068365</v>
+        <v>120067504</v>
       </c>
       <c r="B14" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>746323</v>
+        <v>746486</v>
       </c>
       <c r="R14" t="n">
-        <v>7152700</v>
+        <v>7152501</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120067504</v>
+        <v>120068080</v>
       </c>
       <c r="B15" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2143,25 +2143,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>746486</v>
+        <v>746371</v>
       </c>
       <c r="R15" t="n">
-        <v>7152501</v>
+        <v>7152632</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120067841</v>
+        <v>120066896</v>
       </c>
       <c r="B16" t="n">
-        <v>91840</v>
+        <v>91863</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2255,25 +2255,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>746469</v>
+        <v>746537</v>
       </c>
       <c r="R16" t="n">
-        <v>7152569</v>
+        <v>7152456</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120067885</v>
+        <v>120067935</v>
       </c>
       <c r="B17" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2367,25 +2367,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>746399</v>
+        <v>746381</v>
       </c>
       <c r="R17" t="n">
-        <v>7152617</v>
+        <v>7152596</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,7 +2467,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120067568</v>
+        <v>120068133</v>
       </c>
       <c r="B18" t="n">
         <v>91840</v>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>746484</v>
+        <v>746333</v>
       </c>
       <c r="R18" t="n">
-        <v>7152500</v>
+        <v>7152647</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,7 +2579,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120066631</v>
+        <v>120068331</v>
       </c>
       <c r="B19" t="n">
         <v>91840</v>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>746551</v>
+        <v>746318</v>
       </c>
       <c r="R19" t="n">
-        <v>7152434</v>
+        <v>7152701</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120069348</v>
+        <v>120068346</v>
       </c>
       <c r="B20" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2707,21 +2707,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>746382</v>
+        <v>746324</v>
       </c>
       <c r="R20" t="n">
-        <v>7152570</v>
+        <v>7152703</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120068346</v>
+        <v>120066631</v>
       </c>
       <c r="B21" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2819,21 +2819,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>746324</v>
+        <v>746551</v>
       </c>
       <c r="R21" t="n">
-        <v>7152703</v>
+        <v>7152434</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,7 +2915,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120068383</v>
+        <v>120067568</v>
       </c>
       <c r="B22" t="n">
         <v>91840</v>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>746313</v>
+        <v>746484</v>
       </c>
       <c r="R22" t="n">
-        <v>7152706</v>
+        <v>7152500</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,10 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120068080</v>
+        <v>120069457</v>
       </c>
       <c r="B23" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3039,25 +3039,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>746371</v>
+        <v>746379</v>
       </c>
       <c r="R23" t="n">
-        <v>7152632</v>
+        <v>7152575</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,7 +3139,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120067979</v>
+        <v>120067841</v>
       </c>
       <c r="B24" t="n">
         <v>91840</v>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>746392</v>
+        <v>746469</v>
       </c>
       <c r="R24" t="n">
-        <v>7152615</v>
+        <v>7152569</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3251,10 +3251,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120069608</v>
+        <v>120068255</v>
       </c>
       <c r="B25" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3263,25 +3263,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>746422</v>
+        <v>746352</v>
       </c>
       <c r="R25" t="n">
-        <v>7152546</v>
+        <v>7152686</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3363,10 +3363,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120079797</v>
+        <v>120094901</v>
       </c>
       <c r="B26" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3375,41 +3375,44 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>746432</v>
+        <v>746487</v>
       </c>
       <c r="R26" t="n">
-        <v>7152509</v>
+        <v>7152494</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3447,28 +3450,29 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120094849</v>
+        <v>120079797</v>
       </c>
       <c r="B27" t="n">
-        <v>91840</v>
+        <v>89633</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3477,44 +3481,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>746531</v>
+        <v>746432</v>
       </c>
       <c r="R27" t="n">
-        <v>7152454</v>
+        <v>7152509</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3552,26 +3553,25 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120094897</v>
+        <v>120086295</v>
       </c>
       <c r="B28" t="n">
         <v>91840</v>
@@ -3605,19 +3605,16 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>746482</v>
+        <v>746365</v>
       </c>
       <c r="R28" t="n">
-        <v>7152467</v>
+        <v>7152695</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3658,7 +3655,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3677,10 +3673,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120086266</v>
+        <v>120080337</v>
       </c>
       <c r="B29" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3689,25 +3685,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3717,10 +3713,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>746429</v>
+        <v>746488</v>
       </c>
       <c r="R29" t="n">
-        <v>7152625</v>
+        <v>7152500</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3767,22 +3763,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120086294</v>
+        <v>120086246</v>
       </c>
       <c r="B30" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3791,25 +3787,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3819,10 +3815,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>746310</v>
+        <v>746475</v>
       </c>
       <c r="R30" t="n">
-        <v>7152670</v>
+        <v>7152487</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3881,7 +3877,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120080346</v>
+        <v>120080341</v>
       </c>
       <c r="B31" t="n">
         <v>91840</v>
@@ -3921,10 +3917,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>746461</v>
+        <v>746384</v>
       </c>
       <c r="R31" t="n">
-        <v>7152458</v>
+        <v>7152544</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3983,10 +3979,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120080348</v>
+        <v>120086265</v>
       </c>
       <c r="B32" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3995,25 +3991,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4023,10 +4019,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>746505</v>
+        <v>746353</v>
       </c>
       <c r="R32" t="n">
-        <v>7152451</v>
+        <v>7152592</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4073,19 +4069,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120080336</v>
+        <v>120080340</v>
       </c>
       <c r="B33" t="n">
         <v>91840</v>
@@ -4125,10 +4121,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>746545</v>
+        <v>746398</v>
       </c>
       <c r="R33" t="n">
-        <v>7152464</v>
+        <v>7152548</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4187,10 +4183,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120080295</v>
+        <v>120086280</v>
       </c>
       <c r="B34" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4203,42 +4199,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>746385</v>
+        <v>746527</v>
       </c>
       <c r="R34" t="n">
-        <v>7152570</v>
+        <v>7152434</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4285,22 +4273,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120094922</v>
+        <v>120086228</v>
       </c>
       <c r="B35" t="n">
-        <v>91884</v>
+        <v>74638</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4313,37 +4301,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5449</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>746442</v>
+        <v>746357</v>
       </c>
       <c r="R35" t="n">
-        <v>7152565</v>
+        <v>7152581</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4384,7 +4369,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4403,7 +4387,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120094959</v>
+        <v>120086296</v>
       </c>
       <c r="B36" t="n">
         <v>91840</v>
@@ -4437,19 +4421,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>746300</v>
+        <v>746425</v>
       </c>
       <c r="R36" t="n">
-        <v>7152654</v>
+        <v>7152621</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4490,7 +4471,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4509,7 +4489,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120094869</v>
+        <v>120094886</v>
       </c>
       <c r="B37" t="n">
         <v>91840</v>
@@ -4552,10 +4532,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>746522</v>
+        <v>746500</v>
       </c>
       <c r="R37" t="n">
-        <v>7152453</v>
+        <v>7152466</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4615,7 +4595,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120086297</v>
+        <v>120094907</v>
       </c>
       <c r="B38" t="n">
         <v>91840</v>
@@ -4649,16 +4629,19 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>746473</v>
+        <v>746484</v>
       </c>
       <c r="R38" t="n">
-        <v>7152499</v>
+        <v>7152510</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4699,6 +4682,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4717,10 +4701,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120086246</v>
+        <v>120086263</v>
       </c>
       <c r="B39" t="n">
-        <v>91884</v>
+        <v>92030</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4733,21 +4717,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5449</v>
+        <v>2079</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4757,10 +4741,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>746475</v>
+        <v>746450</v>
       </c>
       <c r="R39" t="n">
-        <v>7152487</v>
+        <v>7152549</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4819,7 +4803,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120086298</v>
+        <v>120086297</v>
       </c>
       <c r="B40" t="n">
         <v>91840</v>
@@ -4859,10 +4843,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>746527</v>
+        <v>746473</v>
       </c>
       <c r="R40" t="n">
-        <v>7152434</v>
+        <v>7152499</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4921,7 +4905,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120094901</v>
+        <v>120086298</v>
       </c>
       <c r="B41" t="n">
         <v>91840</v>
@@ -4955,19 +4939,16 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>746487</v>
+        <v>746527</v>
       </c>
       <c r="R41" t="n">
-        <v>7152494</v>
+        <v>7152434</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5008,7 +4989,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5027,7 +5007,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120079812</v>
+        <v>120080346</v>
       </c>
       <c r="B42" t="n">
         <v>91840</v>
@@ -5067,13 +5047,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>746540</v>
+        <v>746461</v>
       </c>
       <c r="R42" t="n">
-        <v>7152434</v>
+        <v>7152458</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5111,29 +5091,28 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120086276</v>
+        <v>120094922</v>
       </c>
       <c r="B43" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5146,34 +5125,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>746304</v>
+        <v>746442</v>
       </c>
       <c r="R43" t="n">
-        <v>7152657</v>
+        <v>7152565</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5214,6 +5196,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5232,10 +5215,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120080341</v>
+        <v>120080306</v>
       </c>
       <c r="B44" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5244,25 +5227,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5272,10 +5255,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>746384</v>
+        <v>746490</v>
       </c>
       <c r="R44" t="n">
-        <v>7152544</v>
+        <v>7152502</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5334,7 +5317,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120080345</v>
+        <v>120094959</v>
       </c>
       <c r="B45" t="n">
         <v>91840</v>
@@ -5368,16 +5351,19 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>746459</v>
+        <v>746300</v>
       </c>
       <c r="R45" t="n">
-        <v>7152465</v>
+        <v>7152654</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5418,28 +5404,29 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120086269</v>
+        <v>120094951</v>
       </c>
       <c r="B46" t="n">
-        <v>88153</v>
+        <v>91840</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5448,25 +5435,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5479,10 +5466,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>746365</v>
+        <v>746357</v>
       </c>
       <c r="R46" t="n">
-        <v>7152575</v>
+        <v>7152686</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5515,11 +5502,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Inte ihålig men övriga karaktärer stämde.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5547,7 +5529,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120094855</v>
+        <v>120094869</v>
       </c>
       <c r="B47" t="n">
         <v>91840</v>
@@ -5590,10 +5572,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>746547</v>
+        <v>746522</v>
       </c>
       <c r="R47" t="n">
-        <v>7152471</v>
+        <v>7152453</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5653,10 +5635,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120086280</v>
+        <v>120079809</v>
       </c>
       <c r="B48" t="n">
-        <v>78526</v>
+        <v>90712</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5665,41 +5647,44 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>746527</v>
+        <v>746368</v>
       </c>
       <c r="R48" t="n">
-        <v>7152434</v>
+        <v>7152599</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5737,28 +5722,29 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120086263</v>
+        <v>120086277</v>
       </c>
       <c r="B49" t="n">
-        <v>92030</v>
+        <v>78526</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5771,21 +5757,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5795,10 +5781,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>746450</v>
+        <v>746302</v>
       </c>
       <c r="R49" t="n">
-        <v>7152549</v>
+        <v>7152670</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5857,7 +5843,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120086274</v>
+        <v>120086276</v>
       </c>
       <c r="B50" t="n">
         <v>78526</v>
@@ -5897,10 +5883,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>746478</v>
+        <v>746304</v>
       </c>
       <c r="R50" t="n">
-        <v>7152496</v>
+        <v>7152657</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5959,10 +5945,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120080306</v>
+        <v>120086274</v>
       </c>
       <c r="B51" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5975,21 +5961,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5999,10 +5985,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>746490</v>
+        <v>746478</v>
       </c>
       <c r="R51" t="n">
-        <v>7152502</v>
+        <v>7152496</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6049,22 +6035,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120080319</v>
+        <v>120080307</v>
       </c>
       <c r="B52" t="n">
-        <v>92030</v>
+        <v>91884</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6077,21 +6063,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2079</v>
+        <v>5449</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6101,10 +6087,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>746477</v>
+        <v>746426</v>
       </c>
       <c r="R52" t="n">
-        <v>7152502</v>
+        <v>7152510</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6139,11 +6125,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På kolad tallstubbe</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6152,26 +6133,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL52" t="inlineStr">
-        <is>
-          <t>Kolad tallstubbe</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Kolad tallstubbe</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6188,10 +6149,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120080342</v>
+        <v>120086291</v>
       </c>
       <c r="B53" t="n">
-        <v>91840</v>
+        <v>90807</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6200,25 +6161,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6228,10 +6189,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>746478</v>
+        <v>746502</v>
       </c>
       <c r="R53" t="n">
-        <v>7152487</v>
+        <v>7152478</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6278,22 +6239,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120086228</v>
+        <v>120080338</v>
       </c>
       <c r="B54" t="n">
-        <v>74638</v>
+        <v>91840</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6302,25 +6263,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6330,10 +6291,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>746357</v>
+        <v>746455</v>
       </c>
       <c r="R54" t="n">
-        <v>7152581</v>
+        <v>7152561</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6380,19 +6341,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120079802</v>
+        <v>120094916</v>
       </c>
       <c r="B55" t="n">
         <v>91884</v>
@@ -6426,19 +6387,22 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>746495</v>
+        <v>746490</v>
       </c>
       <c r="R55" t="n">
-        <v>7152470</v>
+        <v>7152513</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6476,28 +6440,29 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120086238</v>
+        <v>120086259</v>
       </c>
       <c r="B56" t="n">
-        <v>57463</v>
+        <v>91832</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6510,42 +6475,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>746509</v>
+        <v>746394</v>
       </c>
       <c r="R56" t="n">
-        <v>7152434</v>
+        <v>7152581</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6578,11 +6535,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Två</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6609,10 +6561,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120086275</v>
+        <v>120080349</v>
       </c>
       <c r="B57" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6621,25 +6573,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6649,10 +6601,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>746370</v>
+        <v>746540</v>
       </c>
       <c r="R57" t="n">
-        <v>7152601</v>
+        <v>7152444</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6699,19 +6651,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120094932</v>
+        <v>120079812</v>
       </c>
       <c r="B58" t="n">
         <v>91840</v>
@@ -6745,22 +6697,19 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>746414</v>
+        <v>746540</v>
       </c>
       <c r="R58" t="n">
-        <v>7152584</v>
+        <v>7152434</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6805,22 +6754,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120094907</v>
+        <v>120086275</v>
       </c>
       <c r="B59" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6829,41 +6778,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>746484</v>
+        <v>746370</v>
       </c>
       <c r="R59" t="n">
-        <v>7152510</v>
+        <v>7152601</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6904,7 +6850,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6923,10 +6868,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120080307</v>
+        <v>120086269</v>
       </c>
       <c r="B60" t="n">
-        <v>91884</v>
+        <v>88153</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6939,34 +6884,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5449</v>
+        <v>4962</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>746426</v>
+        <v>746365</v>
       </c>
       <c r="R60" t="n">
-        <v>7152510</v>
+        <v>7152575</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7001,34 +6949,40 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Inte ihålig men övriga karaktärer stämde.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120086245</v>
+        <v>120080295</v>
       </c>
       <c r="B61" t="n">
-        <v>91884</v>
+        <v>57463</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7041,34 +6995,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>746365</v>
+        <v>746385</v>
       </c>
       <c r="R61" t="n">
-        <v>7152575</v>
+        <v>7152570</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7115,22 +7077,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120086277</v>
+        <v>120080343</v>
       </c>
       <c r="B62" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7139,25 +7101,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7167,10 +7129,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>746302</v>
+        <v>746467</v>
       </c>
       <c r="R62" t="n">
-        <v>7152670</v>
+        <v>7152466</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7217,19 +7179,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120086295</v>
+        <v>120094855</v>
       </c>
       <c r="B63" t="n">
         <v>91840</v>
@@ -7263,16 +7225,19 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>746365</v>
+        <v>746547</v>
       </c>
       <c r="R63" t="n">
-        <v>7152695</v>
+        <v>7152471</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7313,6 +7278,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7331,10 +7297,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120086296</v>
+        <v>120086230</v>
       </c>
       <c r="B64" t="n">
-        <v>91840</v>
+        <v>90527</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7347,21 +7313,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7371,10 +7337,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>746425</v>
+        <v>746412</v>
       </c>
       <c r="R64" t="n">
-        <v>7152621</v>
+        <v>7152564</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7433,10 +7399,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120094916</v>
+        <v>120094932</v>
       </c>
       <c r="B65" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7445,25 +7411,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7476,10 +7442,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>746490</v>
+        <v>746414</v>
       </c>
       <c r="R65" t="n">
-        <v>7152513</v>
+        <v>7152584</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7539,10 +7505,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120086230</v>
+        <v>120086294</v>
       </c>
       <c r="B66" t="n">
-        <v>90527</v>
+        <v>91840</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7555,21 +7521,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7579,10 +7545,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>746412</v>
+        <v>746310</v>
       </c>
       <c r="R66" t="n">
-        <v>7152564</v>
+        <v>7152670</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7641,10 +7607,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120094939</v>
+        <v>120080319</v>
       </c>
       <c r="B67" t="n">
-        <v>91840</v>
+        <v>92030</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7653,41 +7619,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>746413</v>
+        <v>746477</v>
       </c>
       <c r="R67" t="n">
-        <v>7152616</v>
+        <v>7152502</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7722,35 +7685,59 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På kolad tallstubbe</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL67" t="inlineStr">
+        <is>
+          <t>Kolad tallstubbe</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Kolad tallstubbe</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120080349</v>
+        <v>120086266</v>
       </c>
       <c r="B68" t="n">
-        <v>91840</v>
+        <v>91863</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7759,25 +7746,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7787,10 +7774,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>746540</v>
+        <v>746429</v>
       </c>
       <c r="R68" t="n">
-        <v>7152444</v>
+        <v>7152625</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7837,19 +7824,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120080337</v>
+        <v>120080348</v>
       </c>
       <c r="B69" t="n">
         <v>91840</v>
@@ -7889,10 +7876,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>746488</v>
+        <v>746505</v>
       </c>
       <c r="R69" t="n">
-        <v>7152500</v>
+        <v>7152451</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7951,7 +7938,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120094951</v>
+        <v>120080336</v>
       </c>
       <c r="B70" t="n">
         <v>91840</v>
@@ -7985,19 +7972,16 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>746357</v>
+        <v>746545</v>
       </c>
       <c r="R70" t="n">
-        <v>7152686</v>
+        <v>7152464</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8038,29 +8022,28 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120086291</v>
+        <v>120080326</v>
       </c>
       <c r="B71" t="n">
-        <v>90807</v>
+        <v>89230</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8073,21 +8056,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>65</v>
+        <v>1596</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8097,10 +8080,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>746502</v>
+        <v>746543</v>
       </c>
       <c r="R71" t="n">
-        <v>7152478</v>
+        <v>7152437</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8147,22 +8130,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120086278</v>
+        <v>120094897</v>
       </c>
       <c r="B72" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8171,38 +8154,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>746365</v>
+        <v>746482</v>
       </c>
       <c r="R72" t="n">
-        <v>7152695</v>
+        <v>7152467</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8243,6 +8229,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8261,10 +8248,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120086272</v>
+        <v>120086278</v>
       </c>
       <c r="B73" t="n">
-        <v>74624</v>
+        <v>78526</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8273,25 +8260,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8301,10 +8288,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>746357</v>
+        <v>746365</v>
       </c>
       <c r="R73" t="n">
-        <v>7152581</v>
+        <v>7152695</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8363,10 +8350,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120086259</v>
+        <v>120086245</v>
       </c>
       <c r="B74" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8379,21 +8366,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8403,10 +8390,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>746394</v>
+        <v>746365</v>
       </c>
       <c r="R74" t="n">
-        <v>7152581</v>
+        <v>7152575</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8465,10 +8452,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120086265</v>
+        <v>120086279</v>
       </c>
       <c r="B75" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8481,21 +8468,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8505,10 +8492,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>746353</v>
+        <v>746397</v>
       </c>
       <c r="R75" t="n">
-        <v>7152592</v>
+        <v>7152654</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8567,10 +8554,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120079805</v>
+        <v>120079802</v>
       </c>
       <c r="B76" t="n">
-        <v>92030</v>
+        <v>91884</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8583,21 +8570,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2079</v>
+        <v>5449</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8607,10 +8594,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>746437</v>
+        <v>746495</v>
       </c>
       <c r="R76" t="n">
-        <v>7152508</v>
+        <v>7152470</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8669,10 +8656,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120079813</v>
+        <v>120086272</v>
       </c>
       <c r="B77" t="n">
-        <v>91840</v>
+        <v>74624</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8685,21 +8672,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8709,13 +8696,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>746517</v>
+        <v>746357</v>
       </c>
       <c r="R77" t="n">
-        <v>7152485</v>
+        <v>7152581</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8759,22 +8746,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120079809</v>
+        <v>120080342</v>
       </c>
       <c r="B78" t="n">
-        <v>90712</v>
+        <v>91840</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8783,44 +8770,41 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>746368</v>
+        <v>746478</v>
       </c>
       <c r="R78" t="n">
-        <v>7152599</v>
+        <v>7152487</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8858,29 +8842,28 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120080338</v>
+        <v>120079805</v>
       </c>
       <c r="B79" t="n">
-        <v>91840</v>
+        <v>92030</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8889,25 +8872,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8917,13 +8900,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>746455</v>
+        <v>746437</v>
       </c>
       <c r="R79" t="n">
-        <v>7152561</v>
+        <v>7152508</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8967,22 +8950,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120080326</v>
+        <v>120079813</v>
       </c>
       <c r="B80" t="n">
-        <v>89230</v>
+        <v>91840</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8991,25 +8974,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1596</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9019,13 +9002,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>746543</v>
+        <v>746517</v>
       </c>
       <c r="R80" t="n">
-        <v>7152437</v>
+        <v>7152485</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9069,22 +9052,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120080340</v>
+        <v>120094945</v>
       </c>
       <c r="B81" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9093,38 +9076,41 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>746398</v>
+        <v>746417</v>
       </c>
       <c r="R81" t="n">
-        <v>7152548</v>
+        <v>7152628</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9165,28 +9151,29 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120080343</v>
+        <v>120086238</v>
       </c>
       <c r="B82" t="n">
-        <v>91840</v>
+        <v>57463</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9195,38 +9182,46 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>746467</v>
+        <v>746509</v>
       </c>
       <c r="R82" t="n">
-        <v>7152466</v>
+        <v>7152434</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9261,6 +9256,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Två</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9273,22 +9273,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120086279</v>
+        <v>120080345</v>
       </c>
       <c r="B83" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9297,25 +9297,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9325,10 +9325,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>746397</v>
+        <v>746459</v>
       </c>
       <c r="R83" t="n">
-        <v>7152654</v>
+        <v>7152465</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9375,22 +9375,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120094945</v>
+        <v>120094849</v>
       </c>
       <c r="B84" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9399,25 +9399,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9430,10 +9430,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>746417</v>
+        <v>746531</v>
       </c>
       <c r="R84" t="n">
-        <v>7152628</v>
+        <v>7152454</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9493,7 +9493,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120094886</v>
+        <v>120094939</v>
       </c>
       <c r="B85" t="n">
         <v>91840</v>
@@ -9536,10 +9536,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>746500</v>
+        <v>746413</v>
       </c>
       <c r="R85" t="n">
-        <v>7152466</v>
+        <v>7152616</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>

--- a/artfynd/A 41672-2024 artfynd.xlsx
+++ b/artfynd/A 41672-2024 artfynd.xlsx
@@ -2579,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120068331</v>
+        <v>120068346</v>
       </c>
       <c r="B19" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2595,21 +2595,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>746318</v>
+        <v>746324</v>
       </c>
       <c r="R19" t="n">
-        <v>7152701</v>
+        <v>7152703</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120068346</v>
+        <v>120068331</v>
       </c>
       <c r="B20" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2707,21 +2707,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>746324</v>
+        <v>746318</v>
       </c>
       <c r="R20" t="n">
-        <v>7152703</v>
+        <v>7152701</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -5423,10 +5423,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120094951</v>
+        <v>120079809</v>
       </c>
       <c r="B46" t="n">
-        <v>91840</v>
+        <v>90712</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5435,25 +5435,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5466,13 +5466,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>746357</v>
+        <v>746368</v>
       </c>
       <c r="R46" t="n">
-        <v>7152686</v>
+        <v>7152599</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5517,19 +5517,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120094869</v>
+        <v>120094951</v>
       </c>
       <c r="B47" t="n">
         <v>91840</v>
@@ -5572,10 +5572,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>746522</v>
+        <v>746357</v>
       </c>
       <c r="R47" t="n">
-        <v>7152453</v>
+        <v>7152686</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5635,10 +5635,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120079809</v>
+        <v>120094869</v>
       </c>
       <c r="B48" t="n">
-        <v>90712</v>
+        <v>91840</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5647,25 +5647,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5678,13 +5678,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>746368</v>
+        <v>746522</v>
       </c>
       <c r="R48" t="n">
-        <v>7152599</v>
+        <v>7152453</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5729,12 +5729,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6766,10 +6766,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120086275</v>
+        <v>120086269</v>
       </c>
       <c r="B59" t="n">
-        <v>78526</v>
+        <v>88153</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6782,34 +6782,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>4962</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>746370</v>
+        <v>746365</v>
       </c>
       <c r="R59" t="n">
-        <v>7152601</v>
+        <v>7152575</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6844,12 +6847,18 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Inte ihålig men övriga karaktärer stämde.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6868,10 +6877,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120086269</v>
+        <v>120086275</v>
       </c>
       <c r="B60" t="n">
-        <v>88153</v>
+        <v>78526</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6884,37 +6893,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4962</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>746365</v>
+        <v>746370</v>
       </c>
       <c r="R60" t="n">
-        <v>7152575</v>
+        <v>7152601</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6949,18 +6955,12 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Inte ihålig men övriga karaktärer stämde.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7399,10 +7399,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120094932</v>
+        <v>120080319</v>
       </c>
       <c r="B65" t="n">
-        <v>91840</v>
+        <v>92030</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7411,41 +7411,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>746414</v>
+        <v>746477</v>
       </c>
       <c r="R65" t="n">
-        <v>7152584</v>
+        <v>7152502</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7480,32 +7477,56 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På kolad tallstubbe</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL65" t="inlineStr">
+        <is>
+          <t>Kolad tallstubbe</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Kolad tallstubbe</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120086294</v>
+        <v>120094932</v>
       </c>
       <c r="B66" t="n">
         <v>91840</v>
@@ -7539,16 +7560,19 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>746310</v>
+        <v>746414</v>
       </c>
       <c r="R66" t="n">
-        <v>7152670</v>
+        <v>7152584</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7589,6 +7613,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7607,10 +7632,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120080319</v>
+        <v>120086294</v>
       </c>
       <c r="B67" t="n">
-        <v>92030</v>
+        <v>91840</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7619,25 +7644,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7647,10 +7672,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>746477</v>
+        <v>746310</v>
       </c>
       <c r="R67" t="n">
-        <v>7152502</v>
+        <v>7152670</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7685,11 +7710,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På kolad tallstubbe</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7698,46 +7718,26 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL67" t="inlineStr">
-        <is>
-          <t>Kolad tallstubbe</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Kolad tallstubbe</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120086266</v>
+        <v>120080348</v>
       </c>
       <c r="B68" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7746,25 +7746,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7774,10 +7774,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>746429</v>
+        <v>746505</v>
       </c>
       <c r="R68" t="n">
-        <v>7152625</v>
+        <v>7152451</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7824,19 +7824,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120080348</v>
+        <v>120080336</v>
       </c>
       <c r="B69" t="n">
         <v>91840</v>
@@ -7876,10 +7876,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>746505</v>
+        <v>746545</v>
       </c>
       <c r="R69" t="n">
-        <v>7152451</v>
+        <v>7152464</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7938,10 +7938,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120080336</v>
+        <v>120086266</v>
       </c>
       <c r="B70" t="n">
-        <v>91840</v>
+        <v>91863</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7950,25 +7950,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7978,10 +7978,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>746545</v>
+        <v>746429</v>
       </c>
       <c r="R70" t="n">
-        <v>7152464</v>
+        <v>7152625</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8028,12 +8028,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8554,10 +8554,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120079802</v>
+        <v>120086272</v>
       </c>
       <c r="B76" t="n">
-        <v>91884</v>
+        <v>74624</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8566,25 +8566,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5449</v>
+        <v>306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8594,13 +8594,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>746495</v>
+        <v>746357</v>
       </c>
       <c r="R76" t="n">
-        <v>7152470</v>
+        <v>7152581</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8644,22 +8644,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120086272</v>
+        <v>120080342</v>
       </c>
       <c r="B77" t="n">
-        <v>74624</v>
+        <v>91840</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8672,21 +8672,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>306</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8696,10 +8696,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>746357</v>
+        <v>746478</v>
       </c>
       <c r="R77" t="n">
-        <v>7152581</v>
+        <v>7152487</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8746,22 +8746,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120080342</v>
+        <v>120079802</v>
       </c>
       <c r="B78" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8770,25 +8770,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8798,13 +8798,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>746478</v>
+        <v>746495</v>
       </c>
       <c r="R78" t="n">
-        <v>7152487</v>
+        <v>7152470</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8848,12 +8848,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>

--- a/artfynd/A 41672-2024 artfynd.xlsx
+++ b/artfynd/A 41672-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120068460</v>
+        <v>120068346</v>
       </c>
       <c r="B2" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>746312</v>
+        <v>746324</v>
       </c>
       <c r="R2" t="n">
-        <v>7152709</v>
+        <v>7152703</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120068300</v>
+        <v>120066631</v>
       </c>
       <c r="B3" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>746336</v>
+        <v>746551</v>
       </c>
       <c r="R3" t="n">
-        <v>7152676</v>
+        <v>7152434</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120067430</v>
+        <v>120067935</v>
       </c>
       <c r="B4" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>746505</v>
+        <v>746381</v>
       </c>
       <c r="R4" t="n">
-        <v>7152499</v>
+        <v>7152596</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120067262</v>
+        <v>120067137</v>
       </c>
       <c r="B5" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
         <v>746520</v>
       </c>
       <c r="R5" t="n">
-        <v>7152494</v>
+        <v>7152487</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120067979</v>
+        <v>120068080</v>
       </c>
       <c r="B6" t="n">
         <v>91840</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>746392</v>
+        <v>746371</v>
       </c>
       <c r="R6" t="n">
-        <v>7152615</v>
+        <v>7152632</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120068365</v>
+        <v>120068133</v>
       </c>
       <c r="B7" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>746323</v>
+        <v>746333</v>
       </c>
       <c r="R7" t="n">
-        <v>7152700</v>
+        <v>7152647</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120068602</v>
+        <v>120067885</v>
       </c>
       <c r="B8" t="n">
-        <v>79636</v>
+        <v>91884</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>5449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>746307</v>
+        <v>746399</v>
       </c>
       <c r="R8" t="n">
-        <v>7152647</v>
+        <v>7152617</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120068383</v>
+        <v>120069457</v>
       </c>
       <c r="B9" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,25 +1471,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>746313</v>
+        <v>746379</v>
       </c>
       <c r="R9" t="n">
-        <v>7152706</v>
+        <v>7152575</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120069608</v>
+        <v>120067568</v>
       </c>
       <c r="B10" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,25 +1583,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>746422</v>
+        <v>746484</v>
       </c>
       <c r="R10" t="n">
-        <v>7152546</v>
+        <v>7152500</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120067137</v>
+        <v>120068365</v>
       </c>
       <c r="B12" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>746520</v>
+        <v>746323</v>
       </c>
       <c r="R12" t="n">
-        <v>7152487</v>
+        <v>7152700</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120067885</v>
+        <v>120067504</v>
       </c>
       <c r="B13" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,21 +1923,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>746399</v>
+        <v>746486</v>
       </c>
       <c r="R13" t="n">
-        <v>7152617</v>
+        <v>7152501</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120067504</v>
+        <v>120068383</v>
       </c>
       <c r="B14" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2031,25 +2031,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>746486</v>
+        <v>746313</v>
       </c>
       <c r="R14" t="n">
-        <v>7152501</v>
+        <v>7152706</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120068080</v>
+        <v>120067430</v>
       </c>
       <c r="B15" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2143,25 +2143,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>746371</v>
+        <v>746505</v>
       </c>
       <c r="R15" t="n">
-        <v>7152632</v>
+        <v>7152499</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120066896</v>
+        <v>120068602</v>
       </c>
       <c r="B16" t="n">
-        <v>91863</v>
+        <v>79636</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2255,25 +2255,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>746537</v>
+        <v>746307</v>
       </c>
       <c r="R16" t="n">
-        <v>7152456</v>
+        <v>7152647</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,7 +2355,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120067935</v>
+        <v>120067979</v>
       </c>
       <c r="B17" t="n">
         <v>91840</v>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>746381</v>
+        <v>746392</v>
       </c>
       <c r="R17" t="n">
-        <v>7152596</v>
+        <v>7152615</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,7 +2467,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120068133</v>
+        <v>120067841</v>
       </c>
       <c r="B18" t="n">
         <v>91840</v>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>746333</v>
+        <v>746469</v>
       </c>
       <c r="R18" t="n">
-        <v>7152647</v>
+        <v>7152569</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120068346</v>
+        <v>120068300</v>
       </c>
       <c r="B19" t="n">
-        <v>91852</v>
+        <v>91863</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2591,25 +2591,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>746324</v>
+        <v>746336</v>
       </c>
       <c r="R19" t="n">
-        <v>7152703</v>
+        <v>7152676</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,7 +2691,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120068331</v>
+        <v>120068460</v>
       </c>
       <c r="B20" t="n">
         <v>91840</v>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>746318</v>
+        <v>746312</v>
       </c>
       <c r="R20" t="n">
-        <v>7152701</v>
+        <v>7152709</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,7 +2803,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120066631</v>
+        <v>120067262</v>
       </c>
       <c r="B21" t="n">
         <v>91840</v>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>746551</v>
+        <v>746520</v>
       </c>
       <c r="R21" t="n">
-        <v>7152434</v>
+        <v>7152494</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,7 +2915,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120067568</v>
+        <v>120068255</v>
       </c>
       <c r="B22" t="n">
         <v>91840</v>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>746484</v>
+        <v>746352</v>
       </c>
       <c r="R22" t="n">
-        <v>7152500</v>
+        <v>7152686</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,10 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120069457</v>
+        <v>120068331</v>
       </c>
       <c r="B23" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3039,25 +3039,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>746379</v>
+        <v>746318</v>
       </c>
       <c r="R23" t="n">
-        <v>7152575</v>
+        <v>7152701</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,10 +3139,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120067841</v>
+        <v>120069608</v>
       </c>
       <c r="B24" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3151,25 +3151,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>746469</v>
+        <v>746422</v>
       </c>
       <c r="R24" t="n">
-        <v>7152569</v>
+        <v>7152546</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3251,10 +3251,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120068255</v>
+        <v>120066896</v>
       </c>
       <c r="B25" t="n">
-        <v>91840</v>
+        <v>91863</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3263,25 +3263,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>746352</v>
+        <v>746537</v>
       </c>
       <c r="R25" t="n">
-        <v>7152686</v>
+        <v>7152456</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3363,7 +3363,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120094901</v>
+        <v>120094869</v>
       </c>
       <c r="B26" t="n">
         <v>91840</v>
@@ -3406,10 +3406,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>746487</v>
+        <v>746522</v>
       </c>
       <c r="R26" t="n">
-        <v>7152494</v>
+        <v>7152453</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3469,10 +3469,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120079797</v>
+        <v>120086245</v>
       </c>
       <c r="B27" t="n">
-        <v>89633</v>
+        <v>91884</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3485,21 +3485,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1962</v>
+        <v>5449</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>746432</v>
+        <v>746365</v>
       </c>
       <c r="R27" t="n">
-        <v>7152509</v>
+        <v>7152575</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3559,22 +3559,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120086295</v>
+        <v>120080326</v>
       </c>
       <c r="B28" t="n">
-        <v>91840</v>
+        <v>89230</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3583,25 +3583,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>1596</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3611,10 +3611,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>746365</v>
+        <v>746543</v>
       </c>
       <c r="R28" t="n">
-        <v>7152695</v>
+        <v>7152437</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3661,22 +3661,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120080337</v>
+        <v>120079809</v>
       </c>
       <c r="B29" t="n">
-        <v>91840</v>
+        <v>90712</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3685,41 +3685,44 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>746488</v>
+        <v>746368</v>
       </c>
       <c r="R29" t="n">
-        <v>7152500</v>
+        <v>7152599</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3757,28 +3760,29 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120086246</v>
+        <v>120086298</v>
       </c>
       <c r="B30" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3787,25 +3791,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3815,10 +3819,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>746475</v>
+        <v>746527</v>
       </c>
       <c r="R30" t="n">
-        <v>7152487</v>
+        <v>7152434</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3877,7 +3881,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120080341</v>
+        <v>120094951</v>
       </c>
       <c r="B31" t="n">
         <v>91840</v>
@@ -3911,16 +3915,19 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>746384</v>
+        <v>746357</v>
       </c>
       <c r="R31" t="n">
-        <v>7152544</v>
+        <v>7152686</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3961,28 +3968,29 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120086265</v>
+        <v>120080345</v>
       </c>
       <c r="B32" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3991,25 +3999,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4019,10 +4027,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>746353</v>
+        <v>746459</v>
       </c>
       <c r="R32" t="n">
-        <v>7152592</v>
+        <v>7152465</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4069,19 +4077,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120080340</v>
+        <v>120094907</v>
       </c>
       <c r="B33" t="n">
         <v>91840</v>
@@ -4115,16 +4123,19 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>746398</v>
+        <v>746484</v>
       </c>
       <c r="R33" t="n">
-        <v>7152548</v>
+        <v>7152510</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4165,28 +4176,29 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120086280</v>
+        <v>120086265</v>
       </c>
       <c r="B34" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4199,21 +4211,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4223,10 +4235,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>746527</v>
+        <v>746353</v>
       </c>
       <c r="R34" t="n">
-        <v>7152434</v>
+        <v>7152592</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4285,10 +4297,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120086228</v>
+        <v>120079812</v>
       </c>
       <c r="B35" t="n">
-        <v>74638</v>
+        <v>91840</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4297,25 +4309,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4325,13 +4337,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>746357</v>
+        <v>746540</v>
       </c>
       <c r="R35" t="n">
-        <v>7152581</v>
+        <v>7152434</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4369,28 +4381,29 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120086296</v>
+        <v>120086246</v>
       </c>
       <c r="B36" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4399,25 +4412,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4427,10 +4440,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>746425</v>
+        <v>746475</v>
       </c>
       <c r="R36" t="n">
-        <v>7152621</v>
+        <v>7152487</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4489,7 +4502,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120094886</v>
+        <v>120080341</v>
       </c>
       <c r="B37" t="n">
         <v>91840</v>
@@ -4523,19 +4536,16 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>746500</v>
+        <v>746384</v>
       </c>
       <c r="R37" t="n">
-        <v>7152466</v>
+        <v>7152544</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4576,26 +4586,25 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120094907</v>
+        <v>120080349</v>
       </c>
       <c r="B38" t="n">
         <v>91840</v>
@@ -4629,19 +4638,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>746484</v>
+        <v>746540</v>
       </c>
       <c r="R38" t="n">
-        <v>7152510</v>
+        <v>7152444</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4682,29 +4688,28 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120086263</v>
+        <v>120079797</v>
       </c>
       <c r="B39" t="n">
-        <v>92030</v>
+        <v>89633</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4717,21 +4722,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4741,13 +4746,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>746450</v>
+        <v>746432</v>
       </c>
       <c r="R39" t="n">
-        <v>7152549</v>
+        <v>7152509</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4791,19 +4796,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120086297</v>
+        <v>120094901</v>
       </c>
       <c r="B40" t="n">
         <v>91840</v>
@@ -4837,16 +4842,19 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>746473</v>
+        <v>746487</v>
       </c>
       <c r="R40" t="n">
-        <v>7152499</v>
+        <v>7152494</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4887,6 +4895,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4905,10 +4914,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120086298</v>
+        <v>120094922</v>
       </c>
       <c r="B41" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4917,38 +4926,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>746527</v>
+        <v>746442</v>
       </c>
       <c r="R41" t="n">
-        <v>7152434</v>
+        <v>7152565</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4989,6 +5001,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5007,10 +5020,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120080346</v>
+        <v>120086291</v>
       </c>
       <c r="B42" t="n">
-        <v>91840</v>
+        <v>90807</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5019,25 +5032,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5047,10 +5060,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>746461</v>
+        <v>746502</v>
       </c>
       <c r="R42" t="n">
-        <v>7152458</v>
+        <v>7152478</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5097,22 +5110,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120094922</v>
+        <v>120086263</v>
       </c>
       <c r="B43" t="n">
-        <v>91884</v>
+        <v>92030</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5125,37 +5138,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5449</v>
+        <v>2079</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>746442</v>
+        <v>746450</v>
       </c>
       <c r="R43" t="n">
-        <v>7152565</v>
+        <v>7152549</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5196,7 +5206,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5215,10 +5224,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120080306</v>
+        <v>120080340</v>
       </c>
       <c r="B44" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5227,25 +5236,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5255,10 +5264,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>746490</v>
+        <v>746398</v>
       </c>
       <c r="R44" t="n">
-        <v>7152502</v>
+        <v>7152548</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5317,7 +5326,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120094959</v>
+        <v>120080336</v>
       </c>
       <c r="B45" t="n">
         <v>91840</v>
@@ -5351,19 +5360,16 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>746300</v>
+        <v>746545</v>
       </c>
       <c r="R45" t="n">
-        <v>7152654</v>
+        <v>7152464</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5404,29 +5410,28 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120079809</v>
+        <v>120086278</v>
       </c>
       <c r="B46" t="n">
-        <v>90712</v>
+        <v>78526</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5435,44 +5440,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>746368</v>
+        <v>746365</v>
       </c>
       <c r="R46" t="n">
-        <v>7152599</v>
+        <v>7152695</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5510,26 +5512,25 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120094951</v>
+        <v>120094897</v>
       </c>
       <c r="B47" t="n">
         <v>91840</v>
@@ -5572,10 +5573,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>746357</v>
+        <v>746482</v>
       </c>
       <c r="R47" t="n">
-        <v>7152686</v>
+        <v>7152467</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5635,10 +5636,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120094869</v>
+        <v>120094945</v>
       </c>
       <c r="B48" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5647,25 +5648,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5678,10 +5679,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>746522</v>
+        <v>746417</v>
       </c>
       <c r="R48" t="n">
-        <v>7152453</v>
+        <v>7152628</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5741,10 +5742,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120086277</v>
+        <v>120094959</v>
       </c>
       <c r="B49" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5753,38 +5754,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>746302</v>
+        <v>746300</v>
       </c>
       <c r="R49" t="n">
-        <v>7152670</v>
+        <v>7152654</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5825,6 +5829,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5843,10 +5848,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120086276</v>
+        <v>120094932</v>
       </c>
       <c r="B50" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5855,38 +5860,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>746304</v>
+        <v>746414</v>
       </c>
       <c r="R50" t="n">
-        <v>7152657</v>
+        <v>7152584</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5927,6 +5935,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5945,10 +5954,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120086274</v>
+        <v>120080306</v>
       </c>
       <c r="B51" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5961,21 +5970,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5985,10 +5994,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>746478</v>
+        <v>746490</v>
       </c>
       <c r="R51" t="n">
-        <v>7152496</v>
+        <v>7152502</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6035,22 +6044,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120080307</v>
+        <v>120086297</v>
       </c>
       <c r="B52" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6059,25 +6068,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6087,10 +6096,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>746426</v>
+        <v>746473</v>
       </c>
       <c r="R52" t="n">
-        <v>7152510</v>
+        <v>7152499</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6137,22 +6146,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120086291</v>
+        <v>120086276</v>
       </c>
       <c r="B53" t="n">
-        <v>90807</v>
+        <v>78526</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6161,25 +6170,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6189,10 +6198,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>746502</v>
+        <v>746304</v>
       </c>
       <c r="R53" t="n">
-        <v>7152478</v>
+        <v>7152657</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6251,10 +6260,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120080338</v>
+        <v>120086266</v>
       </c>
       <c r="B54" t="n">
-        <v>91840</v>
+        <v>91863</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6263,25 +6272,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6291,10 +6300,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>746455</v>
+        <v>746429</v>
       </c>
       <c r="R54" t="n">
-        <v>7152561</v>
+        <v>7152625</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6341,22 +6350,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120094916</v>
+        <v>120086238</v>
       </c>
       <c r="B55" t="n">
-        <v>91884</v>
+        <v>57463</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6369,26 +6378,31 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6396,10 +6410,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>746490</v>
+        <v>746509</v>
       </c>
       <c r="R55" t="n">
-        <v>7152513</v>
+        <v>7152434</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6434,13 +6448,17 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Två</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6459,10 +6477,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120086259</v>
+        <v>120094886</v>
       </c>
       <c r="B56" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6471,38 +6489,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>746394</v>
+        <v>746500</v>
       </c>
       <c r="R56" t="n">
-        <v>7152581</v>
+        <v>7152466</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6543,6 +6564,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6561,10 +6583,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120080349</v>
+        <v>120086272</v>
       </c>
       <c r="B57" t="n">
-        <v>91840</v>
+        <v>74624</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6577,21 +6599,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6601,10 +6623,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>746540</v>
+        <v>746357</v>
       </c>
       <c r="R57" t="n">
-        <v>7152444</v>
+        <v>7152581</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6651,22 +6673,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120079812</v>
+        <v>120080319</v>
       </c>
       <c r="B58" t="n">
-        <v>91840</v>
+        <v>92030</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6675,25 +6697,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6703,13 +6725,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>746540</v>
+        <v>746477</v>
       </c>
       <c r="R58" t="n">
-        <v>7152434</v>
+        <v>7152502</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6741,35 +6763,59 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På kolad tallstubbe</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL58" t="inlineStr">
+        <is>
+          <t>Kolad tallstubbe</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Kolad tallstubbe</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120086269</v>
+        <v>120080348</v>
       </c>
       <c r="B59" t="n">
-        <v>88153</v>
+        <v>91840</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6778,41 +6824,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>746365</v>
+        <v>746505</v>
       </c>
       <c r="R59" t="n">
-        <v>7152575</v>
+        <v>7152451</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6847,37 +6890,31 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Inte ihålig men övriga karaktärer stämde.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120086275</v>
+        <v>120086277</v>
       </c>
       <c r="B60" t="n">
         <v>78526</v>
@@ -6917,10 +6954,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>746370</v>
+        <v>746302</v>
       </c>
       <c r="R60" t="n">
-        <v>7152601</v>
+        <v>7152670</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7089,7 +7126,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120080343</v>
+        <v>120086295</v>
       </c>
       <c r="B62" t="n">
         <v>91840</v>
@@ -7129,10 +7166,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>746467</v>
+        <v>746365</v>
       </c>
       <c r="R62" t="n">
-        <v>7152466</v>
+        <v>7152695</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7179,19 +7216,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120094855</v>
+        <v>120094939</v>
       </c>
       <c r="B63" t="n">
         <v>91840</v>
@@ -7234,10 +7271,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>746547</v>
+        <v>746413</v>
       </c>
       <c r="R63" t="n">
-        <v>7152471</v>
+        <v>7152616</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7297,10 +7334,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120086230</v>
+        <v>120080343</v>
       </c>
       <c r="B64" t="n">
-        <v>90527</v>
+        <v>91840</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7313,21 +7350,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7337,10 +7374,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>746412</v>
+        <v>746467</v>
       </c>
       <c r="R64" t="n">
-        <v>7152564</v>
+        <v>7152466</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7387,22 +7424,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120080319</v>
+        <v>120086279</v>
       </c>
       <c r="B65" t="n">
-        <v>92030</v>
+        <v>78526</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7415,21 +7452,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7439,10 +7476,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>746477</v>
+        <v>746397</v>
       </c>
       <c r="R65" t="n">
-        <v>7152502</v>
+        <v>7152654</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7477,11 +7514,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>På kolad tallstubbe</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7490,46 +7522,26 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL65" t="inlineStr">
-        <is>
-          <t>Kolad tallstubbe</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Kolad tallstubbe</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120094932</v>
+        <v>120086230</v>
       </c>
       <c r="B66" t="n">
-        <v>91840</v>
+        <v>90527</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7542,37 +7554,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>746414</v>
+        <v>746412</v>
       </c>
       <c r="R66" t="n">
-        <v>7152584</v>
+        <v>7152564</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7613,7 +7622,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7632,7 +7640,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120086294</v>
+        <v>120079813</v>
       </c>
       <c r="B67" t="n">
         <v>91840</v>
@@ -7672,13 +7680,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>746310</v>
+        <v>746517</v>
       </c>
       <c r="R67" t="n">
-        <v>7152670</v>
+        <v>7152485</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7722,19 +7730,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120080348</v>
+        <v>120086294</v>
       </c>
       <c r="B68" t="n">
         <v>91840</v>
@@ -7774,10 +7782,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>746505</v>
+        <v>746310</v>
       </c>
       <c r="R68" t="n">
-        <v>7152451</v>
+        <v>7152670</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7824,22 +7832,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120080336</v>
+        <v>120086259</v>
       </c>
       <c r="B69" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7848,25 +7856,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7876,10 +7884,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>746545</v>
+        <v>746394</v>
       </c>
       <c r="R69" t="n">
-        <v>7152464</v>
+        <v>7152581</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7926,22 +7934,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120086266</v>
+        <v>120094849</v>
       </c>
       <c r="B70" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7950,38 +7958,41 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>746429</v>
+        <v>746531</v>
       </c>
       <c r="R70" t="n">
-        <v>7152625</v>
+        <v>7152454</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8022,6 +8033,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8040,10 +8052,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120080326</v>
+        <v>120086280</v>
       </c>
       <c r="B71" t="n">
-        <v>89230</v>
+        <v>78526</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8052,25 +8064,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1596</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8080,10 +8092,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>746543</v>
+        <v>746527</v>
       </c>
       <c r="R71" t="n">
-        <v>7152437</v>
+        <v>7152434</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8130,22 +8142,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120094897</v>
+        <v>120094916</v>
       </c>
       <c r="B72" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8154,25 +8166,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8185,10 +8197,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>746482</v>
+        <v>746490</v>
       </c>
       <c r="R72" t="n">
-        <v>7152467</v>
+        <v>7152513</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8248,10 +8260,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120086278</v>
+        <v>120079805</v>
       </c>
       <c r="B73" t="n">
-        <v>78526</v>
+        <v>92030</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8264,21 +8276,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8288,13 +8300,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>746365</v>
+        <v>746437</v>
       </c>
       <c r="R73" t="n">
-        <v>7152695</v>
+        <v>7152508</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8338,22 +8350,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120086245</v>
+        <v>120086228</v>
       </c>
       <c r="B74" t="n">
-        <v>91884</v>
+        <v>74638</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8366,21 +8378,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5449</v>
+        <v>6440</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8390,10 +8402,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>746365</v>
+        <v>746357</v>
       </c>
       <c r="R74" t="n">
-        <v>7152575</v>
+        <v>7152581</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8452,7 +8464,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120086279</v>
+        <v>120086275</v>
       </c>
       <c r="B75" t="n">
         <v>78526</v>
@@ -8492,10 +8504,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>746397</v>
+        <v>746370</v>
       </c>
       <c r="R75" t="n">
-        <v>7152654</v>
+        <v>7152601</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8554,10 +8566,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120086272</v>
+        <v>120080307</v>
       </c>
       <c r="B76" t="n">
-        <v>74624</v>
+        <v>91884</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8566,25 +8578,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>306</v>
+        <v>5449</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8594,10 +8606,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>746357</v>
+        <v>746426</v>
       </c>
       <c r="R76" t="n">
-        <v>7152581</v>
+        <v>7152510</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8644,19 +8656,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120080342</v>
+        <v>120086296</v>
       </c>
       <c r="B77" t="n">
         <v>91840</v>
@@ -8696,10 +8708,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>746478</v>
+        <v>746425</v>
       </c>
       <c r="R77" t="n">
-        <v>7152487</v>
+        <v>7152621</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8746,22 +8758,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120079802</v>
+        <v>120080338</v>
       </c>
       <c r="B78" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8770,25 +8782,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8798,13 +8810,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>746495</v>
+        <v>746455</v>
       </c>
       <c r="R78" t="n">
-        <v>7152470</v>
+        <v>7152561</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8848,22 +8860,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120079805</v>
+        <v>120094855</v>
       </c>
       <c r="B79" t="n">
-        <v>92030</v>
+        <v>91840</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8872,41 +8884,44 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>746437</v>
+        <v>746547</v>
       </c>
       <c r="R79" t="n">
-        <v>7152508</v>
+        <v>7152471</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8944,28 +8959,29 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120079813</v>
+        <v>120086274</v>
       </c>
       <c r="B80" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8974,25 +8990,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9002,13 +9018,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>746517</v>
+        <v>746478</v>
       </c>
       <c r="R80" t="n">
-        <v>7152485</v>
+        <v>7152496</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9052,22 +9068,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120094945</v>
+        <v>120080346</v>
       </c>
       <c r="B81" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9076,41 +9092,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>746417</v>
+        <v>746461</v>
       </c>
       <c r="R81" t="n">
-        <v>7152628</v>
+        <v>7152458</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9151,29 +9164,28 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120086238</v>
+        <v>120080337</v>
       </c>
       <c r="B82" t="n">
-        <v>57463</v>
+        <v>91840</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9182,46 +9194,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>746509</v>
+        <v>746488</v>
       </c>
       <c r="R82" t="n">
-        <v>7152434</v>
+        <v>7152500</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9256,11 +9260,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Två</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9273,19 +9272,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120080345</v>
+        <v>120080342</v>
       </c>
       <c r="B83" t="n">
         <v>91840</v>
@@ -9325,10 +9324,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>746459</v>
+        <v>746478</v>
       </c>
       <c r="R83" t="n">
-        <v>7152465</v>
+        <v>7152487</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9387,10 +9386,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120094849</v>
+        <v>120079802</v>
       </c>
       <c r="B84" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9399,44 +9398,41 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>746531</v>
+        <v>746495</v>
       </c>
       <c r="R84" t="n">
-        <v>7152454</v>
+        <v>7152470</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9474,29 +9470,28 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120094939</v>
+        <v>120086269</v>
       </c>
       <c r="B85" t="n">
-        <v>91840</v>
+        <v>88153</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9505,25 +9500,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9536,10 +9531,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>746413</v>
+        <v>746365</v>
       </c>
       <c r="R85" t="n">
-        <v>7152616</v>
+        <v>7152575</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9572,6 +9567,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Inte ihålig men övriga karaktärer stämde.</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 41672-2024 artfynd.xlsx
+++ b/artfynd/A 41672-2024 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120066631</v>
+        <v>120067935</v>
       </c>
       <c r="B3" t="n">
         <v>91840</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>746551</v>
+        <v>746381</v>
       </c>
       <c r="R3" t="n">
-        <v>7152434</v>
+        <v>7152596</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120067935</v>
+        <v>120066631</v>
       </c>
       <c r="B4" t="n">
         <v>91840</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>746381</v>
+        <v>746551</v>
       </c>
       <c r="R4" t="n">
-        <v>7152596</v>
+        <v>7152434</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -3139,10 +3139,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120069608</v>
+        <v>120066896</v>
       </c>
       <c r="B24" t="n">
-        <v>91832</v>
+        <v>91863</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>746422</v>
+        <v>746537</v>
       </c>
       <c r="R24" t="n">
-        <v>7152546</v>
+        <v>7152456</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3251,10 +3251,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120066896</v>
+        <v>120069608</v>
       </c>
       <c r="B25" t="n">
-        <v>91863</v>
+        <v>91832</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3267,21 +3267,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>746537</v>
+        <v>746422</v>
       </c>
       <c r="R25" t="n">
-        <v>7152456</v>
+        <v>7152546</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3881,10 +3881,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120094951</v>
+        <v>120086265</v>
       </c>
       <c r="B31" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3893,41 +3893,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>746357</v>
+        <v>746353</v>
       </c>
       <c r="R31" t="n">
-        <v>7152686</v>
+        <v>7152592</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3968,7 +3965,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3987,7 +3983,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120080345</v>
+        <v>120094951</v>
       </c>
       <c r="B32" t="n">
         <v>91840</v>
@@ -4021,16 +4017,19 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>746459</v>
+        <v>746357</v>
       </c>
       <c r="R32" t="n">
-        <v>7152465</v>
+        <v>7152686</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4071,25 +4070,26 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120094907</v>
+        <v>120080345</v>
       </c>
       <c r="B33" t="n">
         <v>91840</v>
@@ -4123,19 +4123,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>746484</v>
+        <v>746459</v>
       </c>
       <c r="R33" t="n">
-        <v>7152510</v>
+        <v>7152465</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4176,29 +4173,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120086265</v>
+        <v>120094907</v>
       </c>
       <c r="B34" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4207,38 +4203,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>746353</v>
+        <v>746484</v>
       </c>
       <c r="R34" t="n">
-        <v>7152592</v>
+        <v>7152510</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4279,6 +4278,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -5020,10 +5020,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120086291</v>
+        <v>120080340</v>
       </c>
       <c r="B42" t="n">
-        <v>90807</v>
+        <v>91840</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5032,25 +5032,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5060,10 +5060,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>746502</v>
+        <v>746398</v>
       </c>
       <c r="R42" t="n">
-        <v>7152478</v>
+        <v>7152548</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5110,22 +5110,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120086263</v>
+        <v>120080336</v>
       </c>
       <c r="B43" t="n">
-        <v>92030</v>
+        <v>91840</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5134,25 +5134,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5162,10 +5162,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>746450</v>
+        <v>746545</v>
       </c>
       <c r="R43" t="n">
-        <v>7152549</v>
+        <v>7152464</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5212,22 +5212,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120080340</v>
+        <v>120086278</v>
       </c>
       <c r="B44" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5236,25 +5236,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5264,10 +5264,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>746398</v>
+        <v>746365</v>
       </c>
       <c r="R44" t="n">
-        <v>7152548</v>
+        <v>7152695</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5314,22 +5314,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120080336</v>
+        <v>120086291</v>
       </c>
       <c r="B45" t="n">
-        <v>91840</v>
+        <v>90807</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5338,25 +5338,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>746545</v>
+        <v>746502</v>
       </c>
       <c r="R45" t="n">
-        <v>7152464</v>
+        <v>7152478</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5416,22 +5416,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120086278</v>
+        <v>120086263</v>
       </c>
       <c r="B46" t="n">
-        <v>78526</v>
+        <v>92030</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5444,21 +5444,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5468,10 +5468,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>746365</v>
+        <v>746450</v>
       </c>
       <c r="R46" t="n">
-        <v>7152695</v>
+        <v>7152549</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -7946,10 +7946,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120094849</v>
+        <v>120079805</v>
       </c>
       <c r="B70" t="n">
-        <v>91840</v>
+        <v>92030</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7958,44 +7958,41 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>746531</v>
+        <v>746437</v>
       </c>
       <c r="R70" t="n">
-        <v>7152454</v>
+        <v>7152508</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8033,29 +8030,28 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120086280</v>
+        <v>120094849</v>
       </c>
       <c r="B71" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8064,38 +8060,41 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>746527</v>
+        <v>746531</v>
       </c>
       <c r="R71" t="n">
-        <v>7152434</v>
+        <v>7152454</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8136,6 +8135,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8154,10 +8154,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120094916</v>
+        <v>120086280</v>
       </c>
       <c r="B72" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8170,37 +8170,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>746490</v>
+        <v>746527</v>
       </c>
       <c r="R72" t="n">
-        <v>7152513</v>
+        <v>7152434</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8241,7 +8238,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8260,10 +8256,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120079805</v>
+        <v>120094916</v>
       </c>
       <c r="B73" t="n">
-        <v>92030</v>
+        <v>91884</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8276,37 +8272,40 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2079</v>
+        <v>5449</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>746437</v>
+        <v>746490</v>
       </c>
       <c r="R73" t="n">
-        <v>7152508</v>
+        <v>7152513</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8344,18 +8343,19 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>

--- a/artfynd/A 41672-2024 artfynd.xlsx
+++ b/artfynd/A 41672-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120068346</v>
+        <v>120069457</v>
       </c>
       <c r="B2" t="n">
-        <v>91852</v>
+        <v>91856</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>746324</v>
+        <v>746379</v>
       </c>
       <c r="R2" t="n">
-        <v>7152703</v>
+        <v>7152575</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120067935</v>
+        <v>120067137</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>746381</v>
+        <v>746520</v>
       </c>
       <c r="R3" t="n">
-        <v>7152596</v>
+        <v>7152487</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120066631</v>
+        <v>120068365</v>
       </c>
       <c r="B4" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>746551</v>
+        <v>746323</v>
       </c>
       <c r="R4" t="n">
-        <v>7152434</v>
+        <v>7152700</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120067137</v>
+        <v>120068300</v>
       </c>
       <c r="B5" t="n">
-        <v>91834</v>
+        <v>91863</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>746520</v>
+        <v>746336</v>
       </c>
       <c r="R5" t="n">
-        <v>7152487</v>
+        <v>7152676</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120068080</v>
+        <v>120069348</v>
       </c>
       <c r="B6" t="n">
         <v>91840</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>746371</v>
+        <v>746382</v>
       </c>
       <c r="R6" t="n">
-        <v>7152632</v>
+        <v>7152570</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120068133</v>
+        <v>120067935</v>
       </c>
       <c r="B7" t="n">
         <v>91840</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>746333</v>
+        <v>746381</v>
       </c>
       <c r="R7" t="n">
-        <v>7152647</v>
+        <v>7152596</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120067885</v>
+        <v>120067568</v>
       </c>
       <c r="B8" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>746399</v>
+        <v>746484</v>
       </c>
       <c r="R8" t="n">
-        <v>7152617</v>
+        <v>7152500</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120069457</v>
+        <v>120067262</v>
       </c>
       <c r="B9" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,25 +1471,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>746379</v>
+        <v>746520</v>
       </c>
       <c r="R9" t="n">
-        <v>7152575</v>
+        <v>7152494</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120067568</v>
+        <v>120069608</v>
       </c>
       <c r="B10" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,25 +1583,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>746484</v>
+        <v>746422</v>
       </c>
       <c r="R10" t="n">
-        <v>7152500</v>
+        <v>7152546</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,7 +1683,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120069348</v>
+        <v>120068080</v>
       </c>
       <c r="B11" t="n">
         <v>91840</v>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>746382</v>
+        <v>746371</v>
       </c>
       <c r="R11" t="n">
-        <v>7152570</v>
+        <v>7152632</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120068365</v>
+        <v>120068255</v>
       </c>
       <c r="B12" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,25 +1807,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>746323</v>
+        <v>746352</v>
       </c>
       <c r="R12" t="n">
-        <v>7152700</v>
+        <v>7152686</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120067504</v>
+        <v>120066631</v>
       </c>
       <c r="B13" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,25 +1919,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>746486</v>
+        <v>746551</v>
       </c>
       <c r="R13" t="n">
-        <v>7152501</v>
+        <v>7152434</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120068383</v>
+        <v>120068346</v>
       </c>
       <c r="B14" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>746313</v>
+        <v>746324</v>
       </c>
       <c r="R14" t="n">
-        <v>7152706</v>
+        <v>7152703</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,7 +2131,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120067430</v>
+        <v>120067504</v>
       </c>
       <c r="B15" t="n">
         <v>91856</v>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>746505</v>
+        <v>746486</v>
       </c>
       <c r="R15" t="n">
-        <v>7152499</v>
+        <v>7152501</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2355,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120067979</v>
+        <v>120066896</v>
       </c>
       <c r="B17" t="n">
-        <v>91840</v>
+        <v>91863</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2367,25 +2367,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>746392</v>
+        <v>746537</v>
       </c>
       <c r="R17" t="n">
-        <v>7152615</v>
+        <v>7152456</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,7 +2467,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120067841</v>
+        <v>120067979</v>
       </c>
       <c r="B18" t="n">
         <v>91840</v>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>746469</v>
+        <v>746392</v>
       </c>
       <c r="R18" t="n">
-        <v>7152569</v>
+        <v>7152615</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120068300</v>
+        <v>120068460</v>
       </c>
       <c r="B19" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2591,25 +2591,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>746336</v>
+        <v>746312</v>
       </c>
       <c r="R19" t="n">
-        <v>7152676</v>
+        <v>7152709</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,7 +2691,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120068460</v>
+        <v>120068331</v>
       </c>
       <c r="B20" t="n">
         <v>91840</v>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>746312</v>
+        <v>746318</v>
       </c>
       <c r="R20" t="n">
-        <v>7152709</v>
+        <v>7152701</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120067262</v>
+        <v>120067885</v>
       </c>
       <c r="B21" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2815,25 +2815,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>746520</v>
+        <v>746399</v>
       </c>
       <c r="R21" t="n">
-        <v>7152494</v>
+        <v>7152617</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,7 +2915,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120068255</v>
+        <v>120068383</v>
       </c>
       <c r="B22" t="n">
         <v>91840</v>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>746352</v>
+        <v>746313</v>
       </c>
       <c r="R22" t="n">
-        <v>7152686</v>
+        <v>7152706</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,7 +3027,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120068331</v>
+        <v>120067841</v>
       </c>
       <c r="B23" t="n">
         <v>91840</v>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>746318</v>
+        <v>746469</v>
       </c>
       <c r="R23" t="n">
-        <v>7152701</v>
+        <v>7152569</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,10 +3139,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120066896</v>
+        <v>120067430</v>
       </c>
       <c r="B24" t="n">
-        <v>91863</v>
+        <v>91856</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>746537</v>
+        <v>746505</v>
       </c>
       <c r="R24" t="n">
-        <v>7152456</v>
+        <v>7152499</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3251,10 +3251,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120069608</v>
+        <v>120068133</v>
       </c>
       <c r="B25" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3263,25 +3263,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>746422</v>
+        <v>746333</v>
       </c>
       <c r="R25" t="n">
-        <v>7152546</v>
+        <v>7152647</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3363,7 +3363,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120094869</v>
+        <v>120079812</v>
       </c>
       <c r="B26" t="n">
         <v>91840</v>
@@ -3397,22 +3397,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>746522</v>
+        <v>746540</v>
       </c>
       <c r="R26" t="n">
-        <v>7152453</v>
+        <v>7152434</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3457,22 +3454,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120086245</v>
+        <v>120094897</v>
       </c>
       <c r="B27" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3481,38 +3478,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>746365</v>
+        <v>746482</v>
       </c>
       <c r="R27" t="n">
-        <v>7152575</v>
+        <v>7152467</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3553,6 +3553,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3571,10 +3572,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120080326</v>
+        <v>120086279</v>
       </c>
       <c r="B28" t="n">
-        <v>89230</v>
+        <v>78526</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3583,25 +3584,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1596</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3611,10 +3612,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>746543</v>
+        <v>746397</v>
       </c>
       <c r="R28" t="n">
-        <v>7152437</v>
+        <v>7152654</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3661,22 +3662,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120079809</v>
+        <v>120079805</v>
       </c>
       <c r="B29" t="n">
-        <v>90712</v>
+        <v>92030</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3685,41 +3686,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>746368</v>
+        <v>746437</v>
       </c>
       <c r="R29" t="n">
-        <v>7152599</v>
+        <v>7152508</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3760,7 +3758,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3779,10 +3776,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120086298</v>
+        <v>120080295</v>
       </c>
       <c r="B30" t="n">
-        <v>91840</v>
+        <v>57463</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3791,38 +3788,46 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>746527</v>
+        <v>746385</v>
       </c>
       <c r="R30" t="n">
-        <v>7152434</v>
+        <v>7152570</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3869,22 +3874,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120086265</v>
+        <v>120086230</v>
       </c>
       <c r="B31" t="n">
-        <v>78263</v>
+        <v>90527</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3893,25 +3898,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3921,10 +3926,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>746353</v>
+        <v>746412</v>
       </c>
       <c r="R31" t="n">
-        <v>7152592</v>
+        <v>7152564</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3983,10 +3988,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120094951</v>
+        <v>120086272</v>
       </c>
       <c r="B32" t="n">
-        <v>91840</v>
+        <v>74624</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3999,27 +4004,24 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
@@ -4029,7 +4031,7 @@
         <v>746357</v>
       </c>
       <c r="R32" t="n">
-        <v>7152686</v>
+        <v>7152581</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4070,7 +4072,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4089,7 +4090,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120080345</v>
+        <v>120094959</v>
       </c>
       <c r="B33" t="n">
         <v>91840</v>
@@ -4123,16 +4124,19 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>746459</v>
+        <v>746300</v>
       </c>
       <c r="R33" t="n">
-        <v>7152465</v>
+        <v>7152654</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4173,25 +4177,26 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120094907</v>
+        <v>120080343</v>
       </c>
       <c r="B34" t="n">
         <v>91840</v>
@@ -4225,19 +4230,16 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>746484</v>
+        <v>746467</v>
       </c>
       <c r="R34" t="n">
-        <v>7152510</v>
+        <v>7152466</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4278,26 +4280,25 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120079812</v>
+        <v>120080345</v>
       </c>
       <c r="B35" t="n">
         <v>91840</v>
@@ -4337,13 +4338,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>746540</v>
+        <v>746459</v>
       </c>
       <c r="R35" t="n">
-        <v>7152434</v>
+        <v>7152465</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4381,29 +4382,28 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120086246</v>
+        <v>120080346</v>
       </c>
       <c r="B36" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4412,25 +4412,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4440,10 +4440,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>746475</v>
+        <v>746461</v>
       </c>
       <c r="R36" t="n">
-        <v>7152487</v>
+        <v>7152458</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4490,19 +4490,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120080341</v>
+        <v>120080338</v>
       </c>
       <c r="B37" t="n">
         <v>91840</v>
@@ -4542,10 +4542,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>746384</v>
+        <v>746455</v>
       </c>
       <c r="R37" t="n">
-        <v>7152544</v>
+        <v>7152561</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4604,10 +4604,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120080349</v>
+        <v>120086263</v>
       </c>
       <c r="B38" t="n">
-        <v>91840</v>
+        <v>92030</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4616,25 +4616,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>746540</v>
+        <v>746450</v>
       </c>
       <c r="R38" t="n">
-        <v>7152444</v>
+        <v>7152549</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4694,22 +4694,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120079797</v>
+        <v>120094951</v>
       </c>
       <c r="B39" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4718,41 +4718,44 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>746432</v>
+        <v>746357</v>
       </c>
       <c r="R39" t="n">
-        <v>7152509</v>
+        <v>7152686</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4790,25 +4793,26 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120094901</v>
+        <v>120086296</v>
       </c>
       <c r="B40" t="n">
         <v>91840</v>
@@ -4842,19 +4846,16 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>746487</v>
+        <v>746425</v>
       </c>
       <c r="R40" t="n">
-        <v>7152494</v>
+        <v>7152621</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4895,7 +4896,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4914,10 +4914,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120094922</v>
+        <v>120094901</v>
       </c>
       <c r="B41" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4926,25 +4926,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>746442</v>
+        <v>746487</v>
       </c>
       <c r="R41" t="n">
-        <v>7152565</v>
+        <v>7152494</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5020,7 +5020,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120080340</v>
+        <v>120094886</v>
       </c>
       <c r="B42" t="n">
         <v>91840</v>
@@ -5054,16 +5054,19 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>746398</v>
+        <v>746500</v>
       </c>
       <c r="R42" t="n">
-        <v>7152548</v>
+        <v>7152466</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5104,28 +5107,29 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120080336</v>
+        <v>120086277</v>
       </c>
       <c r="B43" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5134,25 +5138,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5162,10 +5166,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>746545</v>
+        <v>746302</v>
       </c>
       <c r="R43" t="n">
-        <v>7152464</v>
+        <v>7152670</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5212,19 +5216,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120086278</v>
+        <v>120086276</v>
       </c>
       <c r="B44" t="n">
         <v>78526</v>
@@ -5264,10 +5268,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>746365</v>
+        <v>746304</v>
       </c>
       <c r="R44" t="n">
-        <v>7152695</v>
+        <v>7152657</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5326,10 +5330,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120086291</v>
+        <v>120086266</v>
       </c>
       <c r="B45" t="n">
-        <v>90807</v>
+        <v>91863</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5338,25 +5342,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>65</v>
+        <v>5966</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5366,10 +5370,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>746502</v>
+        <v>746429</v>
       </c>
       <c r="R45" t="n">
-        <v>7152478</v>
+        <v>7152625</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5428,10 +5432,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120086263</v>
+        <v>120094869</v>
       </c>
       <c r="B46" t="n">
-        <v>92030</v>
+        <v>91840</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5440,38 +5444,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>746450</v>
+        <v>746522</v>
       </c>
       <c r="R46" t="n">
-        <v>7152549</v>
+        <v>7152453</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5512,6 +5519,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5530,10 +5538,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120094897</v>
+        <v>120086280</v>
       </c>
       <c r="B47" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5542,41 +5550,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>746482</v>
+        <v>746527</v>
       </c>
       <c r="R47" t="n">
-        <v>7152467</v>
+        <v>7152434</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5617,7 +5622,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5636,10 +5640,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120094945</v>
+        <v>120086238</v>
       </c>
       <c r="B48" t="n">
-        <v>91884</v>
+        <v>57463</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5652,26 +5656,31 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5679,10 +5688,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>746417</v>
+        <v>746509</v>
       </c>
       <c r="R48" t="n">
-        <v>7152628</v>
+        <v>7152434</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5717,13 +5726,17 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Två</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5742,10 +5755,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120094959</v>
+        <v>120079797</v>
       </c>
       <c r="B49" t="n">
-        <v>91840</v>
+        <v>89633</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5754,44 +5767,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>746300</v>
+        <v>746432</v>
       </c>
       <c r="R49" t="n">
-        <v>7152654</v>
+        <v>7152509</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5829,29 +5839,28 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120094932</v>
+        <v>120094922</v>
       </c>
       <c r="B50" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5860,25 +5869,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5891,10 +5900,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>746414</v>
+        <v>746442</v>
       </c>
       <c r="R50" t="n">
-        <v>7152584</v>
+        <v>7152565</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5954,10 +5963,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120080306</v>
+        <v>120080348</v>
       </c>
       <c r="B51" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5966,25 +5975,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5994,10 +6003,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>746490</v>
+        <v>746505</v>
       </c>
       <c r="R51" t="n">
-        <v>7152502</v>
+        <v>7152451</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6056,7 +6065,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120086297</v>
+        <v>120094932</v>
       </c>
       <c r="B52" t="n">
         <v>91840</v>
@@ -6090,16 +6099,19 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>746473</v>
+        <v>746414</v>
       </c>
       <c r="R52" t="n">
-        <v>7152499</v>
+        <v>7152584</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6140,6 +6152,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6158,10 +6171,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120086276</v>
+        <v>120094907</v>
       </c>
       <c r="B53" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6170,38 +6183,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>746304</v>
+        <v>746484</v>
       </c>
       <c r="R53" t="n">
-        <v>7152657</v>
+        <v>7152510</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6242,6 +6258,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6260,10 +6277,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120086266</v>
+        <v>120086295</v>
       </c>
       <c r="B54" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6272,25 +6289,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6300,10 +6317,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>746429</v>
+        <v>746365</v>
       </c>
       <c r="R54" t="n">
-        <v>7152625</v>
+        <v>7152695</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6362,10 +6379,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120086238</v>
+        <v>120079813</v>
       </c>
       <c r="B55" t="n">
-        <v>57463</v>
+        <v>91840</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6374,49 +6391,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>746509</v>
+        <v>746517</v>
       </c>
       <c r="R55" t="n">
-        <v>7152434</v>
+        <v>7152485</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6446,11 +6455,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Två</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6465,19 +6469,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120094886</v>
+        <v>120080336</v>
       </c>
       <c r="B56" t="n">
         <v>91840</v>
@@ -6511,19 +6515,16 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>746500</v>
+        <v>746545</v>
       </c>
       <c r="R56" t="n">
-        <v>7152466</v>
+        <v>7152464</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6564,29 +6565,28 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120086272</v>
+        <v>120086294</v>
       </c>
       <c r="B57" t="n">
-        <v>74624</v>
+        <v>91840</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6599,21 +6599,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>306</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6623,10 +6623,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>746357</v>
+        <v>746310</v>
       </c>
       <c r="R57" t="n">
-        <v>7152581</v>
+        <v>7152670</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6685,10 +6685,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120080319</v>
+        <v>120086246</v>
       </c>
       <c r="B58" t="n">
-        <v>92030</v>
+        <v>91884</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6701,21 +6701,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2079</v>
+        <v>5449</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6725,10 +6725,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>746477</v>
+        <v>746475</v>
       </c>
       <c r="R58" t="n">
-        <v>7152502</v>
+        <v>7152487</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6763,11 +6763,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På kolad tallstubbe</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6776,43 +6771,23 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL58" t="inlineStr">
-        <is>
-          <t>Kolad tallstubbe</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Kolad tallstubbe</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120080348</v>
+        <v>120094849</v>
       </c>
       <c r="B59" t="n">
         <v>91840</v>
@@ -6846,16 +6821,19 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>746505</v>
+        <v>746531</v>
       </c>
       <c r="R59" t="n">
-        <v>7152451</v>
+        <v>7152454</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6896,28 +6874,29 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120086277</v>
+        <v>120086298</v>
       </c>
       <c r="B60" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6926,25 +6905,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6954,10 +6933,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>746302</v>
+        <v>746527</v>
       </c>
       <c r="R60" t="n">
-        <v>7152670</v>
+        <v>7152434</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7016,10 +6995,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120080295</v>
+        <v>120080337</v>
       </c>
       <c r="B61" t="n">
-        <v>57463</v>
+        <v>91840</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7028,46 +7007,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>746385</v>
+        <v>746488</v>
       </c>
       <c r="R61" t="n">
-        <v>7152570</v>
+        <v>7152500</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7126,10 +7097,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120086295</v>
+        <v>120094945</v>
       </c>
       <c r="B62" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7138,38 +7109,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>746365</v>
+        <v>746417</v>
       </c>
       <c r="R62" t="n">
-        <v>7152695</v>
+        <v>7152628</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7210,6 +7184,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7228,10 +7203,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120094939</v>
+        <v>120086245</v>
       </c>
       <c r="B63" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7240,41 +7215,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>746413</v>
+        <v>746365</v>
       </c>
       <c r="R63" t="n">
-        <v>7152616</v>
+        <v>7152575</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7315,7 +7287,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7334,10 +7305,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120080343</v>
+        <v>120079809</v>
       </c>
       <c r="B64" t="n">
-        <v>91840</v>
+        <v>90712</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7346,41 +7317,44 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>746467</v>
+        <v>746368</v>
       </c>
       <c r="R64" t="n">
-        <v>7152466</v>
+        <v>7152599</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7418,28 +7392,29 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120086279</v>
+        <v>120094916</v>
       </c>
       <c r="B65" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7452,34 +7427,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>746397</v>
+        <v>746490</v>
       </c>
       <c r="R65" t="n">
-        <v>7152654</v>
+        <v>7152513</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7520,6 +7498,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7538,10 +7517,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120086230</v>
+        <v>120086297</v>
       </c>
       <c r="B66" t="n">
-        <v>90527</v>
+        <v>91840</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7554,21 +7533,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7578,10 +7557,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>746412</v>
+        <v>746473</v>
       </c>
       <c r="R66" t="n">
-        <v>7152564</v>
+        <v>7152499</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7640,10 +7619,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120079813</v>
+        <v>120086228</v>
       </c>
       <c r="B67" t="n">
-        <v>91840</v>
+        <v>74638</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7652,25 +7631,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>6440</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7680,13 +7659,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>746517</v>
+        <v>746357</v>
       </c>
       <c r="R67" t="n">
-        <v>7152485</v>
+        <v>7152581</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7730,22 +7709,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120086294</v>
+        <v>120086265</v>
       </c>
       <c r="B68" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7754,25 +7733,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7782,10 +7761,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>746310</v>
+        <v>746353</v>
       </c>
       <c r="R68" t="n">
-        <v>7152670</v>
+        <v>7152592</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7844,10 +7823,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120086259</v>
+        <v>120080319</v>
       </c>
       <c r="B69" t="n">
-        <v>91832</v>
+        <v>92030</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7860,21 +7839,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4361</v>
+        <v>2079</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7884,10 +7863,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>746394</v>
+        <v>746477</v>
       </c>
       <c r="R69" t="n">
-        <v>7152581</v>
+        <v>7152502</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7922,6 +7901,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På kolad tallstubbe</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -7930,26 +7914,46 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL69" t="inlineStr">
+        <is>
+          <t>Kolad tallstubbe</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Kolad tallstubbe</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120079805</v>
+        <v>120080326</v>
       </c>
       <c r="B70" t="n">
-        <v>92030</v>
+        <v>89230</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7958,25 +7962,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2079</v>
+        <v>1596</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7986,13 +7990,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>746437</v>
+        <v>746543</v>
       </c>
       <c r="R70" t="n">
-        <v>7152508</v>
+        <v>7152437</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8036,19 +8040,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120094849</v>
+        <v>120080340</v>
       </c>
       <c r="B71" t="n">
         <v>91840</v>
@@ -8082,19 +8086,16 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>746531</v>
+        <v>746398</v>
       </c>
       <c r="R71" t="n">
-        <v>7152454</v>
+        <v>7152548</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8135,29 +8136,28 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120086280</v>
+        <v>120080341</v>
       </c>
       <c r="B72" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8166,25 +8166,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8194,10 +8194,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>746527</v>
+        <v>746384</v>
       </c>
       <c r="R72" t="n">
-        <v>7152434</v>
+        <v>7152544</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8244,22 +8244,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120094916</v>
+        <v>120086275</v>
       </c>
       <c r="B73" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8272,37 +8272,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>746490</v>
+        <v>746370</v>
       </c>
       <c r="R73" t="n">
-        <v>7152513</v>
+        <v>7152601</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8343,7 +8340,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8362,10 +8358,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120086228</v>
+        <v>120080342</v>
       </c>
       <c r="B74" t="n">
-        <v>74638</v>
+        <v>91840</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8374,25 +8370,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8402,10 +8398,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>746357</v>
+        <v>746478</v>
       </c>
       <c r="R74" t="n">
-        <v>7152581</v>
+        <v>7152487</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8452,22 +8448,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120086275</v>
+        <v>120094939</v>
       </c>
       <c r="B75" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8476,38 +8472,41 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>746370</v>
+        <v>746413</v>
       </c>
       <c r="R75" t="n">
-        <v>7152601</v>
+        <v>7152616</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8548,6 +8547,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8566,10 +8566,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120080307</v>
+        <v>120086259</v>
       </c>
       <c r="B76" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8582,21 +8582,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8606,10 +8606,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>746426</v>
+        <v>746394</v>
       </c>
       <c r="R76" t="n">
-        <v>7152510</v>
+        <v>7152581</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8656,22 +8656,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120086296</v>
+        <v>120080306</v>
       </c>
       <c r="B77" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8680,25 +8680,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8708,10 +8708,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>746425</v>
+        <v>746490</v>
       </c>
       <c r="R77" t="n">
-        <v>7152621</v>
+        <v>7152502</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8758,22 +8758,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120080338</v>
+        <v>120080307</v>
       </c>
       <c r="B78" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8782,25 +8782,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8810,10 +8810,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>746455</v>
+        <v>746426</v>
       </c>
       <c r="R78" t="n">
-        <v>7152561</v>
+        <v>7152510</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8872,10 +8872,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120094855</v>
+        <v>120086269</v>
       </c>
       <c r="B79" t="n">
-        <v>91840</v>
+        <v>88153</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8884,25 +8884,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8915,10 +8915,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>746547</v>
+        <v>746365</v>
       </c>
       <c r="R79" t="n">
-        <v>7152471</v>
+        <v>7152575</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8951,6 +8951,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Inte ihålig men övriga karaktärer stämde.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8978,10 +8983,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120086274</v>
+        <v>120080349</v>
       </c>
       <c r="B80" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8990,25 +8995,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9018,10 +9023,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>746478</v>
+        <v>746540</v>
       </c>
       <c r="R80" t="n">
-        <v>7152496</v>
+        <v>7152444</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9068,22 +9073,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120080346</v>
+        <v>120086291</v>
       </c>
       <c r="B81" t="n">
-        <v>91840</v>
+        <v>90807</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9092,25 +9097,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9120,10 +9125,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>746461</v>
+        <v>746502</v>
       </c>
       <c r="R81" t="n">
-        <v>7152458</v>
+        <v>7152478</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9170,22 +9175,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120080337</v>
+        <v>120086278</v>
       </c>
       <c r="B82" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9194,25 +9199,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9222,10 +9227,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>746488</v>
+        <v>746365</v>
       </c>
       <c r="R82" t="n">
-        <v>7152500</v>
+        <v>7152695</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9272,22 +9277,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120080342</v>
+        <v>120086274</v>
       </c>
       <c r="B83" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9296,25 +9301,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9327,7 +9332,7 @@
         <v>746478</v>
       </c>
       <c r="R83" t="n">
-        <v>7152487</v>
+        <v>7152496</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9374,22 +9379,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120079802</v>
+        <v>120094855</v>
       </c>
       <c r="B84" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9398,41 +9403,44 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>746495</v>
+        <v>746547</v>
       </c>
       <c r="R84" t="n">
-        <v>7152470</v>
+        <v>7152471</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9470,28 +9478,29 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120086269</v>
+        <v>120079802</v>
       </c>
       <c r="B85" t="n">
-        <v>88153</v>
+        <v>91884</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9504,40 +9513,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4962</v>
+        <v>5449</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>746365</v>
+        <v>746495</v>
       </c>
       <c r="R85" t="n">
-        <v>7152575</v>
+        <v>7152470</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9569,30 +9575,24 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Inte ihålig men övriga karaktärer stämde.</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>

--- a/artfynd/A 41672-2024 artfynd.xlsx
+++ b/artfynd/A 41672-2024 artfynd.xlsx
@@ -7721,10 +7721,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120086265</v>
+        <v>120080319</v>
       </c>
       <c r="B68" t="n">
-        <v>78263</v>
+        <v>92030</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7737,21 +7737,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7761,10 +7761,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>746353</v>
+        <v>746477</v>
       </c>
       <c r="R68" t="n">
-        <v>7152592</v>
+        <v>7152502</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7799,6 +7799,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På kolad tallstubbe</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7807,26 +7812,46 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL68" t="inlineStr">
+        <is>
+          <t>Kolad tallstubbe</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Kolad tallstubbe</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120080319</v>
+        <v>120080326</v>
       </c>
       <c r="B69" t="n">
-        <v>92030</v>
+        <v>89230</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7835,25 +7860,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2079</v>
+        <v>1596</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7863,10 +7888,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>746477</v>
+        <v>746543</v>
       </c>
       <c r="R69" t="n">
-        <v>7152502</v>
+        <v>7152437</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7901,11 +7926,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På kolad tallstubbe</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -7914,26 +7934,6 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL69" t="inlineStr">
-        <is>
-          <t>Kolad tallstubbe</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Kolad tallstubbe</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -7950,10 +7950,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120080326</v>
+        <v>120086265</v>
       </c>
       <c r="B70" t="n">
-        <v>89230</v>
+        <v>78263</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7962,25 +7962,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1596</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7990,10 +7990,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>746543</v>
+        <v>746353</v>
       </c>
       <c r="R70" t="n">
-        <v>7152437</v>
+        <v>7152592</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8040,22 +8040,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120080340</v>
+        <v>120086275</v>
       </c>
       <c r="B71" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8064,25 +8064,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8092,10 +8092,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>746398</v>
+        <v>746370</v>
       </c>
       <c r="R71" t="n">
-        <v>7152548</v>
+        <v>7152601</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8142,19 +8142,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120080341</v>
+        <v>120080340</v>
       </c>
       <c r="B72" t="n">
         <v>91840</v>
@@ -8194,10 +8194,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>746384</v>
+        <v>746398</v>
       </c>
       <c r="R72" t="n">
-        <v>7152544</v>
+        <v>7152548</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8256,10 +8256,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120086275</v>
+        <v>120080341</v>
       </c>
       <c r="B73" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8268,25 +8268,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8296,10 +8296,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>746370</v>
+        <v>746384</v>
       </c>
       <c r="R73" t="n">
-        <v>7152601</v>
+        <v>7152544</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8346,12 +8346,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8983,10 +8983,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120080349</v>
+        <v>120086291</v>
       </c>
       <c r="B80" t="n">
-        <v>91840</v>
+        <v>90807</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8995,25 +8995,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9023,10 +9023,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>746540</v>
+        <v>746502</v>
       </c>
       <c r="R80" t="n">
-        <v>7152444</v>
+        <v>7152478</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9073,22 +9073,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120086291</v>
+        <v>120080349</v>
       </c>
       <c r="B81" t="n">
-        <v>90807</v>
+        <v>91840</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9097,25 +9097,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9125,10 +9125,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>746502</v>
+        <v>746540</v>
       </c>
       <c r="R81" t="n">
-        <v>7152478</v>
+        <v>7152444</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9175,12 +9175,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9391,10 +9391,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120094855</v>
+        <v>120079802</v>
       </c>
       <c r="B84" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9403,44 +9403,41 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>746547</v>
+        <v>746495</v>
       </c>
       <c r="R84" t="n">
-        <v>7152471</v>
+        <v>7152470</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9478,29 +9475,28 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120079802</v>
+        <v>120094855</v>
       </c>
       <c r="B85" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9509,41 +9505,44 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>746495</v>
+        <v>746547</v>
       </c>
       <c r="R85" t="n">
-        <v>7152470</v>
+        <v>7152471</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9581,18 +9580,19 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>

--- a/artfynd/A 41672-2024 artfynd.xlsx
+++ b/artfynd/A 41672-2024 artfynd.xlsx
@@ -3674,10 +3674,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120079805</v>
+        <v>120080295</v>
       </c>
       <c r="B29" t="n">
-        <v>92030</v>
+        <v>57463</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3690,37 +3690,45 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2079</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>746437</v>
+        <v>746385</v>
       </c>
       <c r="R29" t="n">
-        <v>7152508</v>
+        <v>7152570</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3764,22 +3772,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120080295</v>
+        <v>120086272</v>
       </c>
       <c r="B30" t="n">
-        <v>57463</v>
+        <v>74624</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3788,46 +3796,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>746385</v>
+        <v>746357</v>
       </c>
       <c r="R30" t="n">
-        <v>7152570</v>
+        <v>7152581</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3874,22 +3874,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120086230</v>
+        <v>120079805</v>
       </c>
       <c r="B31" t="n">
-        <v>90527</v>
+        <v>92030</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3898,25 +3898,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3926,13 +3926,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>746412</v>
+        <v>746437</v>
       </c>
       <c r="R31" t="n">
-        <v>7152564</v>
+        <v>7152508</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3976,22 +3976,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120086272</v>
+        <v>120086230</v>
       </c>
       <c r="B32" t="n">
-        <v>74624</v>
+        <v>90527</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4004,21 +4004,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>306</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4028,10 +4028,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>746357</v>
+        <v>746412</v>
       </c>
       <c r="R32" t="n">
-        <v>7152581</v>
+        <v>7152564</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -6787,10 +6787,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120094849</v>
+        <v>120094945</v>
       </c>
       <c r="B59" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6799,25 +6799,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6830,10 +6830,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>746531</v>
+        <v>746417</v>
       </c>
       <c r="R59" t="n">
-        <v>7152454</v>
+        <v>7152628</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6893,7 +6893,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120086298</v>
+        <v>120094849</v>
       </c>
       <c r="B60" t="n">
         <v>91840</v>
@@ -6927,16 +6927,19 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>746527</v>
+        <v>746531</v>
       </c>
       <c r="R60" t="n">
-        <v>7152434</v>
+        <v>7152454</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6977,6 +6980,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6995,7 +6999,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120080337</v>
+        <v>120086298</v>
       </c>
       <c r="B61" t="n">
         <v>91840</v>
@@ -7035,10 +7039,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>746488</v>
+        <v>746527</v>
       </c>
       <c r="R61" t="n">
-        <v>7152500</v>
+        <v>7152434</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7085,22 +7089,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120094945</v>
+        <v>120080337</v>
       </c>
       <c r="B62" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7109,41 +7113,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>746417</v>
+        <v>746488</v>
       </c>
       <c r="R62" t="n">
-        <v>7152628</v>
+        <v>7152500</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7184,19 +7185,18 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7721,10 +7721,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120080319</v>
+        <v>120086265</v>
       </c>
       <c r="B68" t="n">
-        <v>92030</v>
+        <v>78263</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7737,21 +7737,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7761,10 +7761,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>746477</v>
+        <v>746353</v>
       </c>
       <c r="R68" t="n">
-        <v>7152502</v>
+        <v>7152592</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7799,11 +7799,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På kolad tallstubbe</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7812,46 +7807,26 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL68" t="inlineStr">
-        <is>
-          <t>Kolad tallstubbe</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Kolad tallstubbe</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120080326</v>
+        <v>120080319</v>
       </c>
       <c r="B69" t="n">
-        <v>89230</v>
+        <v>92030</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7860,25 +7835,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1596</v>
+        <v>2079</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7888,10 +7863,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>746543</v>
+        <v>746477</v>
       </c>
       <c r="R69" t="n">
-        <v>7152437</v>
+        <v>7152502</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7926,6 +7901,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På kolad tallstubbe</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -7934,6 +7914,26 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL69" t="inlineStr">
+        <is>
+          <t>Kolad tallstubbe</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Kolad tallstubbe</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -7950,10 +7950,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120086265</v>
+        <v>120080326</v>
       </c>
       <c r="B70" t="n">
-        <v>78263</v>
+        <v>89230</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7962,25 +7962,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>1596</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7990,10 +7990,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>746353</v>
+        <v>746543</v>
       </c>
       <c r="R70" t="n">
-        <v>7152592</v>
+        <v>7152437</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8040,12 +8040,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8983,10 +8983,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120086291</v>
+        <v>120080349</v>
       </c>
       <c r="B80" t="n">
-        <v>90807</v>
+        <v>91840</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8995,25 +8995,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9023,10 +9023,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>746502</v>
+        <v>746540</v>
       </c>
       <c r="R80" t="n">
-        <v>7152478</v>
+        <v>7152444</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9073,22 +9073,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120080349</v>
+        <v>120086291</v>
       </c>
       <c r="B81" t="n">
-        <v>91840</v>
+        <v>90807</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9097,25 +9097,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9125,10 +9125,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>746540</v>
+        <v>746502</v>
       </c>
       <c r="R81" t="n">
-        <v>7152444</v>
+        <v>7152478</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9175,12 +9175,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9391,10 +9391,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120079802</v>
+        <v>120094855</v>
       </c>
       <c r="B84" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9403,41 +9403,44 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>746495</v>
+        <v>746547</v>
       </c>
       <c r="R84" t="n">
-        <v>7152470</v>
+        <v>7152471</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9475,28 +9478,29 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120094855</v>
+        <v>120079802</v>
       </c>
       <c r="B85" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9505,44 +9509,41 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>746547</v>
+        <v>746495</v>
       </c>
       <c r="R85" t="n">
-        <v>7152471</v>
+        <v>7152470</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9580,19 +9581,18 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>

--- a/artfynd/A 41672-2024 artfynd.xlsx
+++ b/artfynd/A 41672-2024 artfynd.xlsx
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120066631</v>
+        <v>120067504</v>
       </c>
       <c r="B13" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,25 +1919,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>746551</v>
+        <v>746486</v>
       </c>
       <c r="R13" t="n">
-        <v>7152434</v>
+        <v>7152501</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120068346</v>
+        <v>120066631</v>
       </c>
       <c r="B14" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>746324</v>
+        <v>746551</v>
       </c>
       <c r="R14" t="n">
-        <v>7152703</v>
+        <v>7152434</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120067504</v>
+        <v>120068346</v>
       </c>
       <c r="B15" t="n">
-        <v>91856</v>
+        <v>91852</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2143,25 +2143,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>746486</v>
+        <v>746324</v>
       </c>
       <c r="R15" t="n">
-        <v>7152501</v>
+        <v>7152703</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -4604,10 +4604,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120086263</v>
+        <v>120094951</v>
       </c>
       <c r="B38" t="n">
-        <v>92030</v>
+        <v>91840</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4616,38 +4616,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>746450</v>
+        <v>746357</v>
       </c>
       <c r="R38" t="n">
-        <v>7152549</v>
+        <v>7152686</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4688,6 +4691,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4706,7 +4710,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120094951</v>
+        <v>120086296</v>
       </c>
       <c r="B39" t="n">
         <v>91840</v>
@@ -4740,19 +4744,16 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>746357</v>
+        <v>746425</v>
       </c>
       <c r="R39" t="n">
-        <v>7152686</v>
+        <v>7152621</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4793,7 +4794,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4812,10 +4812,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120086296</v>
+        <v>120086263</v>
       </c>
       <c r="B40" t="n">
-        <v>91840</v>
+        <v>92030</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4824,25 +4824,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4852,10 +4852,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>746425</v>
+        <v>746450</v>
       </c>
       <c r="R40" t="n">
-        <v>7152621</v>
+        <v>7152549</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -6787,10 +6787,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120094945</v>
+        <v>120094849</v>
       </c>
       <c r="B59" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6799,25 +6799,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6830,10 +6830,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>746417</v>
+        <v>746531</v>
       </c>
       <c r="R59" t="n">
-        <v>7152628</v>
+        <v>7152454</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6893,7 +6893,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120094849</v>
+        <v>120086298</v>
       </c>
       <c r="B60" t="n">
         <v>91840</v>
@@ -6927,19 +6927,16 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>746531</v>
+        <v>746527</v>
       </c>
       <c r="R60" t="n">
-        <v>7152454</v>
+        <v>7152434</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6980,7 +6977,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6999,7 +6995,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120086298</v>
+        <v>120080337</v>
       </c>
       <c r="B61" t="n">
         <v>91840</v>
@@ -7039,10 +7035,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>746527</v>
+        <v>746488</v>
       </c>
       <c r="R61" t="n">
-        <v>7152434</v>
+        <v>7152500</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7089,22 +7085,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120080337</v>
+        <v>120094945</v>
       </c>
       <c r="B62" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7113,38 +7109,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>746488</v>
+        <v>746417</v>
       </c>
       <c r="R62" t="n">
-        <v>7152500</v>
+        <v>7152628</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7185,18 +7184,19 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7305,10 +7305,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120079809</v>
+        <v>120094916</v>
       </c>
       <c r="B64" t="n">
-        <v>90712</v>
+        <v>91884</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7317,25 +7317,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1503</v>
+        <v>5449</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7348,13 +7348,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>746368</v>
+        <v>746490</v>
       </c>
       <c r="R64" t="n">
-        <v>7152599</v>
+        <v>7152513</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7399,22 +7399,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120094916</v>
+        <v>120086228</v>
       </c>
       <c r="B65" t="n">
-        <v>91884</v>
+        <v>74638</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7427,37 +7427,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5449</v>
+        <v>6440</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>746490</v>
+        <v>746357</v>
       </c>
       <c r="R65" t="n">
-        <v>7152513</v>
+        <v>7152581</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7498,7 +7495,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7517,10 +7513,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120086297</v>
+        <v>120079809</v>
       </c>
       <c r="B66" t="n">
-        <v>91840</v>
+        <v>90712</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7529,41 +7525,44 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>746473</v>
+        <v>746368</v>
       </c>
       <c r="R66" t="n">
-        <v>7152499</v>
+        <v>7152599</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7601,28 +7600,29 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120086228</v>
+        <v>120086297</v>
       </c>
       <c r="B67" t="n">
-        <v>74638</v>
+        <v>91840</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7631,25 +7631,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7659,10 +7659,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>746357</v>
+        <v>746473</v>
       </c>
       <c r="R67" t="n">
-        <v>7152581</v>
+        <v>7152499</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7721,10 +7721,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120086265</v>
+        <v>120080319</v>
       </c>
       <c r="B68" t="n">
-        <v>78263</v>
+        <v>92030</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7737,21 +7737,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7761,10 +7761,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>746353</v>
+        <v>746477</v>
       </c>
       <c r="R68" t="n">
-        <v>7152592</v>
+        <v>7152502</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7799,6 +7799,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På kolad tallstubbe</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7807,26 +7812,46 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL68" t="inlineStr">
+        <is>
+          <t>Kolad tallstubbe</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Kolad tallstubbe</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120080319</v>
+        <v>120080326</v>
       </c>
       <c r="B69" t="n">
-        <v>92030</v>
+        <v>89230</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7835,25 +7860,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2079</v>
+        <v>1596</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7863,10 +7888,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>746477</v>
+        <v>746543</v>
       </c>
       <c r="R69" t="n">
-        <v>7152502</v>
+        <v>7152437</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7901,11 +7926,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På kolad tallstubbe</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -7914,26 +7934,6 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL69" t="inlineStr">
-        <is>
-          <t>Kolad tallstubbe</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Kolad tallstubbe</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -7950,10 +7950,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120080326</v>
+        <v>120086265</v>
       </c>
       <c r="B70" t="n">
-        <v>89230</v>
+        <v>78263</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7962,25 +7962,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1596</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7990,10 +7990,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>746543</v>
+        <v>746353</v>
       </c>
       <c r="R70" t="n">
-        <v>7152437</v>
+        <v>7152592</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8040,12 +8040,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8983,10 +8983,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120080349</v>
+        <v>120086291</v>
       </c>
       <c r="B80" t="n">
-        <v>91840</v>
+        <v>90807</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8995,25 +8995,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9023,10 +9023,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>746540</v>
+        <v>746502</v>
       </c>
       <c r="R80" t="n">
-        <v>7152444</v>
+        <v>7152478</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9073,22 +9073,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120086291</v>
+        <v>120080349</v>
       </c>
       <c r="B81" t="n">
-        <v>90807</v>
+        <v>91840</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9097,25 +9097,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9125,10 +9125,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>746502</v>
+        <v>746540</v>
       </c>
       <c r="R81" t="n">
-        <v>7152478</v>
+        <v>7152444</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9175,12 +9175,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>

--- a/artfynd/A 41672-2024 artfynd.xlsx
+++ b/artfynd/A 41672-2024 artfynd.xlsx
@@ -3674,10 +3674,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120080295</v>
+        <v>120079805</v>
       </c>
       <c r="B29" t="n">
-        <v>57463</v>
+        <v>92030</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3690,45 +3690,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>2079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>746385</v>
+        <v>746437</v>
       </c>
       <c r="R29" t="n">
-        <v>7152570</v>
+        <v>7152508</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3772,22 +3764,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120086272</v>
+        <v>120080295</v>
       </c>
       <c r="B30" t="n">
-        <v>74624</v>
+        <v>57463</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3796,38 +3788,46 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>306</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>746357</v>
+        <v>746385</v>
       </c>
       <c r="R30" t="n">
-        <v>7152581</v>
+        <v>7152570</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3874,22 +3874,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120079805</v>
+        <v>120086230</v>
       </c>
       <c r="B31" t="n">
-        <v>92030</v>
+        <v>90527</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3898,25 +3898,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3926,13 +3926,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>746437</v>
+        <v>746412</v>
       </c>
       <c r="R31" t="n">
-        <v>7152508</v>
+        <v>7152564</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3976,22 +3976,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120086230</v>
+        <v>120086272</v>
       </c>
       <c r="B32" t="n">
-        <v>90527</v>
+        <v>74624</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4004,21 +4004,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4028,10 +4028,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>746412</v>
+        <v>746357</v>
       </c>
       <c r="R32" t="n">
-        <v>7152564</v>
+        <v>7152581</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -5432,10 +5432,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120094869</v>
+        <v>120086280</v>
       </c>
       <c r="B46" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5444,41 +5444,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>746522</v>
+        <v>746527</v>
       </c>
       <c r="R46" t="n">
-        <v>7152453</v>
+        <v>7152434</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5519,7 +5516,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5538,10 +5534,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120086280</v>
+        <v>120094869</v>
       </c>
       <c r="B47" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5550,38 +5546,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>746527</v>
+        <v>746522</v>
       </c>
       <c r="R47" t="n">
-        <v>7152434</v>
+        <v>7152453</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5622,6 +5621,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6787,10 +6787,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120094849</v>
+        <v>120094945</v>
       </c>
       <c r="B59" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6799,25 +6799,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6830,10 +6830,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>746531</v>
+        <v>746417</v>
       </c>
       <c r="R59" t="n">
-        <v>7152454</v>
+        <v>7152628</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6893,7 +6893,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120086298</v>
+        <v>120094849</v>
       </c>
       <c r="B60" t="n">
         <v>91840</v>
@@ -6927,16 +6927,19 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>746527</v>
+        <v>746531</v>
       </c>
       <c r="R60" t="n">
-        <v>7152434</v>
+        <v>7152454</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6977,6 +6980,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6995,7 +6999,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120080337</v>
+        <v>120086298</v>
       </c>
       <c r="B61" t="n">
         <v>91840</v>
@@ -7035,10 +7039,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>746488</v>
+        <v>746527</v>
       </c>
       <c r="R61" t="n">
-        <v>7152500</v>
+        <v>7152434</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7085,22 +7089,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120094945</v>
+        <v>120080337</v>
       </c>
       <c r="B62" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7109,41 +7113,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>746417</v>
+        <v>746488</v>
       </c>
       <c r="R62" t="n">
-        <v>7152628</v>
+        <v>7152500</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7184,19 +7185,18 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7721,10 +7721,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120080319</v>
+        <v>120086265</v>
       </c>
       <c r="B68" t="n">
-        <v>92030</v>
+        <v>78263</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7737,21 +7737,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7761,10 +7761,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>746477</v>
+        <v>746353</v>
       </c>
       <c r="R68" t="n">
-        <v>7152502</v>
+        <v>7152592</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7799,11 +7799,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På kolad tallstubbe</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7812,46 +7807,26 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL68" t="inlineStr">
-        <is>
-          <t>Kolad tallstubbe</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Kolad tallstubbe</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120080326</v>
+        <v>120080319</v>
       </c>
       <c r="B69" t="n">
-        <v>89230</v>
+        <v>92030</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7860,25 +7835,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1596</v>
+        <v>2079</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7888,10 +7863,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>746543</v>
+        <v>746477</v>
       </c>
       <c r="R69" t="n">
-        <v>7152437</v>
+        <v>7152502</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7926,6 +7901,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På kolad tallstubbe</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -7934,6 +7914,26 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL69" t="inlineStr">
+        <is>
+          <t>Kolad tallstubbe</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Kolad tallstubbe</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -7950,10 +7950,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120086265</v>
+        <v>120080326</v>
       </c>
       <c r="B70" t="n">
-        <v>78263</v>
+        <v>89230</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7962,25 +7962,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>1596</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7990,10 +7990,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>746353</v>
+        <v>746543</v>
       </c>
       <c r="R70" t="n">
-        <v>7152592</v>
+        <v>7152437</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8040,22 +8040,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120086275</v>
+        <v>120080340</v>
       </c>
       <c r="B71" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8064,25 +8064,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8092,10 +8092,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>746370</v>
+        <v>746398</v>
       </c>
       <c r="R71" t="n">
-        <v>7152601</v>
+        <v>7152548</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8142,19 +8142,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120080340</v>
+        <v>120080341</v>
       </c>
       <c r="B72" t="n">
         <v>91840</v>
@@ -8194,10 +8194,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>746398</v>
+        <v>746384</v>
       </c>
       <c r="R72" t="n">
-        <v>7152548</v>
+        <v>7152544</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8256,10 +8256,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120080341</v>
+        <v>120086275</v>
       </c>
       <c r="B73" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8268,25 +8268,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8296,10 +8296,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>746384</v>
+        <v>746370</v>
       </c>
       <c r="R73" t="n">
-        <v>7152544</v>
+        <v>7152601</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8346,12 +8346,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -9391,10 +9391,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120094855</v>
+        <v>120079802</v>
       </c>
       <c r="B84" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9403,44 +9403,41 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>746547</v>
+        <v>746495</v>
       </c>
       <c r="R84" t="n">
-        <v>7152471</v>
+        <v>7152470</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9478,29 +9475,28 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120079802</v>
+        <v>120094855</v>
       </c>
       <c r="B85" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9509,41 +9505,44 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>746495</v>
+        <v>746547</v>
       </c>
       <c r="R85" t="n">
-        <v>7152470</v>
+        <v>7152471</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9581,18 +9580,19 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>

--- a/artfynd/A 41672-2024 artfynd.xlsx
+++ b/artfynd/A 41672-2024 artfynd.xlsx
@@ -3674,10 +3674,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120079805</v>
+        <v>120080295</v>
       </c>
       <c r="B29" t="n">
-        <v>92030</v>
+        <v>57463</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3690,37 +3690,45 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2079</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>746437</v>
+        <v>746385</v>
       </c>
       <c r="R29" t="n">
-        <v>7152508</v>
+        <v>7152570</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3764,22 +3772,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120080295</v>
+        <v>120086272</v>
       </c>
       <c r="B30" t="n">
-        <v>57463</v>
+        <v>74624</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3788,46 +3796,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>746385</v>
+        <v>746357</v>
       </c>
       <c r="R30" t="n">
-        <v>7152570</v>
+        <v>7152581</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3874,22 +3874,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120086230</v>
+        <v>120079805</v>
       </c>
       <c r="B31" t="n">
-        <v>90527</v>
+        <v>92030</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3898,25 +3898,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3926,13 +3926,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>746412</v>
+        <v>746437</v>
       </c>
       <c r="R31" t="n">
-        <v>7152564</v>
+        <v>7152508</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3976,22 +3976,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120086272</v>
+        <v>120086230</v>
       </c>
       <c r="B32" t="n">
-        <v>74624</v>
+        <v>90527</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4004,21 +4004,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>306</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4028,10 +4028,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>746357</v>
+        <v>746412</v>
       </c>
       <c r="R32" t="n">
-        <v>7152581</v>
+        <v>7152564</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -5432,10 +5432,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120086280</v>
+        <v>120094869</v>
       </c>
       <c r="B46" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5444,38 +5444,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>746527</v>
+        <v>746522</v>
       </c>
       <c r="R46" t="n">
-        <v>7152434</v>
+        <v>7152453</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5516,6 +5519,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5534,10 +5538,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120094869</v>
+        <v>120086280</v>
       </c>
       <c r="B47" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5546,41 +5550,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>746522</v>
+        <v>746527</v>
       </c>
       <c r="R47" t="n">
-        <v>7152453</v>
+        <v>7152434</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5621,7 +5622,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5640,10 +5640,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120086238</v>
+        <v>120079797</v>
       </c>
       <c r="B48" t="n">
-        <v>57463</v>
+        <v>89633</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5656,45 +5656,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>1962</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>746509</v>
+        <v>746432</v>
       </c>
       <c r="R48" t="n">
-        <v>7152434</v>
+        <v>7152509</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5724,11 +5716,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Två</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5743,22 +5730,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120079797</v>
+        <v>120094922</v>
       </c>
       <c r="B49" t="n">
-        <v>89633</v>
+        <v>91884</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5771,37 +5758,40 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1962</v>
+        <v>5449</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>746432</v>
+        <v>746442</v>
       </c>
       <c r="R49" t="n">
-        <v>7152509</v>
+        <v>7152565</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5839,28 +5829,29 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120094922</v>
+        <v>120086238</v>
       </c>
       <c r="B50" t="n">
-        <v>91884</v>
+        <v>57463</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5873,26 +5864,31 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5900,10 +5896,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>746442</v>
+        <v>746509</v>
       </c>
       <c r="R50" t="n">
-        <v>7152565</v>
+        <v>7152434</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5938,13 +5934,17 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Två</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -7305,10 +7305,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120094916</v>
+        <v>120079809</v>
       </c>
       <c r="B64" t="n">
-        <v>91884</v>
+        <v>90712</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7317,25 +7317,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5449</v>
+        <v>1503</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7348,13 +7348,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>746490</v>
+        <v>746368</v>
       </c>
       <c r="R64" t="n">
-        <v>7152513</v>
+        <v>7152599</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7399,22 +7399,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120086228</v>
+        <v>120094916</v>
       </c>
       <c r="B65" t="n">
-        <v>74638</v>
+        <v>91884</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7427,34 +7427,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6440</v>
+        <v>5449</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>746357</v>
+        <v>746490</v>
       </c>
       <c r="R65" t="n">
-        <v>7152581</v>
+        <v>7152513</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7495,6 +7498,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7513,10 +7517,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120079809</v>
+        <v>120086297</v>
       </c>
       <c r="B66" t="n">
-        <v>90712</v>
+        <v>91840</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7525,44 +7529,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>746368</v>
+        <v>746473</v>
       </c>
       <c r="R66" t="n">
-        <v>7152599</v>
+        <v>7152499</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7600,29 +7601,28 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120086297</v>
+        <v>120086228</v>
       </c>
       <c r="B67" t="n">
-        <v>91840</v>
+        <v>74638</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7631,25 +7631,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>6440</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7659,10 +7659,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>746473</v>
+        <v>746357</v>
       </c>
       <c r="R67" t="n">
-        <v>7152499</v>
+        <v>7152581</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>

--- a/artfynd/A 41672-2024 artfynd.xlsx
+++ b/artfynd/A 41672-2024 artfynd.xlsx
@@ -5432,10 +5432,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120094869</v>
+        <v>120086280</v>
       </c>
       <c r="B46" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5444,41 +5444,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>746522</v>
+        <v>746527</v>
       </c>
       <c r="R46" t="n">
-        <v>7152453</v>
+        <v>7152434</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5519,7 +5516,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5538,10 +5534,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120086280</v>
+        <v>120094869</v>
       </c>
       <c r="B47" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5550,38 +5546,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>746527</v>
+        <v>746522</v>
       </c>
       <c r="R47" t="n">
-        <v>7152434</v>
+        <v>7152453</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5622,6 +5621,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -7305,10 +7305,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120079809</v>
+        <v>120094916</v>
       </c>
       <c r="B64" t="n">
-        <v>90712</v>
+        <v>91884</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7317,25 +7317,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1503</v>
+        <v>5449</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7348,13 +7348,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>746368</v>
+        <v>746490</v>
       </c>
       <c r="R64" t="n">
-        <v>7152599</v>
+        <v>7152513</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7399,22 +7399,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120094916</v>
+        <v>120086228</v>
       </c>
       <c r="B65" t="n">
-        <v>91884</v>
+        <v>74638</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7427,37 +7427,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5449</v>
+        <v>6440</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>746490</v>
+        <v>746357</v>
       </c>
       <c r="R65" t="n">
-        <v>7152513</v>
+        <v>7152581</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7498,7 +7495,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7517,10 +7513,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120086297</v>
+        <v>120079809</v>
       </c>
       <c r="B66" t="n">
-        <v>91840</v>
+        <v>90712</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7529,41 +7525,44 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>746473</v>
+        <v>746368</v>
       </c>
       <c r="R66" t="n">
-        <v>7152499</v>
+        <v>7152599</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7601,28 +7600,29 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120086228</v>
+        <v>120086297</v>
       </c>
       <c r="B67" t="n">
-        <v>74638</v>
+        <v>91840</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7631,25 +7631,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7659,10 +7659,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>746357</v>
+        <v>746473</v>
       </c>
       <c r="R67" t="n">
-        <v>7152581</v>
+        <v>7152499</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>

--- a/artfynd/A 41672-2024 artfynd.xlsx
+++ b/artfynd/A 41672-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120069457</v>
+        <v>120069608</v>
       </c>
       <c r="B2" t="n">
-        <v>91856</v>
+        <v>91850</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>746379</v>
+        <v>746422</v>
       </c>
       <c r="R2" t="n">
-        <v>7152575</v>
+        <v>7152546</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120067137</v>
+        <v>120069348</v>
       </c>
       <c r="B3" t="n">
-        <v>91834</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>746520</v>
+        <v>746382</v>
       </c>
       <c r="R3" t="n">
-        <v>7152487</v>
+        <v>7152570</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120068365</v>
+        <v>120069457</v>
       </c>
       <c r="B4" t="n">
-        <v>91884</v>
+        <v>91874</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>746323</v>
+        <v>746379</v>
       </c>
       <c r="R4" t="n">
-        <v>7152700</v>
+        <v>7152575</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120068300</v>
+        <v>120067430</v>
       </c>
       <c r="B5" t="n">
-        <v>91863</v>
+        <v>91874</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>746336</v>
+        <v>746505</v>
       </c>
       <c r="R5" t="n">
-        <v>7152676</v>
+        <v>7152499</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120069348</v>
+        <v>120068300</v>
       </c>
       <c r="B6" t="n">
-        <v>91840</v>
+        <v>91881</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>746382</v>
+        <v>746336</v>
       </c>
       <c r="R6" t="n">
-        <v>7152570</v>
+        <v>7152676</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120067935</v>
+        <v>120068080</v>
       </c>
       <c r="B7" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>746381</v>
+        <v>746371</v>
       </c>
       <c r="R7" t="n">
-        <v>7152596</v>
+        <v>7152632</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120067568</v>
+        <v>120067137</v>
       </c>
       <c r="B8" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>746484</v>
+        <v>746520</v>
       </c>
       <c r="R8" t="n">
-        <v>7152500</v>
+        <v>7152487</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120067262</v>
+        <v>120068365</v>
       </c>
       <c r="B9" t="n">
-        <v>91840</v>
+        <v>91902</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,25 +1471,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>746520</v>
+        <v>746323</v>
       </c>
       <c r="R9" t="n">
-        <v>7152494</v>
+        <v>7152700</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120069608</v>
+        <v>120067885</v>
       </c>
       <c r="B10" t="n">
-        <v>91832</v>
+        <v>91902</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>746422</v>
+        <v>746399</v>
       </c>
       <c r="R10" t="n">
-        <v>7152546</v>
+        <v>7152617</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120068080</v>
+        <v>120066631</v>
       </c>
       <c r="B11" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>746371</v>
+        <v>746551</v>
       </c>
       <c r="R11" t="n">
-        <v>7152632</v>
+        <v>7152434</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120068255</v>
+        <v>120067504</v>
       </c>
       <c r="B12" t="n">
-        <v>91840</v>
+        <v>91874</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,25 +1807,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>746352</v>
+        <v>746486</v>
       </c>
       <c r="R12" t="n">
-        <v>7152686</v>
+        <v>7152501</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120067504</v>
+        <v>120068602</v>
       </c>
       <c r="B13" t="n">
-        <v>91856</v>
+        <v>79652</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,25 +1919,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2059</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>746486</v>
+        <v>746307</v>
       </c>
       <c r="R13" t="n">
-        <v>7152501</v>
+        <v>7152647</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120066631</v>
+        <v>120068331</v>
       </c>
       <c r="B14" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>746551</v>
+        <v>746318</v>
       </c>
       <c r="R14" t="n">
-        <v>7152434</v>
+        <v>7152701</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120068346</v>
+        <v>120067935</v>
       </c>
       <c r="B15" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,21 +2147,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>746324</v>
+        <v>746381</v>
       </c>
       <c r="R15" t="n">
-        <v>7152703</v>
+        <v>7152596</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120068602</v>
+        <v>120068255</v>
       </c>
       <c r="B16" t="n">
-        <v>79636</v>
+        <v>91858</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,21 +2259,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>746307</v>
+        <v>746352</v>
       </c>
       <c r="R16" t="n">
-        <v>7152647</v>
+        <v>7152686</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120066896</v>
+        <v>120068133</v>
       </c>
       <c r="B17" t="n">
-        <v>91863</v>
+        <v>91858</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2367,25 +2367,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>746537</v>
+        <v>746333</v>
       </c>
       <c r="R17" t="n">
-        <v>7152456</v>
+        <v>7152647</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120067979</v>
+        <v>120068383</v>
       </c>
       <c r="B18" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>746392</v>
+        <v>746313</v>
       </c>
       <c r="R18" t="n">
-        <v>7152615</v>
+        <v>7152706</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120068460</v>
+        <v>120067262</v>
       </c>
       <c r="B19" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>746312</v>
+        <v>746520</v>
       </c>
       <c r="R19" t="n">
-        <v>7152709</v>
+        <v>7152494</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120068331</v>
+        <v>120067979</v>
       </c>
       <c r="B20" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>746318</v>
+        <v>746392</v>
       </c>
       <c r="R20" t="n">
-        <v>7152701</v>
+        <v>7152615</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120067885</v>
+        <v>120067568</v>
       </c>
       <c r="B21" t="n">
-        <v>91884</v>
+        <v>91858</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2815,25 +2815,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>746399</v>
+        <v>746484</v>
       </c>
       <c r="R21" t="n">
-        <v>7152617</v>
+        <v>7152500</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120068383</v>
+        <v>120068460</v>
       </c>
       <c r="B22" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>746313</v>
+        <v>746312</v>
       </c>
       <c r="R22" t="n">
-        <v>7152706</v>
+        <v>7152709</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,10 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120067841</v>
+        <v>120066896</v>
       </c>
       <c r="B23" t="n">
-        <v>91840</v>
+        <v>91881</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3039,25 +3039,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>746469</v>
+        <v>746537</v>
       </c>
       <c r="R23" t="n">
-        <v>7152569</v>
+        <v>7152456</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,10 +3139,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120067430</v>
+        <v>120068346</v>
       </c>
       <c r="B24" t="n">
-        <v>91856</v>
+        <v>91870</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3151,25 +3151,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>746505</v>
+        <v>746324</v>
       </c>
       <c r="R24" t="n">
-        <v>7152499</v>
+        <v>7152703</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3251,10 +3251,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120068133</v>
+        <v>120067841</v>
       </c>
       <c r="B25" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>746333</v>
+        <v>746469</v>
       </c>
       <c r="R25" t="n">
-        <v>7152647</v>
+        <v>7152569</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3363,10 +3363,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120079812</v>
+        <v>120080307</v>
       </c>
       <c r="B26" t="n">
-        <v>91840</v>
+        <v>91902</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3375,25 +3375,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3403,13 +3403,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>746540</v>
+        <v>746426</v>
       </c>
       <c r="R26" t="n">
-        <v>7152434</v>
+        <v>7152510</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3447,29 +3447,28 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120094897</v>
+        <v>120094959</v>
       </c>
       <c r="B27" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3509,10 +3508,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>746482</v>
+        <v>746300</v>
       </c>
       <c r="R27" t="n">
-        <v>7152467</v>
+        <v>7152654</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3572,10 +3571,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120086279</v>
+        <v>120080336</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
+        <v>91858</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3584,25 +3583,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3612,10 +3611,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>746397</v>
+        <v>746545</v>
       </c>
       <c r="R28" t="n">
-        <v>7152654</v>
+        <v>7152464</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3662,22 +3661,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120080295</v>
+        <v>120094855</v>
       </c>
       <c r="B29" t="n">
-        <v>57463</v>
+        <v>91858</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3686,35 +3685,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3722,10 +3716,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>746385</v>
+        <v>746547</v>
       </c>
       <c r="R29" t="n">
-        <v>7152570</v>
+        <v>7152471</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3766,28 +3760,29 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120086272</v>
+        <v>120086277</v>
       </c>
       <c r="B30" t="n">
-        <v>74624</v>
+        <v>78542</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3796,25 +3791,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3824,10 +3819,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>746357</v>
+        <v>746302</v>
       </c>
       <c r="R30" t="n">
-        <v>7152581</v>
+        <v>7152670</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3886,10 +3881,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120079805</v>
+        <v>120094901</v>
       </c>
       <c r="B31" t="n">
-        <v>92030</v>
+        <v>91858</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3898,41 +3893,44 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>746437</v>
+        <v>746487</v>
       </c>
       <c r="R31" t="n">
-        <v>7152508</v>
+        <v>7152494</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3970,28 +3968,29 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120086230</v>
+        <v>120094939</v>
       </c>
       <c r="B32" t="n">
-        <v>90527</v>
+        <v>91858</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4004,34 +4003,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>746412</v>
+        <v>746413</v>
       </c>
       <c r="R32" t="n">
-        <v>7152564</v>
+        <v>7152616</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4072,6 +4074,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4090,10 +4093,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120094959</v>
+        <v>120086263</v>
       </c>
       <c r="B33" t="n">
-        <v>91840</v>
+        <v>92048</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4102,41 +4105,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>746300</v>
+        <v>746450</v>
       </c>
       <c r="R33" t="n">
-        <v>7152654</v>
+        <v>7152549</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4177,7 +4177,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4196,10 +4195,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120080343</v>
+        <v>120079809</v>
       </c>
       <c r="B34" t="n">
-        <v>91840</v>
+        <v>90730</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4208,41 +4207,44 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>746467</v>
+        <v>746368</v>
       </c>
       <c r="R34" t="n">
-        <v>7152466</v>
+        <v>7152599</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4280,28 +4282,29 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120080345</v>
+        <v>120080338</v>
       </c>
       <c r="B35" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4338,10 +4341,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>746459</v>
+        <v>746455</v>
       </c>
       <c r="R35" t="n">
-        <v>7152465</v>
+        <v>7152561</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4400,10 +4403,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120080346</v>
+        <v>120080349</v>
       </c>
       <c r="B36" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4440,10 +4443,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>746461</v>
+        <v>746540</v>
       </c>
       <c r="R36" t="n">
-        <v>7152458</v>
+        <v>7152444</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4502,10 +4505,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120080338</v>
+        <v>120086297</v>
       </c>
       <c r="B37" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4542,10 +4545,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>746455</v>
+        <v>746473</v>
       </c>
       <c r="R37" t="n">
-        <v>7152561</v>
+        <v>7152499</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4592,22 +4595,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120094951</v>
+        <v>120086259</v>
       </c>
       <c r="B38" t="n">
-        <v>91840</v>
+        <v>91850</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4616,41 +4619,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>746357</v>
+        <v>746394</v>
       </c>
       <c r="R38" t="n">
-        <v>7152686</v>
+        <v>7152581</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4691,7 +4691,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4710,10 +4709,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120086296</v>
+        <v>120086278</v>
       </c>
       <c r="B39" t="n">
-        <v>91840</v>
+        <v>78542</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4722,25 +4721,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4750,10 +4749,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>746425</v>
+        <v>746365</v>
       </c>
       <c r="R39" t="n">
-        <v>7152621</v>
+        <v>7152695</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4812,10 +4811,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120086263</v>
+        <v>120086291</v>
       </c>
       <c r="B40" t="n">
-        <v>92030</v>
+        <v>90825</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4824,25 +4823,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2079</v>
+        <v>65</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4852,10 +4851,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>746450</v>
+        <v>746502</v>
       </c>
       <c r="R40" t="n">
-        <v>7152549</v>
+        <v>7152478</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4914,10 +4913,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120094901</v>
+        <v>120080337</v>
       </c>
       <c r="B41" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4948,19 +4947,16 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>746487</v>
+        <v>746488</v>
       </c>
       <c r="R41" t="n">
-        <v>7152494</v>
+        <v>7152500</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5001,29 +4997,28 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120094886</v>
+        <v>120086266</v>
       </c>
       <c r="B42" t="n">
-        <v>91840</v>
+        <v>91881</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5032,41 +5027,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>746500</v>
+        <v>746429</v>
       </c>
       <c r="R42" t="n">
-        <v>7152466</v>
+        <v>7152625</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5107,7 +5099,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5126,10 +5117,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120086277</v>
+        <v>120086279</v>
       </c>
       <c r="B43" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5166,10 +5157,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>746302</v>
+        <v>746397</v>
       </c>
       <c r="R43" t="n">
-        <v>7152670</v>
+        <v>7152654</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5228,10 +5219,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120086276</v>
+        <v>120080340</v>
       </c>
       <c r="B44" t="n">
-        <v>78526</v>
+        <v>91858</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5240,25 +5231,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5268,10 +5259,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>746304</v>
+        <v>746398</v>
       </c>
       <c r="R44" t="n">
-        <v>7152657</v>
+        <v>7152548</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5318,22 +5309,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120086266</v>
+        <v>120094916</v>
       </c>
       <c r="B45" t="n">
-        <v>91863</v>
+        <v>91902</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5346,34 +5337,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>746429</v>
+        <v>746490</v>
       </c>
       <c r="R45" t="n">
-        <v>7152625</v>
+        <v>7152513</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5414,6 +5408,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5432,10 +5427,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120086280</v>
+        <v>120080326</v>
       </c>
       <c r="B46" t="n">
-        <v>78526</v>
+        <v>89247</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5444,25 +5439,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1596</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5472,10 +5467,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>746527</v>
+        <v>746543</v>
       </c>
       <c r="R46" t="n">
-        <v>7152434</v>
+        <v>7152437</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5522,22 +5517,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120094869</v>
+        <v>120080345</v>
       </c>
       <c r="B47" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5568,19 +5563,16 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>746522</v>
+        <v>746459</v>
       </c>
       <c r="R47" t="n">
-        <v>7152453</v>
+        <v>7152465</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5621,29 +5613,28 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120079797</v>
+        <v>120086294</v>
       </c>
       <c r="B48" t="n">
-        <v>89633</v>
+        <v>91858</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5652,25 +5643,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5680,13 +5671,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>746432</v>
+        <v>746310</v>
       </c>
       <c r="R48" t="n">
-        <v>7152509</v>
+        <v>7152670</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5730,22 +5721,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120094922</v>
+        <v>120080343</v>
       </c>
       <c r="B49" t="n">
-        <v>91884</v>
+        <v>91858</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5754,41 +5745,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>746442</v>
+        <v>746467</v>
       </c>
       <c r="R49" t="n">
-        <v>7152565</v>
+        <v>7152466</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5829,29 +5817,28 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120086238</v>
+        <v>120080348</v>
       </c>
       <c r="B50" t="n">
-        <v>57463</v>
+        <v>91858</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5860,46 +5847,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>746509</v>
+        <v>746505</v>
       </c>
       <c r="R50" t="n">
-        <v>7152434</v>
+        <v>7152451</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5934,11 +5913,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Två</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5951,22 +5925,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120080348</v>
+        <v>120094886</v>
       </c>
       <c r="B51" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5997,16 +5971,19 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>746505</v>
+        <v>746500</v>
       </c>
       <c r="R51" t="n">
-        <v>7152451</v>
+        <v>7152466</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6047,28 +6024,29 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120094932</v>
+        <v>120086269</v>
       </c>
       <c r="B52" t="n">
-        <v>91840</v>
+        <v>88170</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6077,25 +6055,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6108,10 +6086,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>746414</v>
+        <v>746365</v>
       </c>
       <c r="R52" t="n">
-        <v>7152584</v>
+        <v>7152575</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6144,6 +6122,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Inte ihålig men övriga karaktärer stämde.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6171,10 +6154,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120094907</v>
+        <v>120079797</v>
       </c>
       <c r="B53" t="n">
-        <v>91840</v>
+        <v>89650</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6183,44 +6166,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>746484</v>
+        <v>746432</v>
       </c>
       <c r="R53" t="n">
-        <v>7152510</v>
+        <v>7152509</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6258,29 +6238,28 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120086295</v>
+        <v>120079813</v>
       </c>
       <c r="B54" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6317,13 +6296,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>746365</v>
+        <v>746517</v>
       </c>
       <c r="R54" t="n">
-        <v>7152695</v>
+        <v>7152485</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6367,22 +6346,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120079813</v>
+        <v>120094907</v>
       </c>
       <c r="B55" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6413,19 +6392,22 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>746517</v>
+        <v>746484</v>
       </c>
       <c r="R55" t="n">
-        <v>7152485</v>
+        <v>7152510</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6463,28 +6445,29 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120080336</v>
+        <v>120080342</v>
       </c>
       <c r="B56" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6521,10 +6504,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>746545</v>
+        <v>746478</v>
       </c>
       <c r="R56" t="n">
-        <v>7152464</v>
+        <v>7152487</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6583,10 +6566,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120086294</v>
+        <v>120086238</v>
       </c>
       <c r="B57" t="n">
-        <v>91840</v>
+        <v>57473</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6595,38 +6578,46 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>746310</v>
+        <v>746509</v>
       </c>
       <c r="R57" t="n">
-        <v>7152670</v>
+        <v>7152434</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6659,6 +6650,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Två</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6685,10 +6681,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120086246</v>
+        <v>120094951</v>
       </c>
       <c r="B58" t="n">
-        <v>91884</v>
+        <v>91858</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6697,38 +6693,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>746475</v>
+        <v>746357</v>
       </c>
       <c r="R58" t="n">
-        <v>7152487</v>
+        <v>7152686</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6769,6 +6768,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6787,10 +6787,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120094945</v>
+        <v>120079805</v>
       </c>
       <c r="B59" t="n">
-        <v>91884</v>
+        <v>92048</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6803,40 +6803,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5449</v>
+        <v>2079</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>746417</v>
+        <v>746437</v>
       </c>
       <c r="R59" t="n">
-        <v>7152628</v>
+        <v>7152508</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6874,29 +6871,28 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120094849</v>
+        <v>120080346</v>
       </c>
       <c r="B60" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6927,19 +6923,16 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>746531</v>
+        <v>746461</v>
       </c>
       <c r="R60" t="n">
-        <v>7152454</v>
+        <v>7152458</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6980,29 +6973,28 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120086298</v>
+        <v>120094869</v>
       </c>
       <c r="B61" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7033,16 +7025,19 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>746527</v>
+        <v>746522</v>
       </c>
       <c r="R61" t="n">
-        <v>7152434</v>
+        <v>7152453</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7083,6 +7078,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7101,10 +7097,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120080337</v>
+        <v>120086298</v>
       </c>
       <c r="B62" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7141,10 +7137,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>746488</v>
+        <v>746527</v>
       </c>
       <c r="R62" t="n">
-        <v>7152500</v>
+        <v>7152434</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7191,22 +7187,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120086245</v>
+        <v>120080306</v>
       </c>
       <c r="B63" t="n">
-        <v>91884</v>
+        <v>91902</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7243,10 +7239,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>746365</v>
+        <v>746490</v>
       </c>
       <c r="R63" t="n">
-        <v>7152575</v>
+        <v>7152502</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7293,22 +7289,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120094916</v>
+        <v>120086280</v>
       </c>
       <c r="B64" t="n">
-        <v>91884</v>
+        <v>78542</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7321,37 +7317,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>746490</v>
+        <v>746527</v>
       </c>
       <c r="R64" t="n">
-        <v>7152513</v>
+        <v>7152434</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7392,7 +7385,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7411,10 +7403,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120086228</v>
+        <v>120094897</v>
       </c>
       <c r="B65" t="n">
-        <v>74638</v>
+        <v>91858</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7423,38 +7415,41 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>746357</v>
+        <v>746482</v>
       </c>
       <c r="R65" t="n">
-        <v>7152581</v>
+        <v>7152467</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7495,6 +7490,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7513,10 +7509,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120079809</v>
+        <v>120086245</v>
       </c>
       <c r="B66" t="n">
-        <v>90712</v>
+        <v>91902</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7525,44 +7521,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1503</v>
+        <v>5449</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>746368</v>
+        <v>746365</v>
       </c>
       <c r="R66" t="n">
-        <v>7152599</v>
+        <v>7152575</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7600,29 +7593,28 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120086297</v>
+        <v>120086228</v>
       </c>
       <c r="B67" t="n">
-        <v>91840</v>
+        <v>74654</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7631,25 +7623,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>6440</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7659,10 +7651,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>746473</v>
+        <v>746357</v>
       </c>
       <c r="R67" t="n">
-        <v>7152499</v>
+        <v>7152581</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7721,10 +7713,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120086265</v>
+        <v>120086275</v>
       </c>
       <c r="B68" t="n">
-        <v>78263</v>
+        <v>78542</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7737,21 +7729,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7761,10 +7753,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>746353</v>
+        <v>746370</v>
       </c>
       <c r="R68" t="n">
-        <v>7152592</v>
+        <v>7152601</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7823,10 +7815,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120080319</v>
+        <v>120080295</v>
       </c>
       <c r="B69" t="n">
-        <v>92030</v>
+        <v>57473</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7839,34 +7831,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2079</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>746477</v>
+        <v>746385</v>
       </c>
       <c r="R69" t="n">
-        <v>7152502</v>
+        <v>7152570</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7901,11 +7901,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På kolad tallstubbe</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -7914,26 +7909,6 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL69" t="inlineStr">
-        <is>
-          <t>Kolad tallstubbe</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Kolad tallstubbe</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -7950,10 +7925,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120080326</v>
+        <v>120086296</v>
       </c>
       <c r="B70" t="n">
-        <v>89230</v>
+        <v>91858</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7962,25 +7937,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1596</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7990,10 +7965,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>746543</v>
+        <v>746425</v>
       </c>
       <c r="R70" t="n">
-        <v>7152437</v>
+        <v>7152621</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8040,22 +8015,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120080340</v>
+        <v>120086246</v>
       </c>
       <c r="B71" t="n">
-        <v>91840</v>
+        <v>91902</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8064,25 +8039,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8092,10 +8067,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>746398</v>
+        <v>746475</v>
       </c>
       <c r="R71" t="n">
-        <v>7152548</v>
+        <v>7152487</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8142,22 +8117,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120080341</v>
+        <v>120086272</v>
       </c>
       <c r="B72" t="n">
-        <v>91840</v>
+        <v>74640</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8170,21 +8145,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8194,10 +8169,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>746384</v>
+        <v>746357</v>
       </c>
       <c r="R72" t="n">
-        <v>7152544</v>
+        <v>7152581</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8244,22 +8219,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120086275</v>
+        <v>120086276</v>
       </c>
       <c r="B73" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8296,10 +8271,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>746370</v>
+        <v>746304</v>
       </c>
       <c r="R73" t="n">
-        <v>7152601</v>
+        <v>7152657</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8358,10 +8333,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120080342</v>
+        <v>120079802</v>
       </c>
       <c r="B74" t="n">
-        <v>91840</v>
+        <v>91902</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8370,25 +8345,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8398,13 +8373,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>746478</v>
+        <v>746495</v>
       </c>
       <c r="R74" t="n">
-        <v>7152487</v>
+        <v>7152470</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8448,22 +8423,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120094939</v>
+        <v>120086230</v>
       </c>
       <c r="B75" t="n">
-        <v>91840</v>
+        <v>90545</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8476,37 +8451,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>746413</v>
+        <v>746412</v>
       </c>
       <c r="R75" t="n">
-        <v>7152616</v>
+        <v>7152564</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8547,7 +8519,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8566,10 +8537,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120086259</v>
+        <v>120079812</v>
       </c>
       <c r="B76" t="n">
-        <v>91832</v>
+        <v>91858</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8578,25 +8549,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8606,13 +8577,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>746394</v>
+        <v>746540</v>
       </c>
       <c r="R76" t="n">
-        <v>7152581</v>
+        <v>7152434</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8650,28 +8621,29 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120080306</v>
+        <v>120086265</v>
       </c>
       <c r="B77" t="n">
-        <v>91884</v>
+        <v>78279</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8684,21 +8656,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8708,10 +8680,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>746490</v>
+        <v>746353</v>
       </c>
       <c r="R77" t="n">
-        <v>7152502</v>
+        <v>7152592</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8758,22 +8730,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120080307</v>
+        <v>120080341</v>
       </c>
       <c r="B78" t="n">
-        <v>91884</v>
+        <v>91858</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8782,25 +8754,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8810,10 +8782,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>746426</v>
+        <v>746384</v>
       </c>
       <c r="R78" t="n">
-        <v>7152510</v>
+        <v>7152544</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8872,10 +8844,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120086269</v>
+        <v>120086295</v>
       </c>
       <c r="B79" t="n">
-        <v>88153</v>
+        <v>91858</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8884,31 +8856,28 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
@@ -8918,7 +8887,7 @@
         <v>746365</v>
       </c>
       <c r="R79" t="n">
-        <v>7152575</v>
+        <v>7152695</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8953,18 +8922,12 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Inte ihålig men övriga karaktärer stämde.</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8983,10 +8946,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120086291</v>
+        <v>120094849</v>
       </c>
       <c r="B80" t="n">
-        <v>90807</v>
+        <v>91858</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8995,38 +8958,41 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>746502</v>
+        <v>746531</v>
       </c>
       <c r="R80" t="n">
-        <v>7152478</v>
+        <v>7152454</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9067,6 +9033,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -9085,10 +9052,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120080349</v>
+        <v>120094922</v>
       </c>
       <c r="B81" t="n">
-        <v>91840</v>
+        <v>91902</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9097,38 +9064,41 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>746540</v>
+        <v>746442</v>
       </c>
       <c r="R81" t="n">
-        <v>7152444</v>
+        <v>7152565</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9169,28 +9139,29 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120086278</v>
+        <v>120080319</v>
       </c>
       <c r="B82" t="n">
-        <v>78526</v>
+        <v>92048</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9203,21 +9174,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9227,10 +9198,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>746365</v>
+        <v>746477</v>
       </c>
       <c r="R82" t="n">
-        <v>7152695</v>
+        <v>7152502</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9265,6 +9236,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På kolad tallstubbe</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9273,26 +9249,46 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL82" t="inlineStr">
+        <is>
+          <t>Kolad tallstubbe</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Kolad tallstubbe</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120086274</v>
+        <v>120094932</v>
       </c>
       <c r="B83" t="n">
-        <v>78526</v>
+        <v>91858</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9301,38 +9297,41 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>746478</v>
+        <v>746414</v>
       </c>
       <c r="R83" t="n">
-        <v>7152496</v>
+        <v>7152584</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9373,6 +9372,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9391,10 +9391,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120079802</v>
+        <v>120094945</v>
       </c>
       <c r="B84" t="n">
-        <v>91884</v>
+        <v>91902</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9425,19 +9425,22 @@
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>746495</v>
+        <v>746417</v>
       </c>
       <c r="R84" t="n">
-        <v>7152470</v>
+        <v>7152628</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9475,28 +9478,29 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120094855</v>
+        <v>120086274</v>
       </c>
       <c r="B85" t="n">
-        <v>91840</v>
+        <v>78542</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9505,41 +9509,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>746547</v>
+        <v>746478</v>
       </c>
       <c r="R85" t="n">
-        <v>7152471</v>
+        <v>7152496</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9580,7 +9581,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41672-2024 artfynd.xlsx
+++ b/artfynd/A 41672-2024 artfynd.xlsx
@@ -4403,10 +4403,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120080349</v>
+        <v>120086278</v>
       </c>
       <c r="B36" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4415,25 +4415,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>746540</v>
+        <v>746365</v>
       </c>
       <c r="R36" t="n">
-        <v>7152444</v>
+        <v>7152695</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4493,19 +4493,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120086297</v>
+        <v>120080349</v>
       </c>
       <c r="B37" t="n">
         <v>91858</v>
@@ -4545,10 +4545,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>746473</v>
+        <v>746540</v>
       </c>
       <c r="R37" t="n">
-        <v>7152499</v>
+        <v>7152444</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4595,22 +4595,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120086259</v>
+        <v>120086297</v>
       </c>
       <c r="B38" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4619,25 +4619,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4647,10 +4647,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>746394</v>
+        <v>746473</v>
       </c>
       <c r="R38" t="n">
-        <v>7152581</v>
+        <v>7152499</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4709,10 +4709,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120086278</v>
+        <v>120086259</v>
       </c>
       <c r="B39" t="n">
-        <v>78542</v>
+        <v>91850</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4725,21 +4725,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>746365</v>
+        <v>746394</v>
       </c>
       <c r="R39" t="n">
-        <v>7152695</v>
+        <v>7152581</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4811,10 +4811,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120086291</v>
+        <v>120086266</v>
       </c>
       <c r="B40" t="n">
-        <v>90825</v>
+        <v>91881</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4823,25 +4823,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>65</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>746502</v>
+        <v>746429</v>
       </c>
       <c r="R40" t="n">
-        <v>7152478</v>
+        <v>7152625</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4913,10 +4913,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120080337</v>
+        <v>120086291</v>
       </c>
       <c r="B41" t="n">
-        <v>91858</v>
+        <v>90825</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4925,25 +4925,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4953,10 +4953,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>746488</v>
+        <v>746502</v>
       </c>
       <c r="R41" t="n">
-        <v>7152500</v>
+        <v>7152478</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5003,22 +5003,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120086266</v>
+        <v>120080337</v>
       </c>
       <c r="B42" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5027,25 +5027,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5055,10 +5055,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>746429</v>
+        <v>746488</v>
       </c>
       <c r="R42" t="n">
-        <v>7152625</v>
+        <v>7152500</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5105,12 +5105,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5219,10 +5219,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120080340</v>
+        <v>120094916</v>
       </c>
       <c r="B44" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5231,38 +5231,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>746398</v>
+        <v>746490</v>
       </c>
       <c r="R44" t="n">
-        <v>7152548</v>
+        <v>7152513</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5303,28 +5306,29 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120094916</v>
+        <v>120080340</v>
       </c>
       <c r="B45" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5333,41 +5337,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>746490</v>
+        <v>746398</v>
       </c>
       <c r="R45" t="n">
-        <v>7152513</v>
+        <v>7152548</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5408,19 +5409,18 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -8231,10 +8231,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120086276</v>
+        <v>120079802</v>
       </c>
       <c r="B73" t="n">
-        <v>78542</v>
+        <v>91902</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8247,21 +8247,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8271,13 +8271,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>746304</v>
+        <v>746495</v>
       </c>
       <c r="R73" t="n">
-        <v>7152657</v>
+        <v>7152470</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8321,22 +8321,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120079802</v>
+        <v>120086230</v>
       </c>
       <c r="B74" t="n">
-        <v>91902</v>
+        <v>90545</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8345,25 +8345,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5449</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8373,13 +8373,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>746495</v>
+        <v>746412</v>
       </c>
       <c r="R74" t="n">
-        <v>7152470</v>
+        <v>7152564</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8423,22 +8423,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120086230</v>
+        <v>120086276</v>
       </c>
       <c r="B75" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8447,25 +8447,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8475,10 +8475,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>746412</v>
+        <v>746304</v>
       </c>
       <c r="R75" t="n">
-        <v>7152564</v>
+        <v>7152657</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9391,10 +9391,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120094945</v>
+        <v>120086274</v>
       </c>
       <c r="B84" t="n">
-        <v>91902</v>
+        <v>78542</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9407,37 +9407,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>746417</v>
+        <v>746478</v>
       </c>
       <c r="R84" t="n">
-        <v>7152628</v>
+        <v>7152496</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9478,7 +9475,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9497,10 +9493,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120086274</v>
+        <v>120094945</v>
       </c>
       <c r="B85" t="n">
-        <v>78542</v>
+        <v>91902</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9513,34 +9509,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>746478</v>
+        <v>746417</v>
       </c>
       <c r="R85" t="n">
-        <v>7152496</v>
+        <v>7152628</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9581,6 +9580,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41672-2024 artfynd.xlsx
+++ b/artfynd/A 41672-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120069608</v>
+        <v>120067137</v>
       </c>
       <c r="B2" t="n">
-        <v>91850</v>
+        <v>91852</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>746422</v>
+        <v>746520</v>
       </c>
       <c r="R2" t="n">
-        <v>7152546</v>
+        <v>7152487</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120069348</v>
+        <v>120068331</v>
       </c>
       <c r="B3" t="n">
         <v>91858</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>746382</v>
+        <v>746318</v>
       </c>
       <c r="R3" t="n">
-        <v>7152570</v>
+        <v>7152701</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120067430</v>
+        <v>120068080</v>
       </c>
       <c r="B5" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>746505</v>
+        <v>746371</v>
       </c>
       <c r="R5" t="n">
-        <v>7152499</v>
+        <v>7152632</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120068300</v>
+        <v>120069348</v>
       </c>
       <c r="B6" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>746336</v>
+        <v>746382</v>
       </c>
       <c r="R6" t="n">
-        <v>7152676</v>
+        <v>7152570</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120068080</v>
+        <v>120067841</v>
       </c>
       <c r="B7" t="n">
         <v>91858</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>746371</v>
+        <v>746469</v>
       </c>
       <c r="R7" t="n">
-        <v>7152632</v>
+        <v>7152569</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120067137</v>
+        <v>120069608</v>
       </c>
       <c r="B8" t="n">
-        <v>91852</v>
+        <v>91850</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>746520</v>
+        <v>746422</v>
       </c>
       <c r="R8" t="n">
-        <v>7152487</v>
+        <v>7152546</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120068365</v>
+        <v>120068460</v>
       </c>
       <c r="B9" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,25 +1471,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>746323</v>
+        <v>746312</v>
       </c>
       <c r="R9" t="n">
-        <v>7152700</v>
+        <v>7152709</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120067885</v>
+        <v>120067979</v>
       </c>
       <c r="B10" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,25 +1583,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>746399</v>
+        <v>746392</v>
       </c>
       <c r="R10" t="n">
-        <v>7152617</v>
+        <v>7152615</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,7 +1683,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120066631</v>
+        <v>120068133</v>
       </c>
       <c r="B11" t="n">
         <v>91858</v>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>746551</v>
+        <v>746333</v>
       </c>
       <c r="R11" t="n">
-        <v>7152434</v>
+        <v>7152647</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120068602</v>
+        <v>120068300</v>
       </c>
       <c r="B13" t="n">
-        <v>79652</v>
+        <v>91881</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,25 +1919,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>5966</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>746307</v>
+        <v>746336</v>
       </c>
       <c r="R13" t="n">
-        <v>7152647</v>
+        <v>7152676</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120068331</v>
+        <v>120068602</v>
       </c>
       <c r="B14" t="n">
-        <v>91858</v>
+        <v>79652</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>746318</v>
+        <v>746307</v>
       </c>
       <c r="R14" t="n">
-        <v>7152701</v>
+        <v>7152647</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120067935</v>
+        <v>120068365</v>
       </c>
       <c r="B15" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2143,25 +2143,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>746381</v>
+        <v>746323</v>
       </c>
       <c r="R15" t="n">
-        <v>7152596</v>
+        <v>7152700</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120068255</v>
+        <v>120067430</v>
       </c>
       <c r="B16" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2255,25 +2255,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>746352</v>
+        <v>746505</v>
       </c>
       <c r="R16" t="n">
-        <v>7152686</v>
+        <v>7152499</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,7 +2355,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120068133</v>
+        <v>120066631</v>
       </c>
       <c r="B17" t="n">
         <v>91858</v>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>746333</v>
+        <v>746551</v>
       </c>
       <c r="R17" t="n">
-        <v>7152647</v>
+        <v>7152434</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120068383</v>
+        <v>120066896</v>
       </c>
       <c r="B18" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2479,25 +2479,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>746313</v>
+        <v>746537</v>
       </c>
       <c r="R18" t="n">
-        <v>7152706</v>
+        <v>7152456</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120067262</v>
+        <v>120068346</v>
       </c>
       <c r="B19" t="n">
-        <v>91858</v>
+        <v>91870</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2595,21 +2595,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>746520</v>
+        <v>746324</v>
       </c>
       <c r="R19" t="n">
-        <v>7152494</v>
+        <v>7152703</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,7 +2691,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120067979</v>
+        <v>120067935</v>
       </c>
       <c r="B20" t="n">
         <v>91858</v>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>746392</v>
+        <v>746381</v>
       </c>
       <c r="R20" t="n">
-        <v>7152615</v>
+        <v>7152596</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,7 +2803,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120067568</v>
+        <v>120067262</v>
       </c>
       <c r="B21" t="n">
         <v>91858</v>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>746484</v>
+        <v>746520</v>
       </c>
       <c r="R21" t="n">
-        <v>7152500</v>
+        <v>7152494</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,7 +2915,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120068460</v>
+        <v>120067568</v>
       </c>
       <c r="B22" t="n">
         <v>91858</v>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>746312</v>
+        <v>746484</v>
       </c>
       <c r="R22" t="n">
-        <v>7152709</v>
+        <v>7152500</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,10 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120066896</v>
+        <v>120067885</v>
       </c>
       <c r="B23" t="n">
-        <v>91881</v>
+        <v>91902</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3043,21 +3043,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>746537</v>
+        <v>746399</v>
       </c>
       <c r="R23" t="n">
-        <v>7152456</v>
+        <v>7152617</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,10 +3139,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120068346</v>
+        <v>120068255</v>
       </c>
       <c r="B24" t="n">
-        <v>91870</v>
+        <v>91858</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>746324</v>
+        <v>746352</v>
       </c>
       <c r="R24" t="n">
-        <v>7152703</v>
+        <v>7152686</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3251,7 +3251,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120067841</v>
+        <v>120068383</v>
       </c>
       <c r="B25" t="n">
         <v>91858</v>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>746469</v>
+        <v>746313</v>
       </c>
       <c r="R25" t="n">
-        <v>7152569</v>
+        <v>7152706</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3363,10 +3363,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120080307</v>
+        <v>120094932</v>
       </c>
       <c r="B26" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3375,38 +3375,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>746426</v>
+        <v>746414</v>
       </c>
       <c r="R26" t="n">
-        <v>7152510</v>
+        <v>7152584</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3447,25 +3450,26 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120094959</v>
+        <v>120086297</v>
       </c>
       <c r="B27" t="n">
         <v>91858</v>
@@ -3499,19 +3503,16 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>746300</v>
+        <v>746473</v>
       </c>
       <c r="R27" t="n">
-        <v>7152654</v>
+        <v>7152499</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3552,7 +3553,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3571,10 +3571,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120080336</v>
+        <v>120086291</v>
       </c>
       <c r="B28" t="n">
-        <v>91858</v>
+        <v>90825</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3583,25 +3583,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3611,10 +3611,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>746545</v>
+        <v>746502</v>
       </c>
       <c r="R28" t="n">
-        <v>7152464</v>
+        <v>7152478</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3661,22 +3661,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120094855</v>
+        <v>120086279</v>
       </c>
       <c r="B29" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3685,41 +3685,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>746547</v>
+        <v>746397</v>
       </c>
       <c r="R29" t="n">
-        <v>7152471</v>
+        <v>7152654</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3760,7 +3757,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3779,10 +3775,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120086277</v>
+        <v>120080306</v>
       </c>
       <c r="B30" t="n">
-        <v>78542</v>
+        <v>91902</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3795,21 +3791,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3819,10 +3815,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>746302</v>
+        <v>746490</v>
       </c>
       <c r="R30" t="n">
-        <v>7152670</v>
+        <v>7152502</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3869,22 +3865,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120094901</v>
+        <v>120080295</v>
       </c>
       <c r="B31" t="n">
-        <v>91858</v>
+        <v>57473</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3893,30 +3889,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3924,10 +3925,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>746487</v>
+        <v>746385</v>
       </c>
       <c r="R31" t="n">
-        <v>7152494</v>
+        <v>7152570</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3968,26 +3969,25 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120094939</v>
+        <v>120079813</v>
       </c>
       <c r="B32" t="n">
         <v>91858</v>
@@ -4021,22 +4021,19 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>746413</v>
+        <v>746517</v>
       </c>
       <c r="R32" t="n">
-        <v>7152616</v>
+        <v>7152485</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4074,29 +4071,28 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120086263</v>
+        <v>120080343</v>
       </c>
       <c r="B33" t="n">
-        <v>92048</v>
+        <v>91858</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4105,25 +4101,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4133,10 +4129,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>746450</v>
+        <v>746467</v>
       </c>
       <c r="R33" t="n">
-        <v>7152549</v>
+        <v>7152466</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4183,22 +4179,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120079809</v>
+        <v>120086238</v>
       </c>
       <c r="B34" t="n">
-        <v>90730</v>
+        <v>57473</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4207,30 +4203,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1503</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4238,13 +4239,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>746368</v>
+        <v>746509</v>
       </c>
       <c r="R34" t="n">
-        <v>7152599</v>
+        <v>7152434</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4276,35 +4277,39 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Två</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120080338</v>
+        <v>120086230</v>
       </c>
       <c r="B35" t="n">
-        <v>91858</v>
+        <v>90545</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4317,21 +4322,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4341,10 +4346,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>746455</v>
+        <v>746412</v>
       </c>
       <c r="R35" t="n">
-        <v>7152561</v>
+        <v>7152564</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4391,22 +4396,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120086278</v>
+        <v>120094922</v>
       </c>
       <c r="B36" t="n">
-        <v>78542</v>
+        <v>91902</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4419,34 +4424,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>746365</v>
+        <v>746442</v>
       </c>
       <c r="R36" t="n">
-        <v>7152695</v>
+        <v>7152565</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4487,6 +4495,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4505,10 +4514,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120080349</v>
+        <v>120079802</v>
       </c>
       <c r="B37" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4517,25 +4526,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4545,13 +4554,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>746540</v>
+        <v>746495</v>
       </c>
       <c r="R37" t="n">
-        <v>7152444</v>
+        <v>7152470</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4595,22 +4604,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120086297</v>
+        <v>120086263</v>
       </c>
       <c r="B38" t="n">
-        <v>91858</v>
+        <v>92048</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4619,25 +4628,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4647,10 +4656,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>746473</v>
+        <v>746450</v>
       </c>
       <c r="R38" t="n">
-        <v>7152499</v>
+        <v>7152549</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4709,10 +4718,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120086259</v>
+        <v>120086245</v>
       </c>
       <c r="B39" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4725,21 +4734,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4749,10 +4758,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>746394</v>
+        <v>746365</v>
       </c>
       <c r="R39" t="n">
-        <v>7152581</v>
+        <v>7152575</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4811,10 +4820,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120086266</v>
+        <v>120080345</v>
       </c>
       <c r="B40" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4823,25 +4832,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4851,10 +4860,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>746429</v>
+        <v>746459</v>
       </c>
       <c r="R40" t="n">
-        <v>7152625</v>
+        <v>7152465</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4901,22 +4910,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120086291</v>
+        <v>120086294</v>
       </c>
       <c r="B41" t="n">
-        <v>90825</v>
+        <v>91858</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4925,25 +4934,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4953,10 +4962,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>746502</v>
+        <v>746310</v>
       </c>
       <c r="R41" t="n">
-        <v>7152478</v>
+        <v>7152670</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5015,7 +5024,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120080337</v>
+        <v>120094897</v>
       </c>
       <c r="B42" t="n">
         <v>91858</v>
@@ -5049,16 +5058,19 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>746488</v>
+        <v>746482</v>
       </c>
       <c r="R42" t="n">
-        <v>7152500</v>
+        <v>7152467</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5099,28 +5111,29 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120086279</v>
+        <v>120086265</v>
       </c>
       <c r="B43" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5133,21 +5146,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5157,10 +5170,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>746397</v>
+        <v>746353</v>
       </c>
       <c r="R43" t="n">
-        <v>7152654</v>
+        <v>7152592</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5219,10 +5232,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120094916</v>
+        <v>120094907</v>
       </c>
       <c r="B44" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5231,25 +5244,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5262,10 +5275,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>746490</v>
+        <v>746484</v>
       </c>
       <c r="R44" t="n">
-        <v>7152513</v>
+        <v>7152510</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5325,10 +5338,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120080340</v>
+        <v>120086266</v>
       </c>
       <c r="B45" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5337,25 +5350,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5365,10 +5378,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>746398</v>
+        <v>746429</v>
       </c>
       <c r="R45" t="n">
-        <v>7152548</v>
+        <v>7152625</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5415,22 +5428,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120080326</v>
+        <v>120086295</v>
       </c>
       <c r="B46" t="n">
-        <v>89247</v>
+        <v>91858</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5439,25 +5452,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1596</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5467,10 +5480,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>746543</v>
+        <v>746365</v>
       </c>
       <c r="R46" t="n">
-        <v>7152437</v>
+        <v>7152695</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5517,22 +5530,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120080345</v>
+        <v>120094916</v>
       </c>
       <c r="B47" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5541,38 +5554,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>746459</v>
+        <v>746490</v>
       </c>
       <c r="R47" t="n">
-        <v>7152465</v>
+        <v>7152513</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5613,28 +5629,29 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120086294</v>
+        <v>120079805</v>
       </c>
       <c r="B48" t="n">
-        <v>91858</v>
+        <v>92048</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5643,25 +5660,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5671,13 +5688,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>746310</v>
+        <v>746437</v>
       </c>
       <c r="R48" t="n">
-        <v>7152670</v>
+        <v>7152508</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5721,22 +5738,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120080343</v>
+        <v>120086228</v>
       </c>
       <c r="B49" t="n">
-        <v>91858</v>
+        <v>74654</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5745,25 +5762,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5773,10 +5790,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>746467</v>
+        <v>746357</v>
       </c>
       <c r="R49" t="n">
-        <v>7152466</v>
+        <v>7152581</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5823,19 +5840,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120080348</v>
+        <v>120080346</v>
       </c>
       <c r="B50" t="n">
         <v>91858</v>
@@ -5875,10 +5892,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>746505</v>
+        <v>746461</v>
       </c>
       <c r="R50" t="n">
-        <v>7152451</v>
+        <v>7152458</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5937,7 +5954,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120094886</v>
+        <v>120079812</v>
       </c>
       <c r="B51" t="n">
         <v>91858</v>
@@ -5971,22 +5988,19 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>746500</v>
+        <v>746540</v>
       </c>
       <c r="R51" t="n">
-        <v>7152466</v>
+        <v>7152434</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6031,22 +6045,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120086269</v>
+        <v>120080326</v>
       </c>
       <c r="B52" t="n">
-        <v>88170</v>
+        <v>89247</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6055,41 +6069,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4962</v>
+        <v>1596</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>746365</v>
+        <v>746543</v>
       </c>
       <c r="R52" t="n">
-        <v>7152575</v>
+        <v>7152437</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6124,40 +6135,34 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Inte ihålig men övriga karaktärer stämde.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120079797</v>
+        <v>120080336</v>
       </c>
       <c r="B53" t="n">
-        <v>89650</v>
+        <v>91858</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6166,25 +6171,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6194,13 +6199,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>746432</v>
+        <v>746545</v>
       </c>
       <c r="R53" t="n">
-        <v>7152509</v>
+        <v>7152464</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6244,22 +6249,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120079813</v>
+        <v>120086275</v>
       </c>
       <c r="B54" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6268,25 +6273,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6296,13 +6301,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>746517</v>
+        <v>746370</v>
       </c>
       <c r="R54" t="n">
-        <v>7152485</v>
+        <v>7152601</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6346,22 +6351,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120094907</v>
+        <v>120086276</v>
       </c>
       <c r="B55" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6370,41 +6375,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>746484</v>
+        <v>746304</v>
       </c>
       <c r="R55" t="n">
-        <v>7152510</v>
+        <v>7152657</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6445,7 +6447,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6464,10 +6465,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120080342</v>
+        <v>120080319</v>
       </c>
       <c r="B56" t="n">
-        <v>91858</v>
+        <v>92048</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6476,25 +6477,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6504,10 +6505,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>746478</v>
+        <v>746477</v>
       </c>
       <c r="R56" t="n">
-        <v>7152487</v>
+        <v>7152502</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6542,6 +6543,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På kolad tallstubbe</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6550,6 +6556,26 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL56" t="inlineStr">
+        <is>
+          <t>Kolad tallstubbe</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Kolad tallstubbe</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -6566,10 +6592,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120086238</v>
+        <v>120094849</v>
       </c>
       <c r="B57" t="n">
-        <v>57473</v>
+        <v>91858</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6578,35 +6604,30 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6614,10 +6635,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>746509</v>
+        <v>746531</v>
       </c>
       <c r="R57" t="n">
-        <v>7152434</v>
+        <v>7152454</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6652,17 +6673,13 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Två</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6681,10 +6698,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120094951</v>
+        <v>120079809</v>
       </c>
       <c r="B58" t="n">
-        <v>91858</v>
+        <v>90730</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6693,25 +6710,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6724,13 +6741,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>746357</v>
+        <v>746368</v>
       </c>
       <c r="R58" t="n">
-        <v>7152686</v>
+        <v>7152599</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6775,22 +6792,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120079805</v>
+        <v>120094959</v>
       </c>
       <c r="B59" t="n">
-        <v>92048</v>
+        <v>91858</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6799,41 +6816,44 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>746437</v>
+        <v>746300</v>
       </c>
       <c r="R59" t="n">
-        <v>7152508</v>
+        <v>7152654</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6871,25 +6891,26 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120080346</v>
+        <v>120080340</v>
       </c>
       <c r="B60" t="n">
         <v>91858</v>
@@ -6929,10 +6950,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>746461</v>
+        <v>746398</v>
       </c>
       <c r="R60" t="n">
-        <v>7152458</v>
+        <v>7152548</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7097,10 +7118,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120086298</v>
+        <v>120094945</v>
       </c>
       <c r="B62" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7109,38 +7130,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>746527</v>
+        <v>746417</v>
       </c>
       <c r="R62" t="n">
-        <v>7152434</v>
+        <v>7152628</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7181,6 +7205,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7199,10 +7224,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120080306</v>
+        <v>120086277</v>
       </c>
       <c r="B63" t="n">
-        <v>91902</v>
+        <v>78542</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7215,21 +7240,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7239,10 +7264,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>746490</v>
+        <v>746302</v>
       </c>
       <c r="R63" t="n">
-        <v>7152502</v>
+        <v>7152670</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7289,22 +7314,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120086280</v>
+        <v>120080349</v>
       </c>
       <c r="B64" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7313,25 +7338,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7341,10 +7366,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>746527</v>
+        <v>746540</v>
       </c>
       <c r="R64" t="n">
-        <v>7152434</v>
+        <v>7152444</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7391,19 +7416,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120094897</v>
+        <v>120094855</v>
       </c>
       <c r="B65" t="n">
         <v>91858</v>
@@ -7446,10 +7471,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>746482</v>
+        <v>746547</v>
       </c>
       <c r="R65" t="n">
-        <v>7152467</v>
+        <v>7152471</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7509,10 +7534,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120086245</v>
+        <v>120094939</v>
       </c>
       <c r="B66" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7521,38 +7546,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>746365</v>
+        <v>746413</v>
       </c>
       <c r="R66" t="n">
-        <v>7152575</v>
+        <v>7152616</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7593,6 +7621,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7611,10 +7640,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120086228</v>
+        <v>120080341</v>
       </c>
       <c r="B67" t="n">
-        <v>74654</v>
+        <v>91858</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7623,25 +7652,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7651,10 +7680,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>746357</v>
+        <v>746384</v>
       </c>
       <c r="R67" t="n">
-        <v>7152581</v>
+        <v>7152544</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7701,22 +7730,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120086275</v>
+        <v>120080348</v>
       </c>
       <c r="B68" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7725,25 +7754,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7753,10 +7782,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>746370</v>
+        <v>746505</v>
       </c>
       <c r="R68" t="n">
-        <v>7152601</v>
+        <v>7152451</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7803,22 +7832,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120080295</v>
+        <v>120080338</v>
       </c>
       <c r="B69" t="n">
-        <v>57473</v>
+        <v>91858</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7827,46 +7856,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>746385</v>
+        <v>746455</v>
       </c>
       <c r="R69" t="n">
-        <v>7152570</v>
+        <v>7152561</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7925,7 +7946,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120086296</v>
+        <v>120080337</v>
       </c>
       <c r="B70" t="n">
         <v>91858</v>
@@ -7965,10 +7986,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>746425</v>
+        <v>746488</v>
       </c>
       <c r="R70" t="n">
-        <v>7152621</v>
+        <v>7152500</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8015,22 +8036,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120086246</v>
+        <v>120086274</v>
       </c>
       <c r="B71" t="n">
-        <v>91902</v>
+        <v>78542</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8043,21 +8064,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8067,10 +8088,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>746475</v>
+        <v>746478</v>
       </c>
       <c r="R71" t="n">
-        <v>7152487</v>
+        <v>7152496</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8129,10 +8150,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120086272</v>
+        <v>120086280</v>
       </c>
       <c r="B72" t="n">
-        <v>74640</v>
+        <v>78542</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8141,25 +8162,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8169,10 +8190,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>746357</v>
+        <v>746527</v>
       </c>
       <c r="R72" t="n">
-        <v>7152581</v>
+        <v>7152434</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8231,10 +8252,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120079802</v>
+        <v>120086272</v>
       </c>
       <c r="B73" t="n">
-        <v>91902</v>
+        <v>74640</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8243,25 +8264,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5449</v>
+        <v>306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8271,13 +8292,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>746495</v>
+        <v>746357</v>
       </c>
       <c r="R73" t="n">
-        <v>7152470</v>
+        <v>7152581</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8321,22 +8342,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120086230</v>
+        <v>120094886</v>
       </c>
       <c r="B74" t="n">
-        <v>90545</v>
+        <v>91858</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8349,34 +8370,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>746412</v>
+        <v>746500</v>
       </c>
       <c r="R74" t="n">
-        <v>7152564</v>
+        <v>7152466</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8417,6 +8441,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8435,10 +8460,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120086276</v>
+        <v>120080342</v>
       </c>
       <c r="B75" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8447,25 +8472,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8475,10 +8500,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>746304</v>
+        <v>746478</v>
       </c>
       <c r="R75" t="n">
-        <v>7152657</v>
+        <v>7152487</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8525,22 +8550,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120079812</v>
+        <v>120086246</v>
       </c>
       <c r="B76" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8549,25 +8574,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8577,13 +8602,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>746540</v>
+        <v>746475</v>
       </c>
       <c r="R76" t="n">
-        <v>7152434</v>
+        <v>7152487</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8621,29 +8646,28 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120086265</v>
+        <v>120094951</v>
       </c>
       <c r="B77" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8652,38 +8676,41 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>746353</v>
+        <v>746357</v>
       </c>
       <c r="R77" t="n">
-        <v>7152592</v>
+        <v>7152686</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8724,6 +8751,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8742,7 +8770,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120080341</v>
+        <v>120086296</v>
       </c>
       <c r="B78" t="n">
         <v>91858</v>
@@ -8782,10 +8810,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>746384</v>
+        <v>746425</v>
       </c>
       <c r="R78" t="n">
-        <v>7152544</v>
+        <v>7152621</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8832,19 +8860,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120086295</v>
+        <v>120086298</v>
       </c>
       <c r="B79" t="n">
         <v>91858</v>
@@ -8884,10 +8912,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>746365</v>
+        <v>746527</v>
       </c>
       <c r="R79" t="n">
-        <v>7152695</v>
+        <v>7152434</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8946,10 +8974,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120094849</v>
+        <v>120086269</v>
       </c>
       <c r="B80" t="n">
-        <v>91858</v>
+        <v>88170</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8958,25 +8986,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8989,10 +9017,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>746531</v>
+        <v>746365</v>
       </c>
       <c r="R80" t="n">
-        <v>7152454</v>
+        <v>7152575</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9025,6 +9053,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Inte ihålig men övriga karaktärer stämde.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9052,7 +9085,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120094922</v>
+        <v>120080307</v>
       </c>
       <c r="B81" t="n">
         <v>91902</v>
@@ -9086,19 +9119,16 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>746442</v>
+        <v>746426</v>
       </c>
       <c r="R81" t="n">
-        <v>7152565</v>
+        <v>7152510</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9139,29 +9169,28 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120080319</v>
+        <v>120079797</v>
       </c>
       <c r="B82" t="n">
-        <v>92048</v>
+        <v>89650</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9174,21 +9203,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9198,13 +9227,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>746477</v>
+        <v>746432</v>
       </c>
       <c r="R82" t="n">
-        <v>7152502</v>
+        <v>7152509</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9236,11 +9265,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På kolad tallstubbe</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9249,43 +9273,23 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL82" t="inlineStr">
-        <is>
-          <t>Kolad tallstubbe</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Kolad tallstubbe</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120094932</v>
+        <v>120094901</v>
       </c>
       <c r="B83" t="n">
         <v>91858</v>
@@ -9328,10 +9332,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>746414</v>
+        <v>746487</v>
       </c>
       <c r="R83" t="n">
-        <v>7152584</v>
+        <v>7152494</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9391,10 +9395,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120086274</v>
+        <v>120086259</v>
       </c>
       <c r="B84" t="n">
-        <v>78542</v>
+        <v>91850</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9407,21 +9411,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9431,10 +9435,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>746478</v>
+        <v>746394</v>
       </c>
       <c r="R84" t="n">
-        <v>7152496</v>
+        <v>7152581</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9493,10 +9497,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120094945</v>
+        <v>120086278</v>
       </c>
       <c r="B85" t="n">
-        <v>91902</v>
+        <v>78542</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9509,37 +9513,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>746417</v>
+        <v>746365</v>
       </c>
       <c r="R85" t="n">
-        <v>7152628</v>
+        <v>7152695</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9580,7 +9581,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41672-2024 artfynd.xlsx
+++ b/artfynd/A 41672-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120067137</v>
+        <v>120069457</v>
       </c>
       <c r="B2" t="n">
-        <v>91852</v>
+        <v>91874</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>746520</v>
+        <v>746379</v>
       </c>
       <c r="R2" t="n">
-        <v>7152487</v>
+        <v>7152575</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120068331</v>
+        <v>120067137</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>746318</v>
+        <v>746520</v>
       </c>
       <c r="R3" t="n">
-        <v>7152701</v>
+        <v>7152487</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120069457</v>
+        <v>120068331</v>
       </c>
       <c r="B4" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>746379</v>
+        <v>746318</v>
       </c>
       <c r="R4" t="n">
-        <v>7152575</v>
+        <v>7152701</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2579,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120068346</v>
+        <v>120067935</v>
       </c>
       <c r="B19" t="n">
-        <v>91870</v>
+        <v>91858</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2595,21 +2595,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>746324</v>
+        <v>746381</v>
       </c>
       <c r="R19" t="n">
-        <v>7152703</v>
+        <v>7152596</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120067935</v>
+        <v>120068346</v>
       </c>
       <c r="B20" t="n">
-        <v>91858</v>
+        <v>91870</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2707,21 +2707,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>746381</v>
+        <v>746324</v>
       </c>
       <c r="R20" t="n">
-        <v>7152596</v>
+        <v>7152703</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -4191,10 +4191,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120086238</v>
+        <v>120086230</v>
       </c>
       <c r="B34" t="n">
-        <v>57473</v>
+        <v>90545</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4203,46 +4203,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>746509</v>
+        <v>746412</v>
       </c>
       <c r="R34" t="n">
-        <v>7152434</v>
+        <v>7152564</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4275,11 +4267,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Två</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4306,10 +4293,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120086230</v>
+        <v>120086238</v>
       </c>
       <c r="B35" t="n">
-        <v>90545</v>
+        <v>57473</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4318,38 +4305,46 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>746412</v>
+        <v>746509</v>
       </c>
       <c r="R35" t="n">
-        <v>7152564</v>
+        <v>7152434</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4382,6 +4377,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Två</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4408,10 +4408,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120094922</v>
+        <v>120086263</v>
       </c>
       <c r="B36" t="n">
-        <v>91902</v>
+        <v>92048</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4424,37 +4424,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5449</v>
+        <v>2079</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>746442</v>
+        <v>746450</v>
       </c>
       <c r="R36" t="n">
-        <v>7152565</v>
+        <v>7152549</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4495,7 +4492,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4514,7 +4510,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120079802</v>
+        <v>120094922</v>
       </c>
       <c r="B37" t="n">
         <v>91902</v>
@@ -4548,19 +4544,22 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>746495</v>
+        <v>746442</v>
       </c>
       <c r="R37" t="n">
-        <v>7152470</v>
+        <v>7152565</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4598,28 +4597,29 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120086263</v>
+        <v>120079802</v>
       </c>
       <c r="B38" t="n">
-        <v>92048</v>
+        <v>91902</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4632,21 +4632,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2079</v>
+        <v>5449</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>746450</v>
+        <v>746495</v>
       </c>
       <c r="R38" t="n">
-        <v>7152549</v>
+        <v>7152470</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4706,12 +4706,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5232,10 +5232,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120094907</v>
+        <v>120086266</v>
       </c>
       <c r="B44" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5244,41 +5244,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>746484</v>
+        <v>746429</v>
       </c>
       <c r="R44" t="n">
-        <v>7152510</v>
+        <v>7152625</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5319,7 +5316,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5338,10 +5334,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120086266</v>
+        <v>120094907</v>
       </c>
       <c r="B45" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5350,38 +5346,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>746429</v>
+        <v>746484</v>
       </c>
       <c r="R45" t="n">
-        <v>7152625</v>
+        <v>7152510</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5422,6 +5421,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5750,10 +5750,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120086228</v>
+        <v>120080326</v>
       </c>
       <c r="B49" t="n">
-        <v>74654</v>
+        <v>89247</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5762,25 +5762,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>1596</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5790,10 +5790,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>746357</v>
+        <v>746543</v>
       </c>
       <c r="R49" t="n">
-        <v>7152581</v>
+        <v>7152437</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5840,22 +5840,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120080346</v>
+        <v>120086228</v>
       </c>
       <c r="B50" t="n">
-        <v>91858</v>
+        <v>74654</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5864,25 +5864,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5892,10 +5892,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>746461</v>
+        <v>746357</v>
       </c>
       <c r="R50" t="n">
-        <v>7152458</v>
+        <v>7152581</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5942,19 +5942,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120079812</v>
+        <v>120080346</v>
       </c>
       <c r="B51" t="n">
         <v>91858</v>
@@ -5994,13 +5994,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>746540</v>
+        <v>746461</v>
       </c>
       <c r="R51" t="n">
-        <v>7152434</v>
+        <v>7152458</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6038,29 +6038,28 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120080326</v>
+        <v>120079812</v>
       </c>
       <c r="B52" t="n">
-        <v>89247</v>
+        <v>91858</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6069,25 +6068,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1596</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6097,13 +6096,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>746543</v>
+        <v>746540</v>
       </c>
       <c r="R52" t="n">
-        <v>7152437</v>
+        <v>7152434</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6141,18 +6140,19 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6465,10 +6465,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120080319</v>
+        <v>120079809</v>
       </c>
       <c r="B56" t="n">
-        <v>92048</v>
+        <v>90730</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6477,41 +6477,44 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>746477</v>
+        <v>746368</v>
       </c>
       <c r="R56" t="n">
-        <v>7152502</v>
+        <v>7152599</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6543,59 +6546,35 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>På kolad tallstubbe</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL56" t="inlineStr">
-        <is>
-          <t>Kolad tallstubbe</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Kolad tallstubbe</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120094849</v>
+        <v>120080319</v>
       </c>
       <c r="B57" t="n">
-        <v>91858</v>
+        <v>92048</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6604,41 +6583,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>746531</v>
+        <v>746477</v>
       </c>
       <c r="R57" t="n">
-        <v>7152454</v>
+        <v>7152502</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6673,35 +6649,59 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På kolad tallstubbe</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>Kolad tallstubbe</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Kolad tallstubbe</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120079809</v>
+        <v>120094849</v>
       </c>
       <c r="B58" t="n">
-        <v>90730</v>
+        <v>91858</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6710,25 +6710,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6741,13 +6741,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>746368</v>
+        <v>746531</v>
       </c>
       <c r="R58" t="n">
-        <v>7152599</v>
+        <v>7152454</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6792,12 +6792,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7640,10 +7640,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120080341</v>
+        <v>120086274</v>
       </c>
       <c r="B67" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7652,25 +7652,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7680,10 +7680,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>746384</v>
+        <v>746478</v>
       </c>
       <c r="R67" t="n">
-        <v>7152544</v>
+        <v>7152496</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7730,19 +7730,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120080348</v>
+        <v>120080341</v>
       </c>
       <c r="B68" t="n">
         <v>91858</v>
@@ -7782,10 +7782,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>746505</v>
+        <v>746384</v>
       </c>
       <c r="R68" t="n">
-        <v>7152451</v>
+        <v>7152544</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7844,7 +7844,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120080338</v>
+        <v>120080348</v>
       </c>
       <c r="B69" t="n">
         <v>91858</v>
@@ -7884,10 +7884,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>746455</v>
+        <v>746505</v>
       </c>
       <c r="R69" t="n">
-        <v>7152561</v>
+        <v>7152451</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7946,7 +7946,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120080337</v>
+        <v>120080338</v>
       </c>
       <c r="B70" t="n">
         <v>91858</v>
@@ -7986,10 +7986,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>746488</v>
+        <v>746455</v>
       </c>
       <c r="R70" t="n">
-        <v>7152500</v>
+        <v>7152561</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8048,10 +8048,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120086274</v>
+        <v>120080337</v>
       </c>
       <c r="B71" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8060,25 +8060,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8088,10 +8088,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>746478</v>
+        <v>746488</v>
       </c>
       <c r="R71" t="n">
-        <v>7152496</v>
+        <v>7152500</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8138,12 +8138,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 41672-2024 artfynd.xlsx
+++ b/artfynd/A 41672-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120069457</v>
+        <v>120068255</v>
       </c>
       <c r="B2" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>746379</v>
+        <v>746352</v>
       </c>
       <c r="R2" t="n">
-        <v>7152575</v>
+        <v>7152686</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120067137</v>
+        <v>120067430</v>
       </c>
       <c r="B3" t="n">
-        <v>91852</v>
+        <v>91874</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>746520</v>
+        <v>746505</v>
       </c>
       <c r="R3" t="n">
-        <v>7152487</v>
+        <v>7152499</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120068331</v>
+        <v>120066896</v>
       </c>
       <c r="B4" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>746318</v>
+        <v>746537</v>
       </c>
       <c r="R4" t="n">
-        <v>7152701</v>
+        <v>7152456</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120068080</v>
+        <v>120068602</v>
       </c>
       <c r="B5" t="n">
-        <v>91858</v>
+        <v>79652</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>746371</v>
+        <v>746307</v>
       </c>
       <c r="R5" t="n">
-        <v>7152632</v>
+        <v>7152647</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120069348</v>
+        <v>120067935</v>
       </c>
       <c r="B6" t="n">
         <v>91858</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>746382</v>
+        <v>746381</v>
       </c>
       <c r="R6" t="n">
-        <v>7152570</v>
+        <v>7152596</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120069608</v>
+        <v>120069348</v>
       </c>
       <c r="B8" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>746422</v>
+        <v>746382</v>
       </c>
       <c r="R8" t="n">
-        <v>7152546</v>
+        <v>7152570</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120067979</v>
+        <v>120067885</v>
       </c>
       <c r="B10" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,25 +1583,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>746392</v>
+        <v>746399</v>
       </c>
       <c r="R10" t="n">
-        <v>7152615</v>
+        <v>7152617</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120068133</v>
+        <v>120067504</v>
       </c>
       <c r="B11" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,25 +1695,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>746333</v>
+        <v>746486</v>
       </c>
       <c r="R11" t="n">
-        <v>7152647</v>
+        <v>7152501</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120067504</v>
+        <v>120068346</v>
       </c>
       <c r="B12" t="n">
-        <v>91874</v>
+        <v>91870</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,25 +1807,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>746486</v>
+        <v>746324</v>
       </c>
       <c r="R12" t="n">
-        <v>7152501</v>
+        <v>7152703</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120068300</v>
+        <v>120068383</v>
       </c>
       <c r="B13" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,25 +1919,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>746336</v>
+        <v>746313</v>
       </c>
       <c r="R13" t="n">
-        <v>7152676</v>
+        <v>7152706</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120068602</v>
+        <v>120068080</v>
       </c>
       <c r="B14" t="n">
-        <v>79652</v>
+        <v>91858</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>746307</v>
+        <v>746371</v>
       </c>
       <c r="R14" t="n">
-        <v>7152647</v>
+        <v>7152632</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120068365</v>
+        <v>120067137</v>
       </c>
       <c r="B15" t="n">
-        <v>91902</v>
+        <v>91852</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,21 +2147,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>746323</v>
+        <v>746520</v>
       </c>
       <c r="R15" t="n">
-        <v>7152700</v>
+        <v>7152487</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120067430</v>
+        <v>120067568</v>
       </c>
       <c r="B16" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2255,25 +2255,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>746505</v>
+        <v>746484</v>
       </c>
       <c r="R16" t="n">
-        <v>7152499</v>
+        <v>7152500</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120066631</v>
+        <v>120068300</v>
       </c>
       <c r="B17" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2367,25 +2367,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>746551</v>
+        <v>746336</v>
       </c>
       <c r="R17" t="n">
-        <v>7152434</v>
+        <v>7152676</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120066896</v>
+        <v>120067979</v>
       </c>
       <c r="B18" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2479,25 +2479,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>746537</v>
+        <v>746392</v>
       </c>
       <c r="R18" t="n">
-        <v>7152456</v>
+        <v>7152615</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,7 +2579,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120067935</v>
+        <v>120068133</v>
       </c>
       <c r="B19" t="n">
         <v>91858</v>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>746381</v>
+        <v>746333</v>
       </c>
       <c r="R19" t="n">
-        <v>7152596</v>
+        <v>7152647</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120068346</v>
+        <v>120066631</v>
       </c>
       <c r="B20" t="n">
-        <v>91870</v>
+        <v>91858</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2707,21 +2707,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>746324</v>
+        <v>746551</v>
       </c>
       <c r="R20" t="n">
-        <v>7152703</v>
+        <v>7152434</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120067262</v>
+        <v>120069608</v>
       </c>
       <c r="B21" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2815,25 +2815,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>746520</v>
+        <v>746422</v>
       </c>
       <c r="R21" t="n">
-        <v>7152494</v>
+        <v>7152546</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120067568</v>
+        <v>120069457</v>
       </c>
       <c r="B22" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2927,25 +2927,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>746484</v>
+        <v>746379</v>
       </c>
       <c r="R22" t="n">
-        <v>7152500</v>
+        <v>7152575</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,10 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120067885</v>
+        <v>120067262</v>
       </c>
       <c r="B23" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3039,25 +3039,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>746399</v>
+        <v>746520</v>
       </c>
       <c r="R23" t="n">
-        <v>7152617</v>
+        <v>7152494</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,7 +3139,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120068255</v>
+        <v>120068331</v>
       </c>
       <c r="B24" t="n">
         <v>91858</v>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>746352</v>
+        <v>746318</v>
       </c>
       <c r="R24" t="n">
-        <v>7152686</v>
+        <v>7152701</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3251,10 +3251,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120068383</v>
+        <v>120068365</v>
       </c>
       <c r="B25" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3263,25 +3263,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>746313</v>
+        <v>746323</v>
       </c>
       <c r="R25" t="n">
-        <v>7152706</v>
+        <v>7152700</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3363,7 +3363,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120094932</v>
+        <v>120080342</v>
       </c>
       <c r="B26" t="n">
         <v>91858</v>
@@ -3397,19 +3397,16 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>746414</v>
+        <v>746478</v>
       </c>
       <c r="R26" t="n">
-        <v>7152584</v>
+        <v>7152487</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3450,29 +3447,28 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120086297</v>
+        <v>120086265</v>
       </c>
       <c r="B27" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3481,25 +3477,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3509,10 +3505,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>746473</v>
+        <v>746353</v>
       </c>
       <c r="R27" t="n">
-        <v>7152499</v>
+        <v>7152592</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3571,10 +3567,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120086291</v>
+        <v>120080345</v>
       </c>
       <c r="B28" t="n">
-        <v>90825</v>
+        <v>91858</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3583,25 +3579,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3611,10 +3607,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>746502</v>
+        <v>746459</v>
       </c>
       <c r="R28" t="n">
-        <v>7152478</v>
+        <v>7152465</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3661,22 +3657,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120086279</v>
+        <v>120080326</v>
       </c>
       <c r="B29" t="n">
-        <v>78542</v>
+        <v>89247</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3685,25 +3681,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1596</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3713,10 +3709,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>746397</v>
+        <v>746543</v>
       </c>
       <c r="R29" t="n">
-        <v>7152654</v>
+        <v>7152437</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3763,22 +3759,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120080306</v>
+        <v>120080349</v>
       </c>
       <c r="B30" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3787,25 +3783,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3815,10 +3811,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>746490</v>
+        <v>746540</v>
       </c>
       <c r="R30" t="n">
-        <v>7152502</v>
+        <v>7152444</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3877,10 +3873,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120080295</v>
+        <v>120086296</v>
       </c>
       <c r="B31" t="n">
-        <v>57473</v>
+        <v>91858</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3889,46 +3885,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>746385</v>
+        <v>746425</v>
       </c>
       <c r="R31" t="n">
-        <v>7152570</v>
+        <v>7152621</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3975,19 +3963,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120079813</v>
+        <v>120086294</v>
       </c>
       <c r="B32" t="n">
         <v>91858</v>
@@ -4027,13 +4015,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>746517</v>
+        <v>746310</v>
       </c>
       <c r="R32" t="n">
-        <v>7152485</v>
+        <v>7152670</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4077,12 +4065,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4191,10 +4179,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120086230</v>
+        <v>120086276</v>
       </c>
       <c r="B34" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4203,25 +4191,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4231,10 +4219,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>746412</v>
+        <v>746304</v>
       </c>
       <c r="R34" t="n">
-        <v>7152564</v>
+        <v>7152657</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4293,10 +4281,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120086238</v>
+        <v>120086266</v>
       </c>
       <c r="B35" t="n">
-        <v>57473</v>
+        <v>91881</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4309,42 +4297,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>746509</v>
+        <v>746429</v>
       </c>
       <c r="R35" t="n">
-        <v>7152434</v>
+        <v>7152625</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4377,11 +4357,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Två</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4408,10 +4383,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120086263</v>
+        <v>120086269</v>
       </c>
       <c r="B36" t="n">
-        <v>92048</v>
+        <v>88170</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4424,34 +4399,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2079</v>
+        <v>4962</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>746450</v>
+        <v>746365</v>
       </c>
       <c r="R36" t="n">
-        <v>7152549</v>
+        <v>7152575</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4486,12 +4464,18 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Inte ihålig men övriga karaktärer stämde.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4510,10 +4494,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120094922</v>
+        <v>120080295</v>
       </c>
       <c r="B37" t="n">
-        <v>91902</v>
+        <v>57473</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4526,26 +4510,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4553,10 +4542,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>746442</v>
+        <v>746385</v>
       </c>
       <c r="R37" t="n">
-        <v>7152565</v>
+        <v>7152570</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4597,29 +4586,28 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120079802</v>
+        <v>120094886</v>
       </c>
       <c r="B38" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4628,41 +4616,44 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>746495</v>
+        <v>746500</v>
       </c>
       <c r="R38" t="n">
-        <v>7152470</v>
+        <v>7152466</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4700,28 +4691,29 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120086245</v>
+        <v>120080346</v>
       </c>
       <c r="B39" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4730,25 +4722,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4758,10 +4750,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>746365</v>
+        <v>746461</v>
       </c>
       <c r="R39" t="n">
-        <v>7152575</v>
+        <v>7152458</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4808,22 +4800,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120080345</v>
+        <v>120094922</v>
       </c>
       <c r="B40" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4832,38 +4824,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>746459</v>
+        <v>746442</v>
       </c>
       <c r="R40" t="n">
-        <v>7152465</v>
+        <v>7152565</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4904,28 +4899,29 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120086294</v>
+        <v>120079802</v>
       </c>
       <c r="B41" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4934,25 +4930,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4962,13 +4958,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>746310</v>
+        <v>746495</v>
       </c>
       <c r="R41" t="n">
-        <v>7152670</v>
+        <v>7152470</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5012,19 +5008,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120094897</v>
+        <v>120094939</v>
       </c>
       <c r="B42" t="n">
         <v>91858</v>
@@ -5067,10 +5063,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>746482</v>
+        <v>746413</v>
       </c>
       <c r="R42" t="n">
-        <v>7152467</v>
+        <v>7152616</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5130,10 +5126,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120086265</v>
+        <v>120086272</v>
       </c>
       <c r="B43" t="n">
-        <v>78279</v>
+        <v>74640</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5142,25 +5138,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5170,10 +5166,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>746353</v>
+        <v>746357</v>
       </c>
       <c r="R43" t="n">
-        <v>7152592</v>
+        <v>7152581</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5232,10 +5228,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120086266</v>
+        <v>120079805</v>
       </c>
       <c r="B44" t="n">
-        <v>91881</v>
+        <v>92048</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5248,21 +5244,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5966</v>
+        <v>2079</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5272,13 +5268,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>746429</v>
+        <v>746437</v>
       </c>
       <c r="R44" t="n">
-        <v>7152625</v>
+        <v>7152508</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5322,22 +5318,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120094907</v>
+        <v>120086275</v>
       </c>
       <c r="B45" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5346,41 +5342,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>746484</v>
+        <v>746370</v>
       </c>
       <c r="R45" t="n">
-        <v>7152510</v>
+        <v>7152601</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5421,7 +5414,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5440,7 +5432,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120086295</v>
+        <v>120079813</v>
       </c>
       <c r="B46" t="n">
         <v>91858</v>
@@ -5480,13 +5472,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>746365</v>
+        <v>746517</v>
       </c>
       <c r="R46" t="n">
-        <v>7152695</v>
+        <v>7152485</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5530,22 +5522,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120094916</v>
+        <v>120094959</v>
       </c>
       <c r="B47" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5554,25 +5546,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5585,10 +5577,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>746490</v>
+        <v>746300</v>
       </c>
       <c r="R47" t="n">
-        <v>7152513</v>
+        <v>7152654</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5648,10 +5640,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120079805</v>
+        <v>120080340</v>
       </c>
       <c r="B48" t="n">
-        <v>92048</v>
+        <v>91858</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5660,25 +5652,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5688,13 +5680,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>746437</v>
+        <v>746398</v>
       </c>
       <c r="R48" t="n">
-        <v>7152508</v>
+        <v>7152548</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5738,22 +5730,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120080326</v>
+        <v>120079812</v>
       </c>
       <c r="B49" t="n">
-        <v>89247</v>
+        <v>91858</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5762,25 +5754,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1596</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5790,13 +5782,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>746543</v>
+        <v>746540</v>
       </c>
       <c r="R49" t="n">
-        <v>7152437</v>
+        <v>7152434</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5834,28 +5826,29 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120086228</v>
+        <v>120079797</v>
       </c>
       <c r="B50" t="n">
-        <v>74654</v>
+        <v>89650</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5868,21 +5861,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>1962</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5892,13 +5885,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>746357</v>
+        <v>746432</v>
       </c>
       <c r="R50" t="n">
-        <v>7152581</v>
+        <v>7152509</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5942,22 +5935,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120080346</v>
+        <v>120086246</v>
       </c>
       <c r="B51" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5966,25 +5959,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5994,10 +5987,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>746461</v>
+        <v>746475</v>
       </c>
       <c r="R51" t="n">
-        <v>7152458</v>
+        <v>7152487</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6044,22 +6037,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120079812</v>
+        <v>120094945</v>
       </c>
       <c r="B52" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6068,41 +6061,44 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>746540</v>
+        <v>746417</v>
       </c>
       <c r="R52" t="n">
-        <v>7152434</v>
+        <v>7152628</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6147,22 +6143,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120080336</v>
+        <v>120080307</v>
       </c>
       <c r="B53" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6171,25 +6167,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6199,10 +6195,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>746545</v>
+        <v>746426</v>
       </c>
       <c r="R53" t="n">
-        <v>7152464</v>
+        <v>7152510</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6261,10 +6257,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120086275</v>
+        <v>120086295</v>
       </c>
       <c r="B54" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6273,25 +6269,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6301,10 +6297,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>746370</v>
+        <v>746365</v>
       </c>
       <c r="R54" t="n">
-        <v>7152601</v>
+        <v>7152695</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6363,10 +6359,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120086276</v>
+        <v>120094897</v>
       </c>
       <c r="B55" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6375,38 +6371,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>746304</v>
+        <v>746482</v>
       </c>
       <c r="R55" t="n">
-        <v>7152657</v>
+        <v>7152467</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6447,6 +6446,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6465,10 +6465,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120079809</v>
+        <v>120080319</v>
       </c>
       <c r="B56" t="n">
-        <v>90730</v>
+        <v>92048</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6477,44 +6477,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>746368</v>
+        <v>746477</v>
       </c>
       <c r="R56" t="n">
-        <v>7152599</v>
+        <v>7152502</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6546,35 +6543,59 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På kolad tallstubbe</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL56" t="inlineStr">
+        <is>
+          <t>Kolad tallstubbe</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Kolad tallstubbe</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120080319</v>
+        <v>120086245</v>
       </c>
       <c r="B57" t="n">
-        <v>92048</v>
+        <v>91902</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6587,21 +6608,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2079</v>
+        <v>5449</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6611,10 +6632,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>746477</v>
+        <v>746365</v>
       </c>
       <c r="R57" t="n">
-        <v>7152502</v>
+        <v>7152575</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6649,11 +6670,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På kolad tallstubbe</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6662,43 +6678,23 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL57" t="inlineStr">
-        <is>
-          <t>Kolad tallstubbe</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Kolad tallstubbe</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120094849</v>
+        <v>120080337</v>
       </c>
       <c r="B58" t="n">
         <v>91858</v>
@@ -6732,19 +6728,16 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>746531</v>
+        <v>746488</v>
       </c>
       <c r="R58" t="n">
-        <v>7152454</v>
+        <v>7152500</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6785,29 +6778,28 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120094959</v>
+        <v>120086274</v>
       </c>
       <c r="B59" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6816,41 +6808,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>746300</v>
+        <v>746478</v>
       </c>
       <c r="R59" t="n">
-        <v>7152654</v>
+        <v>7152496</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6891,7 +6880,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6910,10 +6898,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120080340</v>
+        <v>120086230</v>
       </c>
       <c r="B60" t="n">
-        <v>91858</v>
+        <v>90545</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6926,21 +6914,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6950,10 +6938,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>746398</v>
+        <v>746412</v>
       </c>
       <c r="R60" t="n">
-        <v>7152548</v>
+        <v>7152564</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7000,22 +6988,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120094869</v>
+        <v>120086238</v>
       </c>
       <c r="B61" t="n">
-        <v>91858</v>
+        <v>57473</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7024,30 +7012,35 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7055,10 +7048,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>746522</v>
+        <v>746509</v>
       </c>
       <c r="R61" t="n">
-        <v>7152453</v>
+        <v>7152434</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7093,13 +7086,17 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Två</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7118,10 +7115,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120094945</v>
+        <v>120086291</v>
       </c>
       <c r="B62" t="n">
-        <v>91902</v>
+        <v>90825</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7130,41 +7127,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5449</v>
+        <v>65</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>746417</v>
+        <v>746502</v>
       </c>
       <c r="R62" t="n">
-        <v>7152628</v>
+        <v>7152478</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7205,7 +7199,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7224,10 +7217,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120086277</v>
+        <v>120086263</v>
       </c>
       <c r="B63" t="n">
-        <v>78542</v>
+        <v>92048</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7240,21 +7233,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7264,10 +7257,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>746302</v>
+        <v>746450</v>
       </c>
       <c r="R63" t="n">
-        <v>7152670</v>
+        <v>7152549</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7326,10 +7319,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120080349</v>
+        <v>120086280</v>
       </c>
       <c r="B64" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7338,25 +7331,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7366,10 +7359,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>746540</v>
+        <v>746527</v>
       </c>
       <c r="R64" t="n">
-        <v>7152444</v>
+        <v>7152434</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7416,22 +7409,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120094855</v>
+        <v>120086279</v>
       </c>
       <c r="B65" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7440,41 +7433,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>746547</v>
+        <v>746397</v>
       </c>
       <c r="R65" t="n">
-        <v>7152471</v>
+        <v>7152654</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7515,7 +7505,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7534,7 +7523,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120094939</v>
+        <v>120080338</v>
       </c>
       <c r="B66" t="n">
         <v>91858</v>
@@ -7568,19 +7557,16 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>746413</v>
+        <v>746455</v>
       </c>
       <c r="R66" t="n">
-        <v>7152616</v>
+        <v>7152561</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7621,29 +7607,28 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120086274</v>
+        <v>120094907</v>
       </c>
       <c r="B67" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7652,38 +7637,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>746478</v>
+        <v>746484</v>
       </c>
       <c r="R67" t="n">
-        <v>7152496</v>
+        <v>7152510</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7724,6 +7712,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7742,7 +7731,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120080341</v>
+        <v>120086298</v>
       </c>
       <c r="B68" t="n">
         <v>91858</v>
@@ -7782,10 +7771,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>746384</v>
+        <v>746527</v>
       </c>
       <c r="R68" t="n">
-        <v>7152544</v>
+        <v>7152434</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7832,22 +7821,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120080348</v>
+        <v>120086259</v>
       </c>
       <c r="B69" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7856,25 +7845,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7884,10 +7873,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>746505</v>
+        <v>746394</v>
       </c>
       <c r="R69" t="n">
-        <v>7152451</v>
+        <v>7152581</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7934,19 +7923,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120080338</v>
+        <v>120080336</v>
       </c>
       <c r="B70" t="n">
         <v>91858</v>
@@ -7986,10 +7975,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>746455</v>
+        <v>746545</v>
       </c>
       <c r="R70" t="n">
-        <v>7152561</v>
+        <v>7152464</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8048,7 +8037,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120080337</v>
+        <v>120094849</v>
       </c>
       <c r="B71" t="n">
         <v>91858</v>
@@ -8082,16 +8071,19 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>746488</v>
+        <v>746531</v>
       </c>
       <c r="R71" t="n">
-        <v>7152500</v>
+        <v>7152454</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8132,28 +8124,29 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120086280</v>
+        <v>120086297</v>
       </c>
       <c r="B72" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8162,25 +8155,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8190,10 +8183,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>746527</v>
+        <v>746473</v>
       </c>
       <c r="R72" t="n">
-        <v>7152434</v>
+        <v>7152499</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8252,10 +8245,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120086272</v>
+        <v>120086228</v>
       </c>
       <c r="B73" t="n">
-        <v>74640</v>
+        <v>74654</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8264,25 +8257,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>306</v>
+        <v>6440</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8354,7 +8347,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120094886</v>
+        <v>120080348</v>
       </c>
       <c r="B74" t="n">
         <v>91858</v>
@@ -8388,19 +8381,16 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>746500</v>
+        <v>746505</v>
       </c>
       <c r="R74" t="n">
-        <v>7152466</v>
+        <v>7152451</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8441,29 +8431,28 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120080342</v>
+        <v>120094916</v>
       </c>
       <c r="B75" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8472,38 +8461,41 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>746478</v>
+        <v>746490</v>
       </c>
       <c r="R75" t="n">
-        <v>7152487</v>
+        <v>7152513</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8544,28 +8536,29 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120086246</v>
+        <v>120094869</v>
       </c>
       <c r="B76" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8574,38 +8567,41 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>746475</v>
+        <v>746522</v>
       </c>
       <c r="R76" t="n">
-        <v>7152487</v>
+        <v>7152453</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8646,6 +8642,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8664,7 +8661,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120094951</v>
+        <v>120094855</v>
       </c>
       <c r="B77" t="n">
         <v>91858</v>
@@ -8707,10 +8704,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>746357</v>
+        <v>746547</v>
       </c>
       <c r="R77" t="n">
-        <v>7152686</v>
+        <v>7152471</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8770,7 +8767,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120086296</v>
+        <v>120080341</v>
       </c>
       <c r="B78" t="n">
         <v>91858</v>
@@ -8810,10 +8807,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>746425</v>
+        <v>746384</v>
       </c>
       <c r="R78" t="n">
-        <v>7152621</v>
+        <v>7152544</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8860,19 +8857,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120086298</v>
+        <v>120094932</v>
       </c>
       <c r="B79" t="n">
         <v>91858</v>
@@ -8906,16 +8903,19 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>746527</v>
+        <v>746414</v>
       </c>
       <c r="R79" t="n">
-        <v>7152434</v>
+        <v>7152584</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8956,6 +8956,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8974,10 +8975,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120086269</v>
+        <v>120086277</v>
       </c>
       <c r="B80" t="n">
-        <v>88170</v>
+        <v>78542</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8990,37 +8991,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4962</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>746365</v>
+        <v>746302</v>
       </c>
       <c r="R80" t="n">
-        <v>7152575</v>
+        <v>7152670</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9055,18 +9053,12 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Inte ihålig men övriga karaktärer stämde.</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -9085,10 +9077,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120080307</v>
+        <v>120086278</v>
       </c>
       <c r="B81" t="n">
-        <v>91902</v>
+        <v>78542</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9101,21 +9093,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9125,10 +9117,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>746426</v>
+        <v>746365</v>
       </c>
       <c r="R81" t="n">
-        <v>7152510</v>
+        <v>7152695</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9175,22 +9167,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120079797</v>
+        <v>120079809</v>
       </c>
       <c r="B82" t="n">
-        <v>89650</v>
+        <v>90730</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9199,38 +9191,41 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1962</v>
+        <v>1503</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>746432</v>
+        <v>746368</v>
       </c>
       <c r="R82" t="n">
-        <v>7152509</v>
+        <v>7152599</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9271,6 +9266,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9289,10 +9285,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120094901</v>
+        <v>120080306</v>
       </c>
       <c r="B83" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9301,41 +9297,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>746487</v>
+        <v>746490</v>
       </c>
       <c r="R83" t="n">
-        <v>7152494</v>
+        <v>7152502</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9376,29 +9369,28 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120086259</v>
+        <v>120094901</v>
       </c>
       <c r="B84" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9407,38 +9399,41 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>746394</v>
+        <v>746487</v>
       </c>
       <c r="R84" t="n">
-        <v>7152581</v>
+        <v>7152494</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9479,6 +9474,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9497,10 +9493,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120086278</v>
+        <v>120094951</v>
       </c>
       <c r="B85" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9509,38 +9505,41 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>746365</v>
+        <v>746357</v>
       </c>
       <c r="R85" t="n">
-        <v>7152695</v>
+        <v>7152686</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9581,6 +9580,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41672-2024 artfynd.xlsx
+++ b/artfynd/A 41672-2024 artfynd.xlsx
@@ -5020,10 +5020,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120094939</v>
+        <v>120086272</v>
       </c>
       <c r="B42" t="n">
-        <v>91858</v>
+        <v>74640</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5036,37 +5036,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>746413</v>
+        <v>746357</v>
       </c>
       <c r="R42" t="n">
-        <v>7152616</v>
+        <v>7152581</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5107,7 +5104,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5126,10 +5122,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120086272</v>
+        <v>120079805</v>
       </c>
       <c r="B43" t="n">
-        <v>74640</v>
+        <v>92048</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5138,25 +5134,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>306</v>
+        <v>2079</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5166,13 +5162,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>746357</v>
+        <v>746437</v>
       </c>
       <c r="R43" t="n">
-        <v>7152581</v>
+        <v>7152508</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5216,22 +5212,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120079805</v>
+        <v>120086275</v>
       </c>
       <c r="B44" t="n">
-        <v>92048</v>
+        <v>78542</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5244,21 +5240,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5268,13 +5264,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>746437</v>
+        <v>746370</v>
       </c>
       <c r="R44" t="n">
-        <v>7152508</v>
+        <v>7152601</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5318,22 +5314,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120086275</v>
+        <v>120094939</v>
       </c>
       <c r="B45" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5342,38 +5338,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>746370</v>
+        <v>746413</v>
       </c>
       <c r="R45" t="n">
-        <v>7152601</v>
+        <v>7152616</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5414,6 +5413,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6257,7 +6257,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120086295</v>
+        <v>120094897</v>
       </c>
       <c r="B54" t="n">
         <v>91858</v>
@@ -6291,16 +6291,19 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>746365</v>
+        <v>746482</v>
       </c>
       <c r="R54" t="n">
-        <v>7152695</v>
+        <v>7152467</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6341,6 +6344,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6359,10 +6363,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120094897</v>
+        <v>120080319</v>
       </c>
       <c r="B55" t="n">
-        <v>91858</v>
+        <v>92048</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6371,41 +6375,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>746482</v>
+        <v>746477</v>
       </c>
       <c r="R55" t="n">
-        <v>7152467</v>
+        <v>7152502</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6440,35 +6441,59 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På kolad tallstubbe</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL55" t="inlineStr">
+        <is>
+          <t>Kolad tallstubbe</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Kolad tallstubbe</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120080319</v>
+        <v>120086245</v>
       </c>
       <c r="B56" t="n">
-        <v>92048</v>
+        <v>91902</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6481,21 +6506,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2079</v>
+        <v>5449</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6505,10 +6530,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>746477</v>
+        <v>746365</v>
       </c>
       <c r="R56" t="n">
-        <v>7152502</v>
+        <v>7152575</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6543,11 +6568,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>På kolad tallstubbe</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6556,46 +6576,26 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL56" t="inlineStr">
-        <is>
-          <t>Kolad tallstubbe</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Kolad tallstubbe</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120086245</v>
+        <v>120086295</v>
       </c>
       <c r="B57" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6604,25 +6604,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6635,7 +6635,7 @@
         <v>746365</v>
       </c>
       <c r="R57" t="n">
-        <v>7152575</v>
+        <v>7152695</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7115,10 +7115,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120086291</v>
+        <v>120086280</v>
       </c>
       <c r="B62" t="n">
-        <v>90825</v>
+        <v>78542</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7127,25 +7127,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>746502</v>
+        <v>746527</v>
       </c>
       <c r="R62" t="n">
-        <v>7152478</v>
+        <v>7152434</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7217,10 +7217,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120086263</v>
+        <v>120086279</v>
       </c>
       <c r="B63" t="n">
-        <v>92048</v>
+        <v>78542</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7233,21 +7233,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7257,10 +7257,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>746450</v>
+        <v>746397</v>
       </c>
       <c r="R63" t="n">
-        <v>7152549</v>
+        <v>7152654</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7319,10 +7319,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120086280</v>
+        <v>120086291</v>
       </c>
       <c r="B64" t="n">
-        <v>78542</v>
+        <v>90825</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7331,25 +7331,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7359,10 +7359,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>746527</v>
+        <v>746502</v>
       </c>
       <c r="R64" t="n">
-        <v>7152434</v>
+        <v>7152478</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7421,10 +7421,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120086279</v>
+        <v>120086263</v>
       </c>
       <c r="B65" t="n">
-        <v>78542</v>
+        <v>92048</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7437,21 +7437,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7461,10 +7461,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>746397</v>
+        <v>746450</v>
       </c>
       <c r="R65" t="n">
-        <v>7152654</v>
+        <v>7152549</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7833,10 +7833,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120086259</v>
+        <v>120080336</v>
       </c>
       <c r="B69" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7845,25 +7845,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7873,10 +7873,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>746394</v>
+        <v>746545</v>
       </c>
       <c r="R69" t="n">
-        <v>7152581</v>
+        <v>7152464</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7923,19 +7923,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120080336</v>
+        <v>120094849</v>
       </c>
       <c r="B70" t="n">
         <v>91858</v>
@@ -7969,16 +7969,19 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>746545</v>
+        <v>746531</v>
       </c>
       <c r="R70" t="n">
-        <v>7152464</v>
+        <v>7152454</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8019,25 +8022,26 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120094849</v>
+        <v>120086297</v>
       </c>
       <c r="B71" t="n">
         <v>91858</v>
@@ -8071,19 +8075,16 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>746531</v>
+        <v>746473</v>
       </c>
       <c r="R71" t="n">
-        <v>7152454</v>
+        <v>7152499</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8124,7 +8125,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8143,10 +8143,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120086297</v>
+        <v>120086259</v>
       </c>
       <c r="B72" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8155,25 +8155,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8183,10 +8183,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>746473</v>
+        <v>746394</v>
       </c>
       <c r="R72" t="n">
-        <v>7152499</v>
+        <v>7152581</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 41672-2024 artfynd.xlsx
+++ b/artfynd/A 41672-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120068255</v>
+        <v>120068460</v>
       </c>
       <c r="B2" t="n">
         <v>91858</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>746352</v>
+        <v>746312</v>
       </c>
       <c r="R2" t="n">
-        <v>7152686</v>
+        <v>7152709</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120067430</v>
+        <v>120068346</v>
       </c>
       <c r="B3" t="n">
-        <v>91874</v>
+        <v>91870</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>746505</v>
+        <v>746324</v>
       </c>
       <c r="R3" t="n">
-        <v>7152499</v>
+        <v>7152703</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120066896</v>
+        <v>120068133</v>
       </c>
       <c r="B4" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>746537</v>
+        <v>746333</v>
       </c>
       <c r="R4" t="n">
-        <v>7152456</v>
+        <v>7152647</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120068602</v>
+        <v>120066896</v>
       </c>
       <c r="B5" t="n">
-        <v>79652</v>
+        <v>91881</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>746307</v>
+        <v>746537</v>
       </c>
       <c r="R5" t="n">
-        <v>7152647</v>
+        <v>7152456</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120067935</v>
+        <v>120067979</v>
       </c>
       <c r="B6" t="n">
         <v>91858</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>746381</v>
+        <v>746392</v>
       </c>
       <c r="R6" t="n">
-        <v>7152596</v>
+        <v>7152615</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120067841</v>
+        <v>120068080</v>
       </c>
       <c r="B7" t="n">
         <v>91858</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>746469</v>
+        <v>746371</v>
       </c>
       <c r="R7" t="n">
-        <v>7152569</v>
+        <v>7152632</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120069348</v>
+        <v>120069457</v>
       </c>
       <c r="B8" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>746382</v>
+        <v>746379</v>
       </c>
       <c r="R8" t="n">
-        <v>7152570</v>
+        <v>7152575</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120068460</v>
+        <v>120068602</v>
       </c>
       <c r="B9" t="n">
-        <v>91858</v>
+        <v>79652</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>746312</v>
+        <v>746307</v>
       </c>
       <c r="R9" t="n">
-        <v>7152709</v>
+        <v>7152647</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120067885</v>
+        <v>120068300</v>
       </c>
       <c r="B10" t="n">
-        <v>91902</v>
+        <v>91881</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>746399</v>
+        <v>746336</v>
       </c>
       <c r="R10" t="n">
-        <v>7152617</v>
+        <v>7152676</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120067504</v>
+        <v>120069608</v>
       </c>
       <c r="B11" t="n">
-        <v>91874</v>
+        <v>91850</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>746486</v>
+        <v>746422</v>
       </c>
       <c r="R11" t="n">
-        <v>7152501</v>
+        <v>7152546</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120068346</v>
+        <v>120069348</v>
       </c>
       <c r="B12" t="n">
-        <v>91870</v>
+        <v>91858</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>746324</v>
+        <v>746382</v>
       </c>
       <c r="R12" t="n">
-        <v>7152703</v>
+        <v>7152570</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,7 +1907,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120068383</v>
+        <v>120068255</v>
       </c>
       <c r="B13" t="n">
         <v>91858</v>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>746313</v>
+        <v>746352</v>
       </c>
       <c r="R13" t="n">
-        <v>7152706</v>
+        <v>7152686</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120068080</v>
+        <v>120068365</v>
       </c>
       <c r="B14" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2031,25 +2031,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>746371</v>
+        <v>746323</v>
       </c>
       <c r="R14" t="n">
-        <v>7152632</v>
+        <v>7152700</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120067137</v>
+        <v>120067504</v>
       </c>
       <c r="B15" t="n">
-        <v>91852</v>
+        <v>91874</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,21 +2147,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>746520</v>
+        <v>746486</v>
       </c>
       <c r="R15" t="n">
-        <v>7152487</v>
+        <v>7152501</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,7 +2243,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120067568</v>
+        <v>120066631</v>
       </c>
       <c r="B16" t="n">
         <v>91858</v>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>746484</v>
+        <v>746551</v>
       </c>
       <c r="R16" t="n">
-        <v>7152500</v>
+        <v>7152434</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120068300</v>
+        <v>120067430</v>
       </c>
       <c r="B17" t="n">
-        <v>91881</v>
+        <v>91874</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,21 +2371,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>746336</v>
+        <v>746505</v>
       </c>
       <c r="R17" t="n">
-        <v>7152676</v>
+        <v>7152499</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,7 +2467,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120067979</v>
+        <v>120068383</v>
       </c>
       <c r="B18" t="n">
         <v>91858</v>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>746392</v>
+        <v>746313</v>
       </c>
       <c r="R18" t="n">
-        <v>7152615</v>
+        <v>7152706</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,7 +2579,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120068133</v>
+        <v>120068331</v>
       </c>
       <c r="B19" t="n">
         <v>91858</v>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>746333</v>
+        <v>746318</v>
       </c>
       <c r="R19" t="n">
-        <v>7152647</v>
+        <v>7152701</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120066631</v>
+        <v>120067137</v>
       </c>
       <c r="B20" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2703,25 +2703,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>746551</v>
+        <v>746520</v>
       </c>
       <c r="R20" t="n">
-        <v>7152434</v>
+        <v>7152487</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120069608</v>
+        <v>120067568</v>
       </c>
       <c r="B21" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2815,25 +2815,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>746422</v>
+        <v>746484</v>
       </c>
       <c r="R21" t="n">
-        <v>7152546</v>
+        <v>7152500</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120069457</v>
+        <v>120067885</v>
       </c>
       <c r="B22" t="n">
-        <v>91874</v>
+        <v>91902</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>746379</v>
+        <v>746399</v>
       </c>
       <c r="R22" t="n">
-        <v>7152575</v>
+        <v>7152617</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3139,7 +3139,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120068331</v>
+        <v>120067841</v>
       </c>
       <c r="B24" t="n">
         <v>91858</v>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>746318</v>
+        <v>746469</v>
       </c>
       <c r="R24" t="n">
-        <v>7152701</v>
+        <v>7152569</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3251,10 +3251,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120068365</v>
+        <v>120067935</v>
       </c>
       <c r="B25" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3263,25 +3263,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>746323</v>
+        <v>746381</v>
       </c>
       <c r="R25" t="n">
-        <v>7152700</v>
+        <v>7152596</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3363,10 +3363,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120080342</v>
+        <v>120086265</v>
       </c>
       <c r="B26" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3375,25 +3375,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>746478</v>
+        <v>746353</v>
       </c>
       <c r="R26" t="n">
-        <v>7152487</v>
+        <v>7152592</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3453,22 +3453,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120086265</v>
+        <v>120094849</v>
       </c>
       <c r="B27" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3477,38 +3477,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>746353</v>
+        <v>746531</v>
       </c>
       <c r="R27" t="n">
-        <v>7152592</v>
+        <v>7152454</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3549,6 +3552,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3567,7 +3571,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120080345</v>
+        <v>120094897</v>
       </c>
       <c r="B28" t="n">
         <v>91858</v>
@@ -3601,16 +3605,19 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>746459</v>
+        <v>746482</v>
       </c>
       <c r="R28" t="n">
-        <v>7152465</v>
+        <v>7152467</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3651,28 +3658,29 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120080326</v>
+        <v>120086263</v>
       </c>
       <c r="B29" t="n">
-        <v>89247</v>
+        <v>92048</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3681,25 +3689,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1596</v>
+        <v>2079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3709,10 +3717,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>746543</v>
+        <v>746450</v>
       </c>
       <c r="R29" t="n">
-        <v>7152437</v>
+        <v>7152549</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3759,22 +3767,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120080349</v>
+        <v>120079802</v>
       </c>
       <c r="B30" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3783,25 +3791,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3811,13 +3819,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>746540</v>
+        <v>746495</v>
       </c>
       <c r="R30" t="n">
-        <v>7152444</v>
+        <v>7152470</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3861,22 +3869,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120086296</v>
+        <v>120086228</v>
       </c>
       <c r="B31" t="n">
-        <v>91858</v>
+        <v>74654</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3885,25 +3893,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3913,10 +3921,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>746425</v>
+        <v>746357</v>
       </c>
       <c r="R31" t="n">
-        <v>7152621</v>
+        <v>7152581</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3975,7 +3983,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120086294</v>
+        <v>120080346</v>
       </c>
       <c r="B32" t="n">
         <v>91858</v>
@@ -4015,10 +4023,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>746310</v>
+        <v>746461</v>
       </c>
       <c r="R32" t="n">
-        <v>7152670</v>
+        <v>7152458</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4065,19 +4073,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120080343</v>
+        <v>120094939</v>
       </c>
       <c r="B33" t="n">
         <v>91858</v>
@@ -4111,16 +4119,19 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>746467</v>
+        <v>746413</v>
       </c>
       <c r="R33" t="n">
-        <v>7152466</v>
+        <v>7152616</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4161,25 +4172,26 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120086276</v>
+        <v>120086274</v>
       </c>
       <c r="B34" t="n">
         <v>78542</v>
@@ -4219,10 +4231,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>746304</v>
+        <v>746478</v>
       </c>
       <c r="R34" t="n">
-        <v>7152657</v>
+        <v>7152496</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4281,10 +4293,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120086266</v>
+        <v>120086280</v>
       </c>
       <c r="B35" t="n">
-        <v>91881</v>
+        <v>78542</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4297,21 +4309,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4321,10 +4333,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>746429</v>
+        <v>746527</v>
       </c>
       <c r="R35" t="n">
-        <v>7152625</v>
+        <v>7152434</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4383,10 +4395,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120086269</v>
+        <v>120080348</v>
       </c>
       <c r="B36" t="n">
-        <v>88170</v>
+        <v>91858</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4395,41 +4407,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>746365</v>
+        <v>746505</v>
       </c>
       <c r="R36" t="n">
-        <v>7152575</v>
+        <v>7152451</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4464,40 +4473,34 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Inte ihålig men övriga karaktärer stämde.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120080295</v>
+        <v>120080349</v>
       </c>
       <c r="B37" t="n">
-        <v>57473</v>
+        <v>91858</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4506,46 +4509,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>746385</v>
+        <v>746540</v>
       </c>
       <c r="R37" t="n">
-        <v>7152570</v>
+        <v>7152444</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4604,10 +4599,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120094886</v>
+        <v>120086291</v>
       </c>
       <c r="B38" t="n">
-        <v>91858</v>
+        <v>90825</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4616,41 +4611,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>746500</v>
+        <v>746502</v>
       </c>
       <c r="R38" t="n">
-        <v>7152466</v>
+        <v>7152478</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4691,7 +4683,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4710,7 +4701,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120080346</v>
+        <v>120080341</v>
       </c>
       <c r="B39" t="n">
         <v>91858</v>
@@ -4750,10 +4741,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>746461</v>
+        <v>746384</v>
       </c>
       <c r="R39" t="n">
-        <v>7152458</v>
+        <v>7152544</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4812,10 +4803,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120094922</v>
+        <v>120094932</v>
       </c>
       <c r="B40" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4824,25 +4815,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4855,10 +4846,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>746442</v>
+        <v>746414</v>
       </c>
       <c r="R40" t="n">
-        <v>7152565</v>
+        <v>7152584</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4918,10 +4909,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120079802</v>
+        <v>120086269</v>
       </c>
       <c r="B41" t="n">
-        <v>91902</v>
+        <v>88170</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4934,37 +4925,40 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5449</v>
+        <v>4962</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>746495</v>
+        <v>746365</v>
       </c>
       <c r="R41" t="n">
-        <v>7152470</v>
+        <v>7152575</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4996,34 +4990,40 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Inte ihålig men övriga karaktärer stämde.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120086272</v>
+        <v>120080295</v>
       </c>
       <c r="B42" t="n">
-        <v>74640</v>
+        <v>57473</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5032,38 +5032,46 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>306</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>746357</v>
+        <v>746385</v>
       </c>
       <c r="R42" t="n">
-        <v>7152581</v>
+        <v>7152570</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5110,22 +5118,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120079805</v>
+        <v>120086294</v>
       </c>
       <c r="B43" t="n">
-        <v>92048</v>
+        <v>91858</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5134,25 +5142,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5162,13 +5170,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>746437</v>
+        <v>746310</v>
       </c>
       <c r="R43" t="n">
-        <v>7152508</v>
+        <v>7152670</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5212,22 +5220,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120086275</v>
+        <v>120094945</v>
       </c>
       <c r="B44" t="n">
-        <v>78542</v>
+        <v>91902</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5240,34 +5248,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>746370</v>
+        <v>746417</v>
       </c>
       <c r="R44" t="n">
-        <v>7152601</v>
+        <v>7152628</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5308,6 +5319,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5326,10 +5338,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120094939</v>
+        <v>120086230</v>
       </c>
       <c r="B45" t="n">
-        <v>91858</v>
+        <v>90545</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5342,37 +5354,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>746413</v>
+        <v>746412</v>
       </c>
       <c r="R45" t="n">
-        <v>7152616</v>
+        <v>7152564</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5413,7 +5422,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5432,10 +5440,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120079813</v>
+        <v>120086238</v>
       </c>
       <c r="B46" t="n">
-        <v>91858</v>
+        <v>57473</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5444,41 +5452,49 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>746517</v>
+        <v>746509</v>
       </c>
       <c r="R46" t="n">
-        <v>7152485</v>
+        <v>7152434</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5508,6 +5524,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Två</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5522,19 +5543,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120094959</v>
+        <v>120086296</v>
       </c>
       <c r="B47" t="n">
         <v>91858</v>
@@ -5568,19 +5589,16 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>746300</v>
+        <v>746425</v>
       </c>
       <c r="R47" t="n">
-        <v>7152654</v>
+        <v>7152621</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5621,7 +5639,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5640,7 +5657,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120080340</v>
+        <v>120079812</v>
       </c>
       <c r="B48" t="n">
         <v>91858</v>
@@ -5680,13 +5697,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>746398</v>
+        <v>746540</v>
       </c>
       <c r="R48" t="n">
-        <v>7152548</v>
+        <v>7152434</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5724,28 +5741,29 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120079812</v>
+        <v>120086259</v>
       </c>
       <c r="B49" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5754,25 +5772,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5782,13 +5800,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>746540</v>
+        <v>746394</v>
       </c>
       <c r="R49" t="n">
-        <v>7152434</v>
+        <v>7152581</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5826,29 +5844,28 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120079797</v>
+        <v>120079805</v>
       </c>
       <c r="B50" t="n">
-        <v>89650</v>
+        <v>92048</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5861,21 +5878,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1962</v>
+        <v>2079</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5885,10 +5902,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>746432</v>
+        <v>746437</v>
       </c>
       <c r="R50" t="n">
-        <v>7152509</v>
+        <v>7152508</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5947,10 +5964,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120086246</v>
+        <v>120094869</v>
       </c>
       <c r="B51" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5959,38 +5976,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>746475</v>
+        <v>746522</v>
       </c>
       <c r="R51" t="n">
-        <v>7152487</v>
+        <v>7152453</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6031,6 +6051,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6049,10 +6070,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120094945</v>
+        <v>120080342</v>
       </c>
       <c r="B52" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6061,41 +6082,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>746417</v>
+        <v>746478</v>
       </c>
       <c r="R52" t="n">
-        <v>7152628</v>
+        <v>7152487</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6136,29 +6154,28 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120080307</v>
+        <v>120080319</v>
       </c>
       <c r="B53" t="n">
-        <v>91902</v>
+        <v>92048</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6171,21 +6188,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5449</v>
+        <v>2079</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6195,10 +6212,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>746426</v>
+        <v>746477</v>
       </c>
       <c r="R53" t="n">
-        <v>7152510</v>
+        <v>7152502</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6233,6 +6250,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På kolad tallstubbe</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6241,6 +6263,26 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>Kolad tallstubbe</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Kolad tallstubbe</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6257,10 +6299,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120094897</v>
+        <v>120079797</v>
       </c>
       <c r="B54" t="n">
-        <v>91858</v>
+        <v>89650</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6269,44 +6311,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>746482</v>
+        <v>746432</v>
       </c>
       <c r="R54" t="n">
-        <v>7152467</v>
+        <v>7152509</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6344,29 +6383,28 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120080319</v>
+        <v>120080326</v>
       </c>
       <c r="B55" t="n">
-        <v>92048</v>
+        <v>89247</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6375,25 +6413,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2079</v>
+        <v>1596</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6403,10 +6441,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>746477</v>
+        <v>746543</v>
       </c>
       <c r="R55" t="n">
-        <v>7152502</v>
+        <v>7152437</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6441,11 +6479,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På kolad tallstubbe</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6454,26 +6487,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL55" t="inlineStr">
-        <is>
-          <t>Kolad tallstubbe</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Kolad tallstubbe</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6490,7 +6503,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120086245</v>
+        <v>120094922</v>
       </c>
       <c r="B56" t="n">
         <v>91902</v>
@@ -6524,16 +6537,19 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>746365</v>
+        <v>746442</v>
       </c>
       <c r="R56" t="n">
-        <v>7152575</v>
+        <v>7152565</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6574,6 +6590,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6592,10 +6609,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120086295</v>
+        <v>120080306</v>
       </c>
       <c r="B57" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6604,25 +6621,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6632,10 +6649,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>746365</v>
+        <v>746490</v>
       </c>
       <c r="R57" t="n">
-        <v>7152695</v>
+        <v>7152502</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6682,22 +6699,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120080337</v>
+        <v>120086278</v>
       </c>
       <c r="B58" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6706,25 +6723,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6734,10 +6751,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>746488</v>
+        <v>746365</v>
       </c>
       <c r="R58" t="n">
-        <v>7152500</v>
+        <v>7152695</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6784,22 +6801,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120086274</v>
+        <v>120094959</v>
       </c>
       <c r="B59" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6808,38 +6825,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>746478</v>
+        <v>746300</v>
       </c>
       <c r="R59" t="n">
-        <v>7152496</v>
+        <v>7152654</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6880,6 +6900,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6898,10 +6919,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120086230</v>
+        <v>120094855</v>
       </c>
       <c r="B60" t="n">
-        <v>90545</v>
+        <v>91858</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6914,34 +6935,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>746412</v>
+        <v>746547</v>
       </c>
       <c r="R60" t="n">
-        <v>7152564</v>
+        <v>7152471</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6982,6 +7006,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7000,10 +7025,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120086238</v>
+        <v>120086246</v>
       </c>
       <c r="B61" t="n">
-        <v>57473</v>
+        <v>91902</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7016,42 +7041,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>5449</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>746509</v>
+        <v>746475</v>
       </c>
       <c r="R61" t="n">
-        <v>7152434</v>
+        <v>7152487</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7084,11 +7101,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Två</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7115,10 +7127,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120086280</v>
+        <v>120094916</v>
       </c>
       <c r="B62" t="n">
-        <v>78542</v>
+        <v>91902</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7131,34 +7143,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>746527</v>
+        <v>746490</v>
       </c>
       <c r="R62" t="n">
-        <v>7152434</v>
+        <v>7152513</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7199,6 +7214,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7217,10 +7233,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120086279</v>
+        <v>120086297</v>
       </c>
       <c r="B63" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7229,25 +7245,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7257,10 +7273,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>746397</v>
+        <v>746473</v>
       </c>
       <c r="R63" t="n">
-        <v>7152654</v>
+        <v>7152499</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7319,10 +7335,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120086291</v>
+        <v>120086245</v>
       </c>
       <c r="B64" t="n">
-        <v>90825</v>
+        <v>91902</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7331,25 +7347,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>65</v>
+        <v>5449</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7359,10 +7375,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>746502</v>
+        <v>746365</v>
       </c>
       <c r="R64" t="n">
-        <v>7152478</v>
+        <v>7152575</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7421,10 +7437,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120086263</v>
+        <v>120080343</v>
       </c>
       <c r="B65" t="n">
-        <v>92048</v>
+        <v>91858</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7433,25 +7449,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7461,10 +7477,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>746450</v>
+        <v>746467</v>
       </c>
       <c r="R65" t="n">
-        <v>7152549</v>
+        <v>7152466</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7511,19 +7527,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120080338</v>
+        <v>120086298</v>
       </c>
       <c r="B66" t="n">
         <v>91858</v>
@@ -7563,10 +7579,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>746455</v>
+        <v>746527</v>
       </c>
       <c r="R66" t="n">
-        <v>7152561</v>
+        <v>7152434</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7613,19 +7629,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120094907</v>
+        <v>120080340</v>
       </c>
       <c r="B67" t="n">
         <v>91858</v>
@@ -7659,19 +7675,16 @@
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>746484</v>
+        <v>746398</v>
       </c>
       <c r="R67" t="n">
-        <v>7152510</v>
+        <v>7152548</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7712,26 +7725,25 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120086298</v>
+        <v>120094901</v>
       </c>
       <c r="B68" t="n">
         <v>91858</v>
@@ -7765,16 +7777,19 @@
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>746527</v>
+        <v>746487</v>
       </c>
       <c r="R68" t="n">
-        <v>7152434</v>
+        <v>7152494</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7815,6 +7830,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7833,7 +7849,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120080336</v>
+        <v>120080337</v>
       </c>
       <c r="B69" t="n">
         <v>91858</v>
@@ -7873,10 +7889,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>746545</v>
+        <v>746488</v>
       </c>
       <c r="R69" t="n">
-        <v>7152464</v>
+        <v>7152500</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7935,10 +7951,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120094849</v>
+        <v>120086276</v>
       </c>
       <c r="B70" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7947,41 +7963,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>746531</v>
+        <v>746304</v>
       </c>
       <c r="R70" t="n">
-        <v>7152454</v>
+        <v>7152657</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8022,7 +8035,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8041,10 +8053,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120086297</v>
+        <v>120086279</v>
       </c>
       <c r="B71" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8053,25 +8065,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8081,10 +8093,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>746473</v>
+        <v>746397</v>
       </c>
       <c r="R71" t="n">
-        <v>7152499</v>
+        <v>7152654</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8143,10 +8155,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120086259</v>
+        <v>120086272</v>
       </c>
       <c r="B72" t="n">
-        <v>91850</v>
+        <v>74640</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8155,25 +8167,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4361</v>
+        <v>306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8183,7 +8195,7 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>746394</v>
+        <v>746357</v>
       </c>
       <c r="R72" t="n">
         <v>7152581</v>
@@ -8245,10 +8257,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120086228</v>
+        <v>120086295</v>
       </c>
       <c r="B73" t="n">
-        <v>74654</v>
+        <v>91858</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8257,25 +8269,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8285,10 +8297,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>746357</v>
+        <v>746365</v>
       </c>
       <c r="R73" t="n">
-        <v>7152581</v>
+        <v>7152695</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8347,7 +8359,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120080348</v>
+        <v>120079813</v>
       </c>
       <c r="B74" t="n">
         <v>91858</v>
@@ -8387,13 +8399,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>746505</v>
+        <v>746517</v>
       </c>
       <c r="R74" t="n">
-        <v>7152451</v>
+        <v>7152485</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8437,22 +8449,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120094916</v>
+        <v>120080338</v>
       </c>
       <c r="B75" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8461,41 +8473,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>746490</v>
+        <v>746455</v>
       </c>
       <c r="R75" t="n">
-        <v>7152513</v>
+        <v>7152561</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8536,29 +8545,28 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120094869</v>
+        <v>120086275</v>
       </c>
       <c r="B76" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8567,41 +8575,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>746522</v>
+        <v>746370</v>
       </c>
       <c r="R76" t="n">
-        <v>7152453</v>
+        <v>7152601</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8642,7 +8647,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8661,10 +8665,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120094855</v>
+        <v>120079809</v>
       </c>
       <c r="B77" t="n">
-        <v>91858</v>
+        <v>90730</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8673,25 +8677,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8704,13 +8708,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>746547</v>
+        <v>746368</v>
       </c>
       <c r="R77" t="n">
-        <v>7152471</v>
+        <v>7152599</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8755,19 +8759,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120080341</v>
+        <v>120094951</v>
       </c>
       <c r="B78" t="n">
         <v>91858</v>
@@ -8801,16 +8805,19 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>746384</v>
+        <v>746357</v>
       </c>
       <c r="R78" t="n">
-        <v>7152544</v>
+        <v>7152686</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8851,25 +8858,26 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120094932</v>
+        <v>120080345</v>
       </c>
       <c r="B79" t="n">
         <v>91858</v>
@@ -8903,19 +8911,16 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>746414</v>
+        <v>746459</v>
       </c>
       <c r="R79" t="n">
-        <v>7152584</v>
+        <v>7152465</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8956,29 +8961,28 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120086277</v>
+        <v>120094886</v>
       </c>
       <c r="B80" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8987,38 +8991,41 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>746302</v>
+        <v>746500</v>
       </c>
       <c r="R80" t="n">
-        <v>7152670</v>
+        <v>7152466</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9059,6 +9066,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -9077,10 +9085,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120086278</v>
+        <v>120094907</v>
       </c>
       <c r="B81" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9089,38 +9097,41 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>746365</v>
+        <v>746484</v>
       </c>
       <c r="R81" t="n">
-        <v>7152695</v>
+        <v>7152510</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9161,6 +9172,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9179,10 +9191,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120079809</v>
+        <v>120086277</v>
       </c>
       <c r="B82" t="n">
-        <v>90730</v>
+        <v>78542</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9191,44 +9203,41 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>746368</v>
+        <v>746302</v>
       </c>
       <c r="R82" t="n">
-        <v>7152599</v>
+        <v>7152670</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9266,29 +9275,28 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120080306</v>
+        <v>120086266</v>
       </c>
       <c r="B83" t="n">
-        <v>91902</v>
+        <v>91881</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9301,21 +9309,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9325,10 +9333,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>746490</v>
+        <v>746429</v>
       </c>
       <c r="R83" t="n">
-        <v>7152502</v>
+        <v>7152625</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9375,19 +9383,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120094901</v>
+        <v>120080336</v>
       </c>
       <c r="B84" t="n">
         <v>91858</v>
@@ -9421,19 +9429,16 @@
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>746487</v>
+        <v>746545</v>
       </c>
       <c r="R84" t="n">
-        <v>7152494</v>
+        <v>7152464</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9474,29 +9479,28 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120094951</v>
+        <v>120080307</v>
       </c>
       <c r="B85" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9505,41 +9509,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>746357</v>
+        <v>746426</v>
       </c>
       <c r="R85" t="n">
-        <v>7152686</v>
+        <v>7152510</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9580,19 +9581,18 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>

--- a/artfynd/A 41672-2024 artfynd.xlsx
+++ b/artfynd/A 41672-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120068460</v>
+        <v>120067262</v>
       </c>
       <c r="B2" t="n">
         <v>91858</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>746312</v>
+        <v>746520</v>
       </c>
       <c r="R2" t="n">
-        <v>7152709</v>
+        <v>7152494</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120068346</v>
+        <v>120067430</v>
       </c>
       <c r="B3" t="n">
-        <v>91870</v>
+        <v>91874</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>746324</v>
+        <v>746505</v>
       </c>
       <c r="R3" t="n">
-        <v>7152703</v>
+        <v>7152499</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120068133</v>
+        <v>120068365</v>
       </c>
       <c r="B4" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>746333</v>
+        <v>746323</v>
       </c>
       <c r="R4" t="n">
-        <v>7152647</v>
+        <v>7152700</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120066896</v>
+        <v>120068346</v>
       </c>
       <c r="B5" t="n">
-        <v>91881</v>
+        <v>91870</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>746537</v>
+        <v>746324</v>
       </c>
       <c r="R5" t="n">
-        <v>7152456</v>
+        <v>7152703</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120067979</v>
+        <v>120068255</v>
       </c>
       <c r="B6" t="n">
         <v>91858</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>746392</v>
+        <v>746352</v>
       </c>
       <c r="R6" t="n">
-        <v>7152615</v>
+        <v>7152686</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120068080</v>
+        <v>120069608</v>
       </c>
       <c r="B7" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>746371</v>
+        <v>746422</v>
       </c>
       <c r="R7" t="n">
-        <v>7152632</v>
+        <v>7152546</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120069457</v>
+        <v>120066631</v>
       </c>
       <c r="B8" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>746379</v>
+        <v>746551</v>
       </c>
       <c r="R8" t="n">
-        <v>7152575</v>
+        <v>7152434</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120068602</v>
+        <v>120067979</v>
       </c>
       <c r="B9" t="n">
-        <v>79652</v>
+        <v>91858</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>746307</v>
+        <v>746392</v>
       </c>
       <c r="R9" t="n">
-        <v>7152647</v>
+        <v>7152615</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120069608</v>
+        <v>120068460</v>
       </c>
       <c r="B11" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,25 +1695,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>746422</v>
+        <v>746312</v>
       </c>
       <c r="R11" t="n">
-        <v>7152546</v>
+        <v>7152709</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,7 +1795,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120069348</v>
+        <v>120067568</v>
       </c>
       <c r="B12" t="n">
         <v>91858</v>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>746382</v>
+        <v>746484</v>
       </c>
       <c r="R12" t="n">
-        <v>7152570</v>
+        <v>7152500</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,7 +1907,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120068255</v>
+        <v>120068331</v>
       </c>
       <c r="B13" t="n">
         <v>91858</v>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>746352</v>
+        <v>746318</v>
       </c>
       <c r="R13" t="n">
-        <v>7152686</v>
+        <v>7152701</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120068365</v>
+        <v>120067841</v>
       </c>
       <c r="B14" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2031,25 +2031,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>746323</v>
+        <v>746469</v>
       </c>
       <c r="R14" t="n">
-        <v>7152700</v>
+        <v>7152569</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,7 +2131,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120067504</v>
+        <v>120069457</v>
       </c>
       <c r="B15" t="n">
         <v>91874</v>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>746486</v>
+        <v>746379</v>
       </c>
       <c r="R15" t="n">
-        <v>7152501</v>
+        <v>7152575</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120066631</v>
+        <v>120066896</v>
       </c>
       <c r="B16" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2255,25 +2255,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>746551</v>
+        <v>746537</v>
       </c>
       <c r="R16" t="n">
-        <v>7152434</v>
+        <v>7152456</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120067430</v>
+        <v>120068383</v>
       </c>
       <c r="B17" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2367,25 +2367,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>746505</v>
+        <v>746313</v>
       </c>
       <c r="R17" t="n">
-        <v>7152499</v>
+        <v>7152706</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120068383</v>
+        <v>120067137</v>
       </c>
       <c r="B18" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2479,25 +2479,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>746313</v>
+        <v>746520</v>
       </c>
       <c r="R18" t="n">
-        <v>7152706</v>
+        <v>7152487</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,7 +2579,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120068331</v>
+        <v>120067935</v>
       </c>
       <c r="B19" t="n">
         <v>91858</v>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>746318</v>
+        <v>746381</v>
       </c>
       <c r="R19" t="n">
-        <v>7152701</v>
+        <v>7152596</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120067137</v>
+        <v>120068133</v>
       </c>
       <c r="B20" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2703,25 +2703,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>746520</v>
+        <v>746333</v>
       </c>
       <c r="R20" t="n">
-        <v>7152487</v>
+        <v>7152647</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120067568</v>
+        <v>120067885</v>
       </c>
       <c r="B21" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2815,25 +2815,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>746484</v>
+        <v>746399</v>
       </c>
       <c r="R21" t="n">
-        <v>7152500</v>
+        <v>7152617</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120067885</v>
+        <v>120067504</v>
       </c>
       <c r="B22" t="n">
-        <v>91902</v>
+        <v>91874</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>746399</v>
+        <v>746486</v>
       </c>
       <c r="R22" t="n">
-        <v>7152617</v>
+        <v>7152501</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,7 +3027,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120067262</v>
+        <v>120069348</v>
       </c>
       <c r="B23" t="n">
         <v>91858</v>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>746520</v>
+        <v>746382</v>
       </c>
       <c r="R23" t="n">
-        <v>7152494</v>
+        <v>7152570</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,7 +3139,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120067841</v>
+        <v>120068080</v>
       </c>
       <c r="B24" t="n">
         <v>91858</v>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>746469</v>
+        <v>746371</v>
       </c>
       <c r="R24" t="n">
-        <v>7152569</v>
+        <v>7152632</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3251,10 +3251,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120067935</v>
+        <v>120068602</v>
       </c>
       <c r="B25" t="n">
-        <v>91858</v>
+        <v>79652</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3267,21 +3267,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>746381</v>
+        <v>746307</v>
       </c>
       <c r="R25" t="n">
-        <v>7152596</v>
+        <v>7152647</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3363,10 +3363,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120086265</v>
+        <v>120086263</v>
       </c>
       <c r="B26" t="n">
-        <v>78279</v>
+        <v>92048</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3379,21 +3379,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>746353</v>
+        <v>746450</v>
       </c>
       <c r="R26" t="n">
-        <v>7152592</v>
+        <v>7152549</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3465,7 +3465,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120094849</v>
+        <v>120080345</v>
       </c>
       <c r="B27" t="n">
         <v>91858</v>
@@ -3499,19 +3499,16 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>746531</v>
+        <v>746459</v>
       </c>
       <c r="R27" t="n">
-        <v>7152454</v>
+        <v>7152465</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3552,26 +3549,25 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120094897</v>
+        <v>120080348</v>
       </c>
       <c r="B28" t="n">
         <v>91858</v>
@@ -3605,19 +3601,16 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>746482</v>
+        <v>746505</v>
       </c>
       <c r="R28" t="n">
-        <v>7152467</v>
+        <v>7152451</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3658,29 +3651,28 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120086263</v>
+        <v>120086295</v>
       </c>
       <c r="B29" t="n">
-        <v>92048</v>
+        <v>91858</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3689,25 +3681,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3717,10 +3709,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>746450</v>
+        <v>746365</v>
       </c>
       <c r="R29" t="n">
-        <v>7152549</v>
+        <v>7152695</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3779,10 +3771,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120079802</v>
+        <v>120080346</v>
       </c>
       <c r="B30" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3791,25 +3783,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3819,13 +3811,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>746495</v>
+        <v>746461</v>
       </c>
       <c r="R30" t="n">
-        <v>7152470</v>
+        <v>7152458</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3869,22 +3861,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120086228</v>
+        <v>120094897</v>
       </c>
       <c r="B31" t="n">
-        <v>74654</v>
+        <v>91858</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3893,38 +3885,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>746357</v>
+        <v>746482</v>
       </c>
       <c r="R31" t="n">
-        <v>7152581</v>
+        <v>7152467</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3965,6 +3960,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3983,10 +3979,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120080346</v>
+        <v>120086276</v>
       </c>
       <c r="B32" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3995,25 +3991,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4023,10 +4019,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>746461</v>
+        <v>746304</v>
       </c>
       <c r="R32" t="n">
-        <v>7152458</v>
+        <v>7152657</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4073,22 +4069,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120094939</v>
+        <v>120086265</v>
       </c>
       <c r="B33" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4097,41 +4093,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>746413</v>
+        <v>746353</v>
       </c>
       <c r="R33" t="n">
-        <v>7152616</v>
+        <v>7152592</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4172,7 +4165,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4191,10 +4183,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120086274</v>
+        <v>120086259</v>
       </c>
       <c r="B34" t="n">
-        <v>78542</v>
+        <v>91850</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4207,21 +4199,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4231,10 +4223,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>746478</v>
+        <v>746394</v>
       </c>
       <c r="R34" t="n">
-        <v>7152496</v>
+        <v>7152581</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4293,7 +4285,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120086280</v>
+        <v>120086277</v>
       </c>
       <c r="B35" t="n">
         <v>78542</v>
@@ -4333,10 +4325,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>746527</v>
+        <v>746302</v>
       </c>
       <c r="R35" t="n">
-        <v>7152434</v>
+        <v>7152670</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4395,7 +4387,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120080348</v>
+        <v>120080342</v>
       </c>
       <c r="B36" t="n">
         <v>91858</v>
@@ -4435,10 +4427,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>746505</v>
+        <v>746478</v>
       </c>
       <c r="R36" t="n">
-        <v>7152451</v>
+        <v>7152487</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4497,10 +4489,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120080349</v>
+        <v>120094922</v>
       </c>
       <c r="B37" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4509,38 +4501,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>746540</v>
+        <v>746442</v>
       </c>
       <c r="R37" t="n">
-        <v>7152444</v>
+        <v>7152565</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4581,28 +4576,29 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120086291</v>
+        <v>120086280</v>
       </c>
       <c r="B38" t="n">
-        <v>90825</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4611,25 +4607,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4639,10 +4635,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>746502</v>
+        <v>746527</v>
       </c>
       <c r="R38" t="n">
-        <v>7152478</v>
+        <v>7152434</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4701,10 +4697,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120080341</v>
+        <v>120094945</v>
       </c>
       <c r="B39" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4713,38 +4709,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>746384</v>
+        <v>746417</v>
       </c>
       <c r="R39" t="n">
-        <v>7152544</v>
+        <v>7152628</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4785,25 +4784,26 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120094932</v>
+        <v>120086294</v>
       </c>
       <c r="B40" t="n">
         <v>91858</v>
@@ -4837,19 +4837,16 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>746414</v>
+        <v>746310</v>
       </c>
       <c r="R40" t="n">
-        <v>7152584</v>
+        <v>7152670</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4890,7 +4887,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4909,10 +4905,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120086269</v>
+        <v>120086297</v>
       </c>
       <c r="B41" t="n">
-        <v>88170</v>
+        <v>91858</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4921,41 +4917,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>746365</v>
+        <v>746473</v>
       </c>
       <c r="R41" t="n">
-        <v>7152575</v>
+        <v>7152499</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4990,18 +4983,12 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Inte ihålig men övriga karaktärer stämde.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5020,10 +5007,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120080295</v>
+        <v>120080319</v>
       </c>
       <c r="B42" t="n">
-        <v>57473</v>
+        <v>92048</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5036,42 +5023,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>2079</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>746385</v>
+        <v>746477</v>
       </c>
       <c r="R42" t="n">
-        <v>7152570</v>
+        <v>7152502</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5106,6 +5085,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På kolad tallstubbe</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5114,6 +5098,26 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL42" t="inlineStr">
+        <is>
+          <t>Kolad tallstubbe</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Kolad tallstubbe</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5130,7 +5134,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120086294</v>
+        <v>120080338</v>
       </c>
       <c r="B43" t="n">
         <v>91858</v>
@@ -5170,10 +5174,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>746310</v>
+        <v>746455</v>
       </c>
       <c r="R43" t="n">
-        <v>7152670</v>
+        <v>7152561</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5220,22 +5224,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120094945</v>
+        <v>120094869</v>
       </c>
       <c r="B44" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5244,25 +5248,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5275,10 +5279,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>746417</v>
+        <v>746522</v>
       </c>
       <c r="R44" t="n">
-        <v>7152628</v>
+        <v>7152453</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5338,10 +5342,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120086230</v>
+        <v>120094907</v>
       </c>
       <c r="B45" t="n">
-        <v>90545</v>
+        <v>91858</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5354,34 +5358,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>746412</v>
+        <v>746484</v>
       </c>
       <c r="R45" t="n">
-        <v>7152564</v>
+        <v>7152510</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5422,6 +5429,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5440,10 +5448,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120086238</v>
+        <v>120079805</v>
       </c>
       <c r="B46" t="n">
-        <v>57473</v>
+        <v>92048</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5456,45 +5464,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>2079</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>746509</v>
+        <v>746437</v>
       </c>
       <c r="R46" t="n">
-        <v>7152434</v>
+        <v>7152508</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5524,11 +5524,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Två</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5543,19 +5538,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120086296</v>
+        <v>120094901</v>
       </c>
       <c r="B47" t="n">
         <v>91858</v>
@@ -5589,16 +5584,19 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>746425</v>
+        <v>746487</v>
       </c>
       <c r="R47" t="n">
-        <v>7152621</v>
+        <v>7152494</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5639,6 +5637,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5657,7 +5656,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120079812</v>
+        <v>120086296</v>
       </c>
       <c r="B48" t="n">
         <v>91858</v>
@@ -5697,13 +5696,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>746540</v>
+        <v>746425</v>
       </c>
       <c r="R48" t="n">
-        <v>7152434</v>
+        <v>7152621</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5741,29 +5740,28 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120086259</v>
+        <v>120079813</v>
       </c>
       <c r="B49" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5772,25 +5770,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5800,13 +5798,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>746394</v>
+        <v>746517</v>
       </c>
       <c r="R49" t="n">
-        <v>7152581</v>
+        <v>7152485</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5850,22 +5848,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120079805</v>
+        <v>120086238</v>
       </c>
       <c r="B50" t="n">
-        <v>92048</v>
+        <v>57473</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5878,37 +5876,45 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2079</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>746437</v>
+        <v>746509</v>
       </c>
       <c r="R50" t="n">
-        <v>7152508</v>
+        <v>7152434</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5938,6 +5944,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Två</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5952,22 +5963,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120094869</v>
+        <v>120086269</v>
       </c>
       <c r="B51" t="n">
-        <v>91858</v>
+        <v>88170</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5976,25 +5987,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6007,10 +6018,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>746522</v>
+        <v>746365</v>
       </c>
       <c r="R51" t="n">
-        <v>7152453</v>
+        <v>7152575</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6043,6 +6054,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Inte ihålig men övriga karaktärer stämde.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6070,10 +6086,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120080342</v>
+        <v>120079797</v>
       </c>
       <c r="B52" t="n">
-        <v>91858</v>
+        <v>89650</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6082,25 +6098,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6110,13 +6126,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>746478</v>
+        <v>746432</v>
       </c>
       <c r="R52" t="n">
-        <v>7152487</v>
+        <v>7152509</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6160,22 +6176,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120080319</v>
+        <v>120094886</v>
       </c>
       <c r="B53" t="n">
-        <v>92048</v>
+        <v>91858</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6184,38 +6200,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>746477</v>
+        <v>746500</v>
       </c>
       <c r="R53" t="n">
-        <v>7152502</v>
+        <v>7152466</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6250,59 +6269,35 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På kolad tallstubbe</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL53" t="inlineStr">
-        <is>
-          <t>Kolad tallstubbe</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Kolad tallstubbe</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120079797</v>
+        <v>120080336</v>
       </c>
       <c r="B54" t="n">
-        <v>89650</v>
+        <v>91858</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6311,25 +6306,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6339,13 +6334,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>746432</v>
+        <v>746545</v>
       </c>
       <c r="R54" t="n">
-        <v>7152509</v>
+        <v>7152464</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6389,22 +6384,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120080326</v>
+        <v>120086228</v>
       </c>
       <c r="B55" t="n">
-        <v>89247</v>
+        <v>74654</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6413,25 +6408,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1596</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6441,10 +6436,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>746543</v>
+        <v>746357</v>
       </c>
       <c r="R55" t="n">
-        <v>7152437</v>
+        <v>7152581</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6491,22 +6486,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120094922</v>
+        <v>120080340</v>
       </c>
       <c r="B56" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6515,41 +6510,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>746442</v>
+        <v>746398</v>
       </c>
       <c r="R56" t="n">
-        <v>7152565</v>
+        <v>7152548</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6590,29 +6582,28 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120080306</v>
+        <v>120086272</v>
       </c>
       <c r="B57" t="n">
-        <v>91902</v>
+        <v>74640</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6621,25 +6612,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5449</v>
+        <v>306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6649,10 +6640,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>746490</v>
+        <v>746357</v>
       </c>
       <c r="R57" t="n">
-        <v>7152502</v>
+        <v>7152581</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6699,22 +6690,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120086278</v>
+        <v>120086298</v>
       </c>
       <c r="B58" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6723,25 +6714,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6751,10 +6742,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>746365</v>
+        <v>746527</v>
       </c>
       <c r="R58" t="n">
-        <v>7152695</v>
+        <v>7152434</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6813,10 +6804,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120094959</v>
+        <v>120094916</v>
       </c>
       <c r="B59" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6825,25 +6816,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6856,10 +6847,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>746300</v>
+        <v>746490</v>
       </c>
       <c r="R59" t="n">
-        <v>7152654</v>
+        <v>7152513</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6919,10 +6910,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120094855</v>
+        <v>120079802</v>
       </c>
       <c r="B60" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6931,44 +6922,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>746547</v>
+        <v>746495</v>
       </c>
       <c r="R60" t="n">
-        <v>7152471</v>
+        <v>7152470</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7006,29 +6994,28 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120086246</v>
+        <v>120080295</v>
       </c>
       <c r="B61" t="n">
-        <v>91902</v>
+        <v>57473</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7041,34 +7028,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>746475</v>
+        <v>746385</v>
       </c>
       <c r="R61" t="n">
-        <v>7152487</v>
+        <v>7152570</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7115,22 +7110,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120094916</v>
+        <v>120080326</v>
       </c>
       <c r="B62" t="n">
-        <v>91902</v>
+        <v>89247</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7139,41 +7134,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5449</v>
+        <v>1596</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>746490</v>
+        <v>746543</v>
       </c>
       <c r="R62" t="n">
-        <v>7152513</v>
+        <v>7152437</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7214,29 +7206,28 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120086297</v>
+        <v>120086230</v>
       </c>
       <c r="B63" t="n">
-        <v>91858</v>
+        <v>90545</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7249,21 +7240,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7273,10 +7264,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>746473</v>
+        <v>746412</v>
       </c>
       <c r="R63" t="n">
-        <v>7152499</v>
+        <v>7152564</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7335,10 +7326,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120086245</v>
+        <v>120080343</v>
       </c>
       <c r="B64" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7347,25 +7338,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7375,10 +7366,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>746365</v>
+        <v>746467</v>
       </c>
       <c r="R64" t="n">
-        <v>7152575</v>
+        <v>7152466</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7425,22 +7416,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120080343</v>
+        <v>120086274</v>
       </c>
       <c r="B65" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7449,25 +7440,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7477,10 +7468,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>746467</v>
+        <v>746478</v>
       </c>
       <c r="R65" t="n">
-        <v>7152466</v>
+        <v>7152496</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7527,22 +7518,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120086298</v>
+        <v>120086278</v>
       </c>
       <c r="B66" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7551,25 +7542,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7579,10 +7570,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>746527</v>
+        <v>746365</v>
       </c>
       <c r="R66" t="n">
-        <v>7152434</v>
+        <v>7152695</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7641,10 +7632,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120080340</v>
+        <v>120080307</v>
       </c>
       <c r="B67" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7653,25 +7644,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7681,10 +7672,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>746398</v>
+        <v>746426</v>
       </c>
       <c r="R67" t="n">
-        <v>7152548</v>
+        <v>7152510</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7743,7 +7734,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120094901</v>
+        <v>120080349</v>
       </c>
       <c r="B68" t="n">
         <v>91858</v>
@@ -7777,19 +7768,16 @@
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>746487</v>
+        <v>746540</v>
       </c>
       <c r="R68" t="n">
-        <v>7152494</v>
+        <v>7152444</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7830,26 +7818,25 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120080337</v>
+        <v>120094932</v>
       </c>
       <c r="B69" t="n">
         <v>91858</v>
@@ -7883,16 +7870,19 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>746488</v>
+        <v>746414</v>
       </c>
       <c r="R69" t="n">
-        <v>7152500</v>
+        <v>7152584</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7933,28 +7923,29 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120086276</v>
+        <v>120094855</v>
       </c>
       <c r="B70" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7963,38 +7954,41 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>746304</v>
+        <v>746547</v>
       </c>
       <c r="R70" t="n">
-        <v>7152657</v>
+        <v>7152471</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8035,6 +8029,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8155,10 +8150,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120086272</v>
+        <v>120080306</v>
       </c>
       <c r="B72" t="n">
-        <v>74640</v>
+        <v>91902</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8167,25 +8162,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>306</v>
+        <v>5449</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8195,10 +8190,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>746357</v>
+        <v>746490</v>
       </c>
       <c r="R72" t="n">
-        <v>7152581</v>
+        <v>7152502</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8245,22 +8240,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120086295</v>
+        <v>120086246</v>
       </c>
       <c r="B73" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8269,25 +8264,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8297,10 +8292,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>746365</v>
+        <v>746475</v>
       </c>
       <c r="R73" t="n">
-        <v>7152695</v>
+        <v>7152487</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8359,10 +8354,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120079813</v>
+        <v>120079809</v>
       </c>
       <c r="B74" t="n">
-        <v>91858</v>
+        <v>90730</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8371,38 +8366,41 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>746517</v>
+        <v>746368</v>
       </c>
       <c r="R74" t="n">
-        <v>7152485</v>
+        <v>7152599</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8443,6 +8441,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8461,10 +8460,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120080338</v>
+        <v>120086245</v>
       </c>
       <c r="B75" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8473,25 +8472,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8501,10 +8500,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>746455</v>
+        <v>746365</v>
       </c>
       <c r="R75" t="n">
-        <v>7152561</v>
+        <v>7152575</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8551,22 +8550,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120086275</v>
+        <v>120086291</v>
       </c>
       <c r="B76" t="n">
-        <v>78542</v>
+        <v>90825</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8575,25 +8574,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8603,10 +8602,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>746370</v>
+        <v>746502</v>
       </c>
       <c r="R76" t="n">
-        <v>7152601</v>
+        <v>7152478</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8665,10 +8664,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120079809</v>
+        <v>120094951</v>
       </c>
       <c r="B77" t="n">
-        <v>90730</v>
+        <v>91858</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8677,25 +8676,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8708,13 +8707,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>746368</v>
+        <v>746357</v>
       </c>
       <c r="R77" t="n">
-        <v>7152599</v>
+        <v>7152686</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8759,19 +8758,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120094951</v>
+        <v>120079812</v>
       </c>
       <c r="B78" t="n">
         <v>91858</v>
@@ -8805,22 +8804,19 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>746357</v>
+        <v>746540</v>
       </c>
       <c r="R78" t="n">
-        <v>7152686</v>
+        <v>7152434</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8865,19 +8861,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120080345</v>
+        <v>120080337</v>
       </c>
       <c r="B79" t="n">
         <v>91858</v>
@@ -8917,10 +8913,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>746459</v>
+        <v>746488</v>
       </c>
       <c r="R79" t="n">
-        <v>7152465</v>
+        <v>7152500</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8979,10 +8975,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120094886</v>
+        <v>120086275</v>
       </c>
       <c r="B80" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8991,41 +8987,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>746500</v>
+        <v>746370</v>
       </c>
       <c r="R80" t="n">
-        <v>7152466</v>
+        <v>7152601</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9066,7 +9059,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -9085,7 +9077,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120094907</v>
+        <v>120094959</v>
       </c>
       <c r="B81" t="n">
         <v>91858</v>
@@ -9128,10 +9120,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>746484</v>
+        <v>746300</v>
       </c>
       <c r="R81" t="n">
-        <v>7152510</v>
+        <v>7152654</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9191,10 +9183,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120086277</v>
+        <v>120080341</v>
       </c>
       <c r="B82" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9203,25 +9195,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9231,10 +9223,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>746302</v>
+        <v>746384</v>
       </c>
       <c r="R82" t="n">
-        <v>7152670</v>
+        <v>7152544</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9281,22 +9273,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120086266</v>
+        <v>120094849</v>
       </c>
       <c r="B83" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9305,38 +9297,41 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>746429</v>
+        <v>746531</v>
       </c>
       <c r="R83" t="n">
-        <v>7152625</v>
+        <v>7152454</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9377,6 +9372,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9395,7 +9391,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120080336</v>
+        <v>120094939</v>
       </c>
       <c r="B84" t="n">
         <v>91858</v>
@@ -9429,16 +9425,19 @@
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>746545</v>
+        <v>746413</v>
       </c>
       <c r="R84" t="n">
-        <v>7152464</v>
+        <v>7152616</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9479,28 +9478,29 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120080307</v>
+        <v>120086266</v>
       </c>
       <c r="B85" t="n">
-        <v>91902</v>
+        <v>91881</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9513,21 +9513,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9537,10 +9537,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>746426</v>
+        <v>746429</v>
       </c>
       <c r="R85" t="n">
-        <v>7152510</v>
+        <v>7152625</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9587,12 +9587,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>

--- a/artfynd/A 41672-2024 artfynd.xlsx
+++ b/artfynd/A 41672-2024 artfynd.xlsx
@@ -3363,10 +3363,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120086263</v>
+        <v>120080345</v>
       </c>
       <c r="B26" t="n">
-        <v>92048</v>
+        <v>91858</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3375,25 +3375,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>746450</v>
+        <v>746459</v>
       </c>
       <c r="R26" t="n">
-        <v>7152549</v>
+        <v>7152465</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3453,19 +3453,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120080345</v>
+        <v>120080348</v>
       </c>
       <c r="B27" t="n">
         <v>91858</v>
@@ -3505,10 +3505,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>746459</v>
+        <v>746505</v>
       </c>
       <c r="R27" t="n">
-        <v>7152465</v>
+        <v>7152451</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3567,7 +3567,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120080348</v>
+        <v>120086295</v>
       </c>
       <c r="B28" t="n">
         <v>91858</v>
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>746505</v>
+        <v>746365</v>
       </c>
       <c r="R28" t="n">
-        <v>7152451</v>
+        <v>7152695</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3657,19 +3657,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120086295</v>
+        <v>120080346</v>
       </c>
       <c r="B29" t="n">
         <v>91858</v>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>746365</v>
+        <v>746461</v>
       </c>
       <c r="R29" t="n">
-        <v>7152695</v>
+        <v>7152458</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3759,19 +3759,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120080346</v>
+        <v>120094897</v>
       </c>
       <c r="B30" t="n">
         <v>91858</v>
@@ -3805,16 +3805,19 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>746461</v>
+        <v>746482</v>
       </c>
       <c r="R30" t="n">
-        <v>7152458</v>
+        <v>7152467</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3855,28 +3858,29 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120094897</v>
+        <v>120086265</v>
       </c>
       <c r="B31" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3885,41 +3889,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>746482</v>
+        <v>746353</v>
       </c>
       <c r="R31" t="n">
-        <v>7152467</v>
+        <v>7152592</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3960,7 +3961,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3979,10 +3979,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120086276</v>
+        <v>120086263</v>
       </c>
       <c r="B32" t="n">
-        <v>78542</v>
+        <v>92048</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3995,21 +3995,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>746304</v>
+        <v>746450</v>
       </c>
       <c r="R32" t="n">
-        <v>7152657</v>
+        <v>7152549</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4081,10 +4081,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120086265</v>
+        <v>120086276</v>
       </c>
       <c r="B33" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4097,21 +4097,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>746353</v>
+        <v>746304</v>
       </c>
       <c r="R33" t="n">
-        <v>7152592</v>
+        <v>7152657</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4183,10 +4183,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120086259</v>
+        <v>120086277</v>
       </c>
       <c r="B34" t="n">
-        <v>91850</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4199,21 +4199,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>746394</v>
+        <v>746302</v>
       </c>
       <c r="R34" t="n">
-        <v>7152581</v>
+        <v>7152670</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4285,10 +4285,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120086277</v>
+        <v>120080342</v>
       </c>
       <c r="B35" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4297,25 +4297,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4325,10 +4325,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>746302</v>
+        <v>746478</v>
       </c>
       <c r="R35" t="n">
-        <v>7152670</v>
+        <v>7152487</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4375,22 +4375,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120080342</v>
+        <v>120086259</v>
       </c>
       <c r="B36" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4399,25 +4399,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4427,10 +4427,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>746478</v>
+        <v>746394</v>
       </c>
       <c r="R36" t="n">
-        <v>7152487</v>
+        <v>7152581</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4477,12 +4477,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -5342,10 +5342,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120094907</v>
+        <v>120079805</v>
       </c>
       <c r="B45" t="n">
-        <v>91858</v>
+        <v>92048</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5354,44 +5354,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>746484</v>
+        <v>746437</v>
       </c>
       <c r="R45" t="n">
-        <v>7152510</v>
+        <v>7152508</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5429,29 +5426,28 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120079805</v>
+        <v>120094907</v>
       </c>
       <c r="B46" t="n">
-        <v>92048</v>
+        <v>91858</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5460,41 +5456,44 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>746437</v>
+        <v>746484</v>
       </c>
       <c r="R46" t="n">
-        <v>7152508</v>
+        <v>7152510</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5532,18 +5531,19 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -6804,10 +6804,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120094916</v>
+        <v>120080295</v>
       </c>
       <c r="B59" t="n">
-        <v>91902</v>
+        <v>57473</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6820,26 +6820,31 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6847,10 +6852,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>746490</v>
+        <v>746385</v>
       </c>
       <c r="R59" t="n">
-        <v>7152513</v>
+        <v>7152570</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6891,26 +6896,25 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120079802</v>
+        <v>120094916</v>
       </c>
       <c r="B60" t="n">
         <v>91902</v>
@@ -6944,19 +6948,22 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>746495</v>
+        <v>746490</v>
       </c>
       <c r="R60" t="n">
-        <v>7152470</v>
+        <v>7152513</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6994,28 +7001,29 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120080295</v>
+        <v>120079802</v>
       </c>
       <c r="B61" t="n">
-        <v>57473</v>
+        <v>91902</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7028,45 +7036,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>5449</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>746385</v>
+        <v>746495</v>
       </c>
       <c r="R61" t="n">
-        <v>7152570</v>
+        <v>7152470</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7110,12 +7110,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7428,7 +7428,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120086274</v>
+        <v>120086278</v>
       </c>
       <c r="B65" t="n">
         <v>78542</v>
@@ -7468,10 +7468,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>746478</v>
+        <v>746365</v>
       </c>
       <c r="R65" t="n">
-        <v>7152496</v>
+        <v>7152695</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7530,7 +7530,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120086278</v>
+        <v>120086274</v>
       </c>
       <c r="B66" t="n">
         <v>78542</v>
@@ -7570,10 +7570,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>746365</v>
+        <v>746478</v>
       </c>
       <c r="R66" t="n">
-        <v>7152695</v>
+        <v>7152496</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7734,7 +7734,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120080349</v>
+        <v>120094932</v>
       </c>
       <c r="B68" t="n">
         <v>91858</v>
@@ -7768,16 +7768,19 @@
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>746540</v>
+        <v>746414</v>
       </c>
       <c r="R68" t="n">
-        <v>7152444</v>
+        <v>7152584</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7818,25 +7821,26 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120094932</v>
+        <v>120094855</v>
       </c>
       <c r="B69" t="n">
         <v>91858</v>
@@ -7879,10 +7883,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>746414</v>
+        <v>746547</v>
       </c>
       <c r="R69" t="n">
-        <v>7152584</v>
+        <v>7152471</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7942,10 +7946,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120094855</v>
+        <v>120086279</v>
       </c>
       <c r="B70" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7954,41 +7958,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>746547</v>
+        <v>746397</v>
       </c>
       <c r="R70" t="n">
-        <v>7152471</v>
+        <v>7152654</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8029,7 +8030,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8048,10 +8048,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120086279</v>
+        <v>120086245</v>
       </c>
       <c r="B71" t="n">
-        <v>78542</v>
+        <v>91902</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8064,21 +8064,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8088,10 +8088,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>746397</v>
+        <v>746365</v>
       </c>
       <c r="R71" t="n">
-        <v>7152654</v>
+        <v>7152575</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8460,10 +8460,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120086245</v>
+        <v>120080349</v>
       </c>
       <c r="B75" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8472,25 +8472,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8500,10 +8500,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>746365</v>
+        <v>746540</v>
       </c>
       <c r="R75" t="n">
-        <v>7152575</v>
+        <v>7152444</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8550,22 +8550,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120086291</v>
+        <v>120094951</v>
       </c>
       <c r="B76" t="n">
-        <v>90825</v>
+        <v>91858</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8574,38 +8574,41 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>746502</v>
+        <v>746357</v>
       </c>
       <c r="R76" t="n">
-        <v>7152478</v>
+        <v>7152686</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8646,6 +8649,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8664,7 +8668,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120094951</v>
+        <v>120079812</v>
       </c>
       <c r="B77" t="n">
         <v>91858</v>
@@ -8698,22 +8702,19 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>746357</v>
+        <v>746540</v>
       </c>
       <c r="R77" t="n">
-        <v>7152686</v>
+        <v>7152434</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8758,22 +8759,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120079812</v>
+        <v>120086291</v>
       </c>
       <c r="B78" t="n">
-        <v>91858</v>
+        <v>90825</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8782,25 +8783,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8810,13 +8811,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>746540</v>
+        <v>746502</v>
       </c>
       <c r="R78" t="n">
-        <v>7152434</v>
+        <v>7152478</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8854,19 +8855,18 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>

--- a/artfynd/A 41672-2024 artfynd.xlsx
+++ b/artfynd/A 41672-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120067262</v>
+        <v>120069457</v>
       </c>
       <c r="B2" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>746520</v>
+        <v>746379</v>
       </c>
       <c r="R2" t="n">
-        <v>7152494</v>
+        <v>7152575</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120067430</v>
+        <v>120067841</v>
       </c>
       <c r="B3" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>746505</v>
+        <v>746469</v>
       </c>
       <c r="R3" t="n">
-        <v>7152499</v>
+        <v>7152569</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120068365</v>
+        <v>120067504</v>
       </c>
       <c r="B4" t="n">
-        <v>91902</v>
+        <v>91874</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>746323</v>
+        <v>746486</v>
       </c>
       <c r="R4" t="n">
-        <v>7152700</v>
+        <v>7152501</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120068346</v>
+        <v>120068383</v>
       </c>
       <c r="B5" t="n">
-        <v>91870</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>746324</v>
+        <v>746313</v>
       </c>
       <c r="R5" t="n">
-        <v>7152703</v>
+        <v>7152706</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120068255</v>
+        <v>120068080</v>
       </c>
       <c r="B6" t="n">
         <v>91858</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>746352</v>
+        <v>746371</v>
       </c>
       <c r="R6" t="n">
-        <v>7152686</v>
+        <v>7152632</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120069608</v>
+        <v>120067935</v>
       </c>
       <c r="B7" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>746422</v>
+        <v>746381</v>
       </c>
       <c r="R7" t="n">
-        <v>7152546</v>
+        <v>7152596</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,7 +1347,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120066631</v>
+        <v>120068255</v>
       </c>
       <c r="B8" t="n">
         <v>91858</v>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>746551</v>
+        <v>746352</v>
       </c>
       <c r="R8" t="n">
-        <v>7152434</v>
+        <v>7152686</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120067979</v>
+        <v>120068460</v>
       </c>
       <c r="B9" t="n">
         <v>91858</v>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>746392</v>
+        <v>746312</v>
       </c>
       <c r="R9" t="n">
-        <v>7152615</v>
+        <v>7152709</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120068300</v>
+        <v>120067262</v>
       </c>
       <c r="B10" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,25 +1583,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>746336</v>
+        <v>746520</v>
       </c>
       <c r="R10" t="n">
-        <v>7152676</v>
+        <v>7152494</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120068460</v>
+        <v>120067885</v>
       </c>
       <c r="B11" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,25 +1695,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>746312</v>
+        <v>746399</v>
       </c>
       <c r="R11" t="n">
-        <v>7152709</v>
+        <v>7152617</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,7 +1795,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120067568</v>
+        <v>120068331</v>
       </c>
       <c r="B12" t="n">
         <v>91858</v>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>746484</v>
+        <v>746318</v>
       </c>
       <c r="R12" t="n">
-        <v>7152500</v>
+        <v>7152701</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120068331</v>
+        <v>120068300</v>
       </c>
       <c r="B13" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,25 +1919,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>746318</v>
+        <v>746336</v>
       </c>
       <c r="R13" t="n">
-        <v>7152701</v>
+        <v>7152676</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,7 +2019,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120067841</v>
+        <v>120069348</v>
       </c>
       <c r="B14" t="n">
         <v>91858</v>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>746469</v>
+        <v>746382</v>
       </c>
       <c r="R14" t="n">
-        <v>7152569</v>
+        <v>7152570</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120069457</v>
+        <v>120067568</v>
       </c>
       <c r="B15" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2143,25 +2143,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>746379</v>
+        <v>746484</v>
       </c>
       <c r="R15" t="n">
-        <v>7152575</v>
+        <v>7152500</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120066896</v>
+        <v>120068365</v>
       </c>
       <c r="B16" t="n">
-        <v>91881</v>
+        <v>91902</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,21 +2259,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>746537</v>
+        <v>746323</v>
       </c>
       <c r="R16" t="n">
-        <v>7152456</v>
+        <v>7152700</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120068383</v>
+        <v>120067430</v>
       </c>
       <c r="B17" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2367,25 +2367,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>746313</v>
+        <v>746505</v>
       </c>
       <c r="R17" t="n">
-        <v>7152706</v>
+        <v>7152499</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120067137</v>
+        <v>120066896</v>
       </c>
       <c r="B18" t="n">
-        <v>91852</v>
+        <v>91881</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2483,21 +2483,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>746520</v>
+        <v>746537</v>
       </c>
       <c r="R18" t="n">
-        <v>7152487</v>
+        <v>7152456</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,7 +2579,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120067935</v>
+        <v>120068133</v>
       </c>
       <c r="B19" t="n">
         <v>91858</v>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>746381</v>
+        <v>746333</v>
       </c>
       <c r="R19" t="n">
-        <v>7152596</v>
+        <v>7152647</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,7 +2691,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120068133</v>
+        <v>120067979</v>
       </c>
       <c r="B20" t="n">
         <v>91858</v>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>746333</v>
+        <v>746392</v>
       </c>
       <c r="R20" t="n">
-        <v>7152647</v>
+        <v>7152615</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120067885</v>
+        <v>120069608</v>
       </c>
       <c r="B21" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2819,21 +2819,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>746399</v>
+        <v>746422</v>
       </c>
       <c r="R21" t="n">
-        <v>7152617</v>
+        <v>7152546</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120067504</v>
+        <v>120067137</v>
       </c>
       <c r="B22" t="n">
-        <v>91874</v>
+        <v>91852</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>746486</v>
+        <v>746520</v>
       </c>
       <c r="R22" t="n">
-        <v>7152501</v>
+        <v>7152487</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,7 +3027,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120069348</v>
+        <v>120066631</v>
       </c>
       <c r="B23" t="n">
         <v>91858</v>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>746382</v>
+        <v>746551</v>
       </c>
       <c r="R23" t="n">
-        <v>7152570</v>
+        <v>7152434</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,10 +3139,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120068080</v>
+        <v>120068346</v>
       </c>
       <c r="B24" t="n">
-        <v>91858</v>
+        <v>91870</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>746371</v>
+        <v>746324</v>
       </c>
       <c r="R24" t="n">
-        <v>7152632</v>
+        <v>7152703</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3363,7 +3363,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120080345</v>
+        <v>120080340</v>
       </c>
       <c r="B26" t="n">
         <v>91858</v>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>746459</v>
+        <v>746398</v>
       </c>
       <c r="R26" t="n">
-        <v>7152465</v>
+        <v>7152548</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3465,10 +3465,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120080348</v>
+        <v>120079802</v>
       </c>
       <c r="B27" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3477,25 +3477,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3505,13 +3505,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>746505</v>
+        <v>746495</v>
       </c>
       <c r="R27" t="n">
-        <v>7152451</v>
+        <v>7152470</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3555,22 +3555,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120086295</v>
+        <v>120080307</v>
       </c>
       <c r="B28" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3579,25 +3579,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>746365</v>
+        <v>746426</v>
       </c>
       <c r="R28" t="n">
-        <v>7152695</v>
+        <v>7152510</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3657,22 +3657,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120080346</v>
+        <v>120086238</v>
       </c>
       <c r="B29" t="n">
-        <v>91858</v>
+        <v>57473</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3681,38 +3681,46 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>746461</v>
+        <v>746509</v>
       </c>
       <c r="R29" t="n">
-        <v>7152458</v>
+        <v>7152434</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3747,6 +3755,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Två</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3759,22 +3772,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120094897</v>
+        <v>120094916</v>
       </c>
       <c r="B30" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3783,25 +3796,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3814,10 +3827,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>746482</v>
+        <v>746490</v>
       </c>
       <c r="R30" t="n">
-        <v>7152467</v>
+        <v>7152513</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3877,10 +3890,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120086265</v>
+        <v>120094945</v>
       </c>
       <c r="B31" t="n">
-        <v>78279</v>
+        <v>91902</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3893,34 +3906,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>5449</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>746353</v>
+        <v>746417</v>
       </c>
       <c r="R31" t="n">
-        <v>7152592</v>
+        <v>7152628</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3961,6 +3977,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3979,10 +3996,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120086263</v>
+        <v>120079809</v>
       </c>
       <c r="B32" t="n">
-        <v>92048</v>
+        <v>90730</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3991,41 +4008,44 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>746450</v>
+        <v>746368</v>
       </c>
       <c r="R32" t="n">
-        <v>7152549</v>
+        <v>7152599</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4063,28 +4083,29 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120086276</v>
+        <v>120094922</v>
       </c>
       <c r="B33" t="n">
-        <v>78542</v>
+        <v>91902</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4097,34 +4118,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>746304</v>
+        <v>746442</v>
       </c>
       <c r="R33" t="n">
-        <v>7152657</v>
+        <v>7152565</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4165,6 +4189,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4183,10 +4208,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120086277</v>
+        <v>120086298</v>
       </c>
       <c r="B34" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4195,25 +4220,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4223,10 +4248,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>746302</v>
+        <v>746527</v>
       </c>
       <c r="R34" t="n">
-        <v>7152670</v>
+        <v>7152434</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4285,7 +4310,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120080342</v>
+        <v>120086297</v>
       </c>
       <c r="B35" t="n">
         <v>91858</v>
@@ -4325,10 +4350,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>746478</v>
+        <v>746473</v>
       </c>
       <c r="R35" t="n">
-        <v>7152487</v>
+        <v>7152499</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4375,22 +4400,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120086259</v>
+        <v>120094897</v>
       </c>
       <c r="B36" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4399,38 +4424,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>746394</v>
+        <v>746482</v>
       </c>
       <c r="R36" t="n">
-        <v>7152581</v>
+        <v>7152467</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4471,6 +4499,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4489,10 +4518,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120094922</v>
+        <v>120080349</v>
       </c>
       <c r="B37" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4501,41 +4530,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>746442</v>
+        <v>746540</v>
       </c>
       <c r="R37" t="n">
-        <v>7152565</v>
+        <v>7152444</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4576,29 +4602,28 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120086280</v>
+        <v>120079813</v>
       </c>
       <c r="B38" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4607,25 +4632,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4635,13 +4660,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>746527</v>
+        <v>746517</v>
       </c>
       <c r="R38" t="n">
-        <v>7152434</v>
+        <v>7152485</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4685,22 +4710,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120094945</v>
+        <v>120086276</v>
       </c>
       <c r="B39" t="n">
-        <v>91902</v>
+        <v>78542</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4713,37 +4738,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>746417</v>
+        <v>746304</v>
       </c>
       <c r="R39" t="n">
-        <v>7152628</v>
+        <v>7152657</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4784,7 +4806,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4803,10 +4824,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120086294</v>
+        <v>120086272</v>
       </c>
       <c r="B40" t="n">
-        <v>91858</v>
+        <v>74640</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4819,21 +4840,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4843,10 +4864,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>746310</v>
+        <v>746357</v>
       </c>
       <c r="R40" t="n">
-        <v>7152670</v>
+        <v>7152581</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4905,7 +4926,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120086297</v>
+        <v>120094907</v>
       </c>
       <c r="B41" t="n">
         <v>91858</v>
@@ -4939,16 +4960,19 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>746473</v>
+        <v>746484</v>
       </c>
       <c r="R41" t="n">
-        <v>7152499</v>
+        <v>7152510</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4989,6 +5013,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5007,10 +5032,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120080319</v>
+        <v>120080306</v>
       </c>
       <c r="B42" t="n">
-        <v>92048</v>
+        <v>91902</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5023,21 +5048,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2079</v>
+        <v>5449</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5047,7 +5072,7 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>746477</v>
+        <v>746490</v>
       </c>
       <c r="R42" t="n">
         <v>7152502</v>
@@ -5085,11 +5110,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På kolad tallstubbe</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5098,26 +5118,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL42" t="inlineStr">
-        <is>
-          <t>Kolad tallstubbe</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Kolad tallstubbe</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5134,10 +5134,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120080338</v>
+        <v>120086245</v>
       </c>
       <c r="B43" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5146,25 +5146,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5174,10 +5174,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>746455</v>
+        <v>746365</v>
       </c>
       <c r="R43" t="n">
-        <v>7152561</v>
+        <v>7152575</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5224,19 +5224,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120094869</v>
+        <v>120094932</v>
       </c>
       <c r="B44" t="n">
         <v>91858</v>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>746522</v>
+        <v>746414</v>
       </c>
       <c r="R44" t="n">
-        <v>7152453</v>
+        <v>7152584</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5342,10 +5342,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120079805</v>
+        <v>120086266</v>
       </c>
       <c r="B45" t="n">
-        <v>92048</v>
+        <v>91881</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5358,21 +5358,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2079</v>
+        <v>5966</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5382,13 +5382,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>746437</v>
+        <v>746429</v>
       </c>
       <c r="R45" t="n">
-        <v>7152508</v>
+        <v>7152625</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5432,22 +5432,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120094907</v>
+        <v>120086265</v>
       </c>
       <c r="B46" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5456,41 +5456,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>746484</v>
+        <v>746353</v>
       </c>
       <c r="R46" t="n">
-        <v>7152510</v>
+        <v>7152592</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5531,7 +5528,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5550,7 +5546,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120094901</v>
+        <v>120094886</v>
       </c>
       <c r="B47" t="n">
         <v>91858</v>
@@ -5593,10 +5589,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>746487</v>
+        <v>746500</v>
       </c>
       <c r="R47" t="n">
-        <v>7152494</v>
+        <v>7152466</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5656,10 +5652,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120086296</v>
+        <v>120086259</v>
       </c>
       <c r="B48" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5668,25 +5664,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5696,10 +5692,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>746425</v>
+        <v>746394</v>
       </c>
       <c r="R48" t="n">
-        <v>7152621</v>
+        <v>7152581</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5758,10 +5754,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120079813</v>
+        <v>120086246</v>
       </c>
       <c r="B49" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5770,25 +5766,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5798,13 +5794,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>746517</v>
+        <v>746475</v>
       </c>
       <c r="R49" t="n">
-        <v>7152485</v>
+        <v>7152487</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5848,22 +5844,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120086238</v>
+        <v>120086263</v>
       </c>
       <c r="B50" t="n">
-        <v>57473</v>
+        <v>92048</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5876,42 +5872,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>2079</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>746509</v>
+        <v>746450</v>
       </c>
       <c r="R50" t="n">
-        <v>7152434</v>
+        <v>7152549</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5944,11 +5932,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Två</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5975,10 +5958,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120086269</v>
+        <v>120086296</v>
       </c>
       <c r="B51" t="n">
-        <v>88170</v>
+        <v>91858</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5987,41 +5970,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>746365</v>
+        <v>746425</v>
       </c>
       <c r="R51" t="n">
-        <v>7152575</v>
+        <v>7152621</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6056,18 +6036,12 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Inte ihålig men övriga karaktärer stämde.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6086,10 +6060,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120079797</v>
+        <v>120086295</v>
       </c>
       <c r="B52" t="n">
-        <v>89650</v>
+        <v>91858</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6098,25 +6072,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6126,13 +6100,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>746432</v>
+        <v>746365</v>
       </c>
       <c r="R52" t="n">
-        <v>7152509</v>
+        <v>7152695</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6176,22 +6150,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120094886</v>
+        <v>120086277</v>
       </c>
       <c r="B53" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6200,41 +6174,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>746500</v>
+        <v>746302</v>
       </c>
       <c r="R53" t="n">
-        <v>7152466</v>
+        <v>7152670</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6275,7 +6246,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6294,10 +6264,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120080336</v>
+        <v>120086269</v>
       </c>
       <c r="B54" t="n">
-        <v>91858</v>
+        <v>88170</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6306,38 +6276,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>746545</v>
+        <v>746365</v>
       </c>
       <c r="R54" t="n">
-        <v>7152464</v>
+        <v>7152575</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6372,34 +6345,40 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Inte ihålig men övriga karaktärer stämde.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120086228</v>
+        <v>120086278</v>
       </c>
       <c r="B55" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6412,21 +6391,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6436,10 +6415,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>746357</v>
+        <v>746365</v>
       </c>
       <c r="R55" t="n">
-        <v>7152581</v>
+        <v>7152695</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6498,10 +6477,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120080340</v>
+        <v>120079797</v>
       </c>
       <c r="B56" t="n">
-        <v>91858</v>
+        <v>89650</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6510,25 +6489,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6538,13 +6517,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>746398</v>
+        <v>746432</v>
       </c>
       <c r="R56" t="n">
-        <v>7152548</v>
+        <v>7152509</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6588,22 +6567,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120086272</v>
+        <v>120086274</v>
       </c>
       <c r="B57" t="n">
-        <v>74640</v>
+        <v>78542</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6612,25 +6591,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6640,10 +6619,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>746357</v>
+        <v>746478</v>
       </c>
       <c r="R57" t="n">
-        <v>7152581</v>
+        <v>7152496</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6702,10 +6681,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120086298</v>
+        <v>120086279</v>
       </c>
       <c r="B58" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6714,25 +6693,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6742,10 +6721,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>746527</v>
+        <v>746397</v>
       </c>
       <c r="R58" t="n">
-        <v>7152434</v>
+        <v>7152654</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6804,10 +6783,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120080295</v>
+        <v>120080326</v>
       </c>
       <c r="B59" t="n">
-        <v>57473</v>
+        <v>89247</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6816,46 +6795,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>1596</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>746385</v>
+        <v>746543</v>
       </c>
       <c r="R59" t="n">
-        <v>7152570</v>
+        <v>7152437</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6914,10 +6885,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120094916</v>
+        <v>120086291</v>
       </c>
       <c r="B60" t="n">
-        <v>91902</v>
+        <v>90825</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6926,41 +6897,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5449</v>
+        <v>65</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>746490</v>
+        <v>746502</v>
       </c>
       <c r="R60" t="n">
-        <v>7152513</v>
+        <v>7152478</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7001,7 +6969,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7020,10 +6987,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120079802</v>
+        <v>120086280</v>
       </c>
       <c r="B61" t="n">
-        <v>91902</v>
+        <v>78542</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7036,21 +7003,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7060,13 +7027,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>746495</v>
+        <v>746527</v>
       </c>
       <c r="R61" t="n">
-        <v>7152470</v>
+        <v>7152434</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7110,22 +7077,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120080326</v>
+        <v>120080319</v>
       </c>
       <c r="B62" t="n">
-        <v>89247</v>
+        <v>92048</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7134,25 +7101,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1596</v>
+        <v>2079</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7162,10 +7129,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>746543</v>
+        <v>746477</v>
       </c>
       <c r="R62" t="n">
-        <v>7152437</v>
+        <v>7152502</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7200,6 +7167,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På kolad tallstubbe</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7208,6 +7180,26 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL62" t="inlineStr">
+        <is>
+          <t>Kolad tallstubbe</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Kolad tallstubbe</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7224,10 +7216,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120086230</v>
+        <v>120080345</v>
       </c>
       <c r="B63" t="n">
-        <v>90545</v>
+        <v>91858</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7240,21 +7232,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7264,10 +7256,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>746412</v>
+        <v>746459</v>
       </c>
       <c r="R63" t="n">
-        <v>7152564</v>
+        <v>7152465</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7314,19 +7306,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120080343</v>
+        <v>120080341</v>
       </c>
       <c r="B64" t="n">
         <v>91858</v>
@@ -7366,10 +7358,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>746467</v>
+        <v>746384</v>
       </c>
       <c r="R64" t="n">
-        <v>7152466</v>
+        <v>7152544</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7428,10 +7420,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120086278</v>
+        <v>120086294</v>
       </c>
       <c r="B65" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7440,25 +7432,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7468,10 +7460,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>746365</v>
+        <v>746310</v>
       </c>
       <c r="R65" t="n">
-        <v>7152695</v>
+        <v>7152670</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7530,10 +7522,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120086274</v>
+        <v>120094855</v>
       </c>
       <c r="B66" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7542,38 +7534,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>746478</v>
+        <v>746547</v>
       </c>
       <c r="R66" t="n">
-        <v>7152496</v>
+        <v>7152471</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7614,6 +7609,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7632,10 +7628,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120080307</v>
+        <v>120094951</v>
       </c>
       <c r="B67" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7644,38 +7640,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>746426</v>
+        <v>746357</v>
       </c>
       <c r="R67" t="n">
-        <v>7152510</v>
+        <v>7152686</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7716,25 +7715,26 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120094932</v>
+        <v>120080343</v>
       </c>
       <c r="B68" t="n">
         <v>91858</v>
@@ -7768,19 +7768,16 @@
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>746414</v>
+        <v>746467</v>
       </c>
       <c r="R68" t="n">
-        <v>7152584</v>
+        <v>7152466</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7821,26 +7818,25 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120094855</v>
+        <v>120094939</v>
       </c>
       <c r="B69" t="n">
         <v>91858</v>
@@ -7883,10 +7879,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>746547</v>
+        <v>746413</v>
       </c>
       <c r="R69" t="n">
-        <v>7152471</v>
+        <v>7152616</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7946,10 +7942,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120086279</v>
+        <v>120094869</v>
       </c>
       <c r="B70" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7958,38 +7954,41 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>746397</v>
+        <v>746522</v>
       </c>
       <c r="R70" t="n">
-        <v>7152654</v>
+        <v>7152453</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8030,6 +8029,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8048,10 +8048,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120086245</v>
+        <v>120080338</v>
       </c>
       <c r="B71" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8060,25 +8060,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8088,10 +8088,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>746365</v>
+        <v>746455</v>
       </c>
       <c r="R71" t="n">
-        <v>7152575</v>
+        <v>7152561</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8138,22 +8138,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120080306</v>
+        <v>120086275</v>
       </c>
       <c r="B72" t="n">
-        <v>91902</v>
+        <v>78542</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8166,21 +8166,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8190,10 +8190,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>746490</v>
+        <v>746370</v>
       </c>
       <c r="R72" t="n">
-        <v>7152502</v>
+        <v>7152601</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8240,22 +8240,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120086246</v>
+        <v>120086228</v>
       </c>
       <c r="B73" t="n">
-        <v>91902</v>
+        <v>74654</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8268,21 +8268,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5449</v>
+        <v>6440</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8292,10 +8292,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>746475</v>
+        <v>746357</v>
       </c>
       <c r="R73" t="n">
-        <v>7152487</v>
+        <v>7152581</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8354,10 +8354,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120079809</v>
+        <v>120079805</v>
       </c>
       <c r="B74" t="n">
-        <v>90730</v>
+        <v>92048</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8366,41 +8366,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>746368</v>
+        <v>746437</v>
       </c>
       <c r="R74" t="n">
-        <v>7152599</v>
+        <v>7152508</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8441,7 +8438,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8460,7 +8456,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120080349</v>
+        <v>120094959</v>
       </c>
       <c r="B75" t="n">
         <v>91858</v>
@@ -8494,16 +8490,19 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>746540</v>
+        <v>746300</v>
       </c>
       <c r="R75" t="n">
-        <v>7152444</v>
+        <v>7152654</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8544,25 +8543,26 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120094951</v>
+        <v>120094901</v>
       </c>
       <c r="B76" t="n">
         <v>91858</v>
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>746357</v>
+        <v>746487</v>
       </c>
       <c r="R76" t="n">
-        <v>7152686</v>
+        <v>7152494</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8668,7 +8668,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120079812</v>
+        <v>120080346</v>
       </c>
       <c r="B77" t="n">
         <v>91858</v>
@@ -8708,13 +8708,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>746540</v>
+        <v>746461</v>
       </c>
       <c r="R77" t="n">
-        <v>7152434</v>
+        <v>7152458</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8752,29 +8752,28 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120086291</v>
+        <v>120079812</v>
       </c>
       <c r="B78" t="n">
-        <v>90825</v>
+        <v>91858</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8783,25 +8782,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8811,13 +8810,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>746502</v>
+        <v>746540</v>
       </c>
       <c r="R78" t="n">
-        <v>7152478</v>
+        <v>7152434</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8855,28 +8854,29 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120080337</v>
+        <v>120080295</v>
       </c>
       <c r="B79" t="n">
-        <v>91858</v>
+        <v>57473</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8885,38 +8885,46 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>746488</v>
+        <v>746385</v>
       </c>
       <c r="R79" t="n">
-        <v>7152500</v>
+        <v>7152570</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8975,10 +8983,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120086275</v>
+        <v>120080336</v>
       </c>
       <c r="B80" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8987,25 +8995,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9015,10 +9023,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>746370</v>
+        <v>746545</v>
       </c>
       <c r="R80" t="n">
-        <v>7152601</v>
+        <v>7152464</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9065,19 +9073,19 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120094959</v>
+        <v>120080348</v>
       </c>
       <c r="B81" t="n">
         <v>91858</v>
@@ -9111,19 +9119,16 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>746300</v>
+        <v>746505</v>
       </c>
       <c r="R81" t="n">
-        <v>7152654</v>
+        <v>7152451</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9164,29 +9169,28 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120080341</v>
+        <v>120086230</v>
       </c>
       <c r="B82" t="n">
-        <v>91858</v>
+        <v>90545</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9199,21 +9203,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9223,10 +9227,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>746384</v>
+        <v>746412</v>
       </c>
       <c r="R82" t="n">
-        <v>7152544</v>
+        <v>7152564</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9273,19 +9277,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120094849</v>
+        <v>120080342</v>
       </c>
       <c r="B83" t="n">
         <v>91858</v>
@@ -9319,19 +9323,16 @@
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>746531</v>
+        <v>746478</v>
       </c>
       <c r="R83" t="n">
-        <v>7152454</v>
+        <v>7152487</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9372,26 +9373,25 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120094939</v>
+        <v>120094849</v>
       </c>
       <c r="B84" t="n">
         <v>91858</v>
@@ -9434,10 +9434,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>746413</v>
+        <v>746531</v>
       </c>
       <c r="R84" t="n">
-        <v>7152616</v>
+        <v>7152454</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9497,10 +9497,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120086266</v>
+        <v>120080337</v>
       </c>
       <c r="B85" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9509,25 +9509,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9537,10 +9537,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>746429</v>
+        <v>746488</v>
       </c>
       <c r="R85" t="n">
-        <v>7152625</v>
+        <v>7152500</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9587,12 +9587,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>

--- a/artfynd/A 41672-2024 artfynd.xlsx
+++ b/artfynd/A 41672-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120069457</v>
+        <v>120068383</v>
       </c>
       <c r="B2" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>746379</v>
+        <v>746313</v>
       </c>
       <c r="R2" t="n">
-        <v>7152575</v>
+        <v>7152706</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120067841</v>
+        <v>120067137</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>746469</v>
+        <v>746520</v>
       </c>
       <c r="R3" t="n">
-        <v>7152569</v>
+        <v>7152487</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120067504</v>
+        <v>120068346</v>
       </c>
       <c r="B4" t="n">
-        <v>91874</v>
+        <v>91870</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>746486</v>
+        <v>746324</v>
       </c>
       <c r="R4" t="n">
-        <v>7152501</v>
+        <v>7152703</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120068383</v>
+        <v>120066631</v>
       </c>
       <c r="B5" t="n">
         <v>91858</v>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>746313</v>
+        <v>746551</v>
       </c>
       <c r="R5" t="n">
-        <v>7152706</v>
+        <v>7152434</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120068080</v>
+        <v>120069608</v>
       </c>
       <c r="B6" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>746371</v>
+        <v>746422</v>
       </c>
       <c r="R6" t="n">
-        <v>7152632</v>
+        <v>7152546</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120067935</v>
+        <v>120067885</v>
       </c>
       <c r="B7" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>746381</v>
+        <v>746399</v>
       </c>
       <c r="R7" t="n">
-        <v>7152596</v>
+        <v>7152617</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120068255</v>
+        <v>120068300</v>
       </c>
       <c r="B8" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>746352</v>
+        <v>746336</v>
       </c>
       <c r="R8" t="n">
-        <v>7152686</v>
+        <v>7152676</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120068460</v>
+        <v>120068080</v>
       </c>
       <c r="B9" t="n">
         <v>91858</v>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>746312</v>
+        <v>746371</v>
       </c>
       <c r="R9" t="n">
-        <v>7152709</v>
+        <v>7152632</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120067885</v>
+        <v>120067935</v>
       </c>
       <c r="B11" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,25 +1695,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>746399</v>
+        <v>746381</v>
       </c>
       <c r="R11" t="n">
-        <v>7152617</v>
+        <v>7152596</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120068331</v>
+        <v>120067430</v>
       </c>
       <c r="B12" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,25 +1807,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>746318</v>
+        <v>746505</v>
       </c>
       <c r="R12" t="n">
-        <v>7152701</v>
+        <v>7152499</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120068300</v>
+        <v>120068602</v>
       </c>
       <c r="B13" t="n">
-        <v>91881</v>
+        <v>79652</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,25 +1919,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5966</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>746336</v>
+        <v>746307</v>
       </c>
       <c r="R13" t="n">
-        <v>7152676</v>
+        <v>7152647</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,7 +2019,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120069348</v>
+        <v>120068460</v>
       </c>
       <c r="B14" t="n">
         <v>91858</v>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>746382</v>
+        <v>746312</v>
       </c>
       <c r="R14" t="n">
-        <v>7152570</v>
+        <v>7152709</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,7 +2131,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120067568</v>
+        <v>120068133</v>
       </c>
       <c r="B15" t="n">
         <v>91858</v>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>746484</v>
+        <v>746333</v>
       </c>
       <c r="R15" t="n">
-        <v>7152500</v>
+        <v>7152647</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120068365</v>
+        <v>120066896</v>
       </c>
       <c r="B16" t="n">
-        <v>91902</v>
+        <v>91881</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,21 +2259,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>746323</v>
+        <v>746537</v>
       </c>
       <c r="R16" t="n">
-        <v>7152700</v>
+        <v>7152456</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120067430</v>
+        <v>120067979</v>
       </c>
       <c r="B17" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2367,25 +2367,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>746505</v>
+        <v>746392</v>
       </c>
       <c r="R17" t="n">
-        <v>7152499</v>
+        <v>7152615</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120066896</v>
+        <v>120069457</v>
       </c>
       <c r="B18" t="n">
-        <v>91881</v>
+        <v>91874</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2483,21 +2483,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>746537</v>
+        <v>746379</v>
       </c>
       <c r="R18" t="n">
-        <v>7152456</v>
+        <v>7152575</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,7 +2579,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120068133</v>
+        <v>120068331</v>
       </c>
       <c r="B19" t="n">
         <v>91858</v>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>746333</v>
+        <v>746318</v>
       </c>
       <c r="R19" t="n">
-        <v>7152647</v>
+        <v>7152701</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,7 +2691,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120067979</v>
+        <v>120068255</v>
       </c>
       <c r="B20" t="n">
         <v>91858</v>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>746392</v>
+        <v>746352</v>
       </c>
       <c r="R20" t="n">
-        <v>7152615</v>
+        <v>7152686</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120069608</v>
+        <v>120067841</v>
       </c>
       <c r="B21" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2815,25 +2815,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>746422</v>
+        <v>746469</v>
       </c>
       <c r="R21" t="n">
-        <v>7152546</v>
+        <v>7152569</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120067137</v>
+        <v>120067504</v>
       </c>
       <c r="B22" t="n">
-        <v>91852</v>
+        <v>91874</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>746520</v>
+        <v>746486</v>
       </c>
       <c r="R22" t="n">
-        <v>7152487</v>
+        <v>7152501</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,7 +3027,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120066631</v>
+        <v>120069348</v>
       </c>
       <c r="B23" t="n">
         <v>91858</v>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>746551</v>
+        <v>746382</v>
       </c>
       <c r="R23" t="n">
-        <v>7152434</v>
+        <v>7152570</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,10 +3139,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120068346</v>
+        <v>120068365</v>
       </c>
       <c r="B24" t="n">
-        <v>91870</v>
+        <v>91902</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3151,25 +3151,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>746324</v>
+        <v>746323</v>
       </c>
       <c r="R24" t="n">
-        <v>7152703</v>
+        <v>7152700</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3251,10 +3251,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120068602</v>
+        <v>120067568</v>
       </c>
       <c r="B25" t="n">
-        <v>79652</v>
+        <v>91858</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3267,21 +3267,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>746307</v>
+        <v>746484</v>
       </c>
       <c r="R25" t="n">
-        <v>7152647</v>
+        <v>7152500</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3363,7 +3363,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120080340</v>
+        <v>120094869</v>
       </c>
       <c r="B26" t="n">
         <v>91858</v>
@@ -3397,16 +3397,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>746398</v>
+        <v>746522</v>
       </c>
       <c r="R26" t="n">
-        <v>7152548</v>
+        <v>7152453</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3447,28 +3450,29 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120079802</v>
+        <v>120086238</v>
       </c>
       <c r="B27" t="n">
-        <v>91902</v>
+        <v>57473</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3481,37 +3485,45 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>746495</v>
+        <v>746509</v>
       </c>
       <c r="R27" t="n">
-        <v>7152470</v>
+        <v>7152434</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3541,6 +3553,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Två</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3555,22 +3572,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120080307</v>
+        <v>120086298</v>
       </c>
       <c r="B28" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3579,25 +3596,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3607,10 +3624,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>746426</v>
+        <v>746527</v>
       </c>
       <c r="R28" t="n">
-        <v>7152510</v>
+        <v>7152434</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3657,22 +3674,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120086238</v>
+        <v>120080341</v>
       </c>
       <c r="B29" t="n">
-        <v>57473</v>
+        <v>91858</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3681,46 +3698,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>746509</v>
+        <v>746384</v>
       </c>
       <c r="R29" t="n">
-        <v>7152434</v>
+        <v>7152544</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3755,11 +3764,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Två</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3772,22 +3776,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120094916</v>
+        <v>120080342</v>
       </c>
       <c r="B30" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3796,41 +3800,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>746490</v>
+        <v>746478</v>
       </c>
       <c r="R30" t="n">
-        <v>7152513</v>
+        <v>7152487</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3871,29 +3872,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120094945</v>
+        <v>120086269</v>
       </c>
       <c r="B31" t="n">
-        <v>91902</v>
+        <v>88170</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3906,21 +3906,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5449</v>
+        <v>4962</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3933,10 +3933,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>746417</v>
+        <v>746365</v>
       </c>
       <c r="R31" t="n">
-        <v>7152628</v>
+        <v>7152575</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3969,6 +3969,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Inte ihålig men övriga karaktärer stämde.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3996,10 +4001,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120079809</v>
+        <v>120079805</v>
       </c>
       <c r="B32" t="n">
-        <v>90730</v>
+        <v>92048</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4008,41 +4013,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>746368</v>
+        <v>746437</v>
       </c>
       <c r="R32" t="n">
-        <v>7152599</v>
+        <v>7152508</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4083,7 +4085,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4102,7 +4103,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120094922</v>
+        <v>120079802</v>
       </c>
       <c r="B33" t="n">
         <v>91902</v>
@@ -4136,22 +4137,19 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>746442</v>
+        <v>746495</v>
       </c>
       <c r="R33" t="n">
-        <v>7152565</v>
+        <v>7152470</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4189,29 +4187,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120086298</v>
+        <v>120079797</v>
       </c>
       <c r="B34" t="n">
-        <v>91858</v>
+        <v>89650</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4220,25 +4217,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4248,13 +4245,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>746527</v>
+        <v>746432</v>
       </c>
       <c r="R34" t="n">
-        <v>7152434</v>
+        <v>7152509</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4298,19 +4295,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120086297</v>
+        <v>120094939</v>
       </c>
       <c r="B35" t="n">
         <v>91858</v>
@@ -4344,16 +4341,19 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>746473</v>
+        <v>746413</v>
       </c>
       <c r="R35" t="n">
-        <v>7152499</v>
+        <v>7152616</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4394,6 +4394,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4412,10 +4413,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120094897</v>
+        <v>120080307</v>
       </c>
       <c r="B36" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4424,41 +4425,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>746482</v>
+        <v>746426</v>
       </c>
       <c r="R36" t="n">
-        <v>7152467</v>
+        <v>7152510</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4499,29 +4497,28 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120080349</v>
+        <v>120086280</v>
       </c>
       <c r="B37" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4530,25 +4527,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4558,10 +4555,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>746540</v>
+        <v>746527</v>
       </c>
       <c r="R37" t="n">
-        <v>7152444</v>
+        <v>7152434</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4608,19 +4605,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120079813</v>
+        <v>120080345</v>
       </c>
       <c r="B38" t="n">
         <v>91858</v>
@@ -4660,13 +4657,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>746517</v>
+        <v>746459</v>
       </c>
       <c r="R38" t="n">
-        <v>7152485</v>
+        <v>7152465</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4710,22 +4707,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120086276</v>
+        <v>120086296</v>
       </c>
       <c r="B39" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4734,25 +4731,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4762,10 +4759,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>746304</v>
+        <v>746425</v>
       </c>
       <c r="R39" t="n">
-        <v>7152657</v>
+        <v>7152621</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4824,10 +4821,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120086272</v>
+        <v>120079812</v>
       </c>
       <c r="B40" t="n">
-        <v>74640</v>
+        <v>91858</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4840,21 +4837,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>306</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4864,13 +4861,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>746357</v>
+        <v>746540</v>
       </c>
       <c r="R40" t="n">
-        <v>7152581</v>
+        <v>7152434</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4908,25 +4905,26 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120094907</v>
+        <v>120094901</v>
       </c>
       <c r="B41" t="n">
         <v>91858</v>
@@ -4969,10 +4967,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>746484</v>
+        <v>746487</v>
       </c>
       <c r="R41" t="n">
-        <v>7152510</v>
+        <v>7152494</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5032,10 +5030,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120080306</v>
+        <v>120086277</v>
       </c>
       <c r="B42" t="n">
-        <v>91902</v>
+        <v>78542</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5048,21 +5046,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5072,10 +5070,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>746490</v>
+        <v>746302</v>
       </c>
       <c r="R42" t="n">
-        <v>7152502</v>
+        <v>7152670</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5122,22 +5120,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120086245</v>
+        <v>120086265</v>
       </c>
       <c r="B43" t="n">
-        <v>91902</v>
+        <v>78279</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5150,21 +5148,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5174,10 +5172,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>746365</v>
+        <v>746353</v>
       </c>
       <c r="R43" t="n">
-        <v>7152575</v>
+        <v>7152592</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5236,10 +5234,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120094932</v>
+        <v>120086272</v>
       </c>
       <c r="B44" t="n">
-        <v>91858</v>
+        <v>74640</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5252,37 +5250,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>746414</v>
+        <v>746357</v>
       </c>
       <c r="R44" t="n">
-        <v>7152584</v>
+        <v>7152581</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5323,7 +5318,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5342,10 +5336,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120086266</v>
+        <v>120094959</v>
       </c>
       <c r="B45" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5354,38 +5348,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>746429</v>
+        <v>746300</v>
       </c>
       <c r="R45" t="n">
-        <v>7152625</v>
+        <v>7152654</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5426,6 +5423,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5444,10 +5442,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120086265</v>
+        <v>120080348</v>
       </c>
       <c r="B46" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5456,25 +5454,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5484,10 +5482,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>746353</v>
+        <v>746505</v>
       </c>
       <c r="R46" t="n">
-        <v>7152592</v>
+        <v>7152451</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5534,19 +5532,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120094886</v>
+        <v>120080337</v>
       </c>
       <c r="B47" t="n">
         <v>91858</v>
@@ -5580,19 +5578,16 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>746500</v>
+        <v>746488</v>
       </c>
       <c r="R47" t="n">
-        <v>7152466</v>
+        <v>7152500</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5633,29 +5628,28 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120086259</v>
+        <v>120094897</v>
       </c>
       <c r="B48" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5664,38 +5658,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>746394</v>
+        <v>746482</v>
       </c>
       <c r="R48" t="n">
-        <v>7152581</v>
+        <v>7152467</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5736,6 +5733,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5754,10 +5752,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120086246</v>
+        <v>120080336</v>
       </c>
       <c r="B49" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5766,25 +5764,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5794,10 +5792,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>746475</v>
+        <v>746545</v>
       </c>
       <c r="R49" t="n">
-        <v>7152487</v>
+        <v>7152464</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5844,22 +5842,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120086263</v>
+        <v>120086230</v>
       </c>
       <c r="B50" t="n">
-        <v>92048</v>
+        <v>90545</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5868,25 +5866,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5896,10 +5894,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>746450</v>
+        <v>746412</v>
       </c>
       <c r="R50" t="n">
-        <v>7152549</v>
+        <v>7152564</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5958,10 +5956,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120086296</v>
+        <v>120094945</v>
       </c>
       <c r="B51" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5970,38 +5968,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>746425</v>
+        <v>746417</v>
       </c>
       <c r="R51" t="n">
-        <v>7152621</v>
+        <v>7152628</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6042,6 +6043,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6060,10 +6062,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120086295</v>
+        <v>120080306</v>
       </c>
       <c r="B52" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6072,25 +6074,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6100,10 +6102,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>746365</v>
+        <v>746490</v>
       </c>
       <c r="R52" t="n">
-        <v>7152695</v>
+        <v>7152502</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6150,22 +6152,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120086277</v>
+        <v>120080346</v>
       </c>
       <c r="B53" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6174,25 +6176,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6202,10 +6204,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>746302</v>
+        <v>746461</v>
       </c>
       <c r="R53" t="n">
-        <v>7152670</v>
+        <v>7152458</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6252,22 +6254,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120086269</v>
+        <v>120094932</v>
       </c>
       <c r="B54" t="n">
-        <v>88170</v>
+        <v>91858</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6276,25 +6278,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6307,10 +6309,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>746365</v>
+        <v>746414</v>
       </c>
       <c r="R54" t="n">
-        <v>7152575</v>
+        <v>7152584</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6343,11 +6345,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Inte ihålig men övriga karaktärer stämde.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6375,10 +6372,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120086278</v>
+        <v>120094855</v>
       </c>
       <c r="B55" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6387,38 +6384,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>746365</v>
+        <v>746547</v>
       </c>
       <c r="R55" t="n">
-        <v>7152695</v>
+        <v>7152471</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6459,6 +6459,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6477,10 +6478,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120079797</v>
+        <v>120080319</v>
       </c>
       <c r="B56" t="n">
-        <v>89650</v>
+        <v>92048</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6493,21 +6494,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1962</v>
+        <v>2079</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6517,13 +6518,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>746432</v>
+        <v>746477</v>
       </c>
       <c r="R56" t="n">
-        <v>7152509</v>
+        <v>7152502</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6555,6 +6556,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På kolad tallstubbe</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6563,26 +6569,46 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL56" t="inlineStr">
+        <is>
+          <t>Kolad tallstubbe</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Kolad tallstubbe</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120086274</v>
+        <v>120094922</v>
       </c>
       <c r="B57" t="n">
-        <v>78542</v>
+        <v>91902</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6595,34 +6621,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>746478</v>
+        <v>746442</v>
       </c>
       <c r="R57" t="n">
-        <v>7152496</v>
+        <v>7152565</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6663,6 +6692,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6681,10 +6711,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120086279</v>
+        <v>120094916</v>
       </c>
       <c r="B58" t="n">
-        <v>78542</v>
+        <v>91902</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6697,34 +6727,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>746397</v>
+        <v>746490</v>
       </c>
       <c r="R58" t="n">
-        <v>7152654</v>
+        <v>7152513</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6765,6 +6798,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6783,10 +6817,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120080326</v>
+        <v>120086274</v>
       </c>
       <c r="B59" t="n">
-        <v>89247</v>
+        <v>78542</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6795,25 +6829,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1596</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6823,10 +6857,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>746543</v>
+        <v>746478</v>
       </c>
       <c r="R59" t="n">
-        <v>7152437</v>
+        <v>7152496</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6873,22 +6907,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120086291</v>
+        <v>120079813</v>
       </c>
       <c r="B60" t="n">
-        <v>90825</v>
+        <v>91858</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6897,25 +6931,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6925,13 +6959,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>746502</v>
+        <v>746517</v>
       </c>
       <c r="R60" t="n">
-        <v>7152478</v>
+        <v>7152485</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6975,19 +7009,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120086280</v>
+        <v>120086279</v>
       </c>
       <c r="B61" t="n">
         <v>78542</v>
@@ -7027,10 +7061,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>746527</v>
+        <v>746397</v>
       </c>
       <c r="R61" t="n">
-        <v>7152434</v>
+        <v>7152654</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7089,10 +7123,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120080319</v>
+        <v>120086291</v>
       </c>
       <c r="B62" t="n">
-        <v>92048</v>
+        <v>90825</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7101,25 +7135,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2079</v>
+        <v>65</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7129,10 +7163,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>746477</v>
+        <v>746502</v>
       </c>
       <c r="R62" t="n">
-        <v>7152502</v>
+        <v>7152478</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7167,11 +7201,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>På kolad tallstubbe</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7180,46 +7209,26 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL62" t="inlineStr">
-        <is>
-          <t>Kolad tallstubbe</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Kolad tallstubbe</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120080345</v>
+        <v>120086228</v>
       </c>
       <c r="B63" t="n">
-        <v>91858</v>
+        <v>74654</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7228,25 +7237,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>6440</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7256,10 +7265,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>746459</v>
+        <v>746357</v>
       </c>
       <c r="R63" t="n">
-        <v>7152465</v>
+        <v>7152581</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7306,22 +7315,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120080341</v>
+        <v>120086245</v>
       </c>
       <c r="B64" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7330,25 +7339,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7358,10 +7367,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>746384</v>
+        <v>746365</v>
       </c>
       <c r="R64" t="n">
-        <v>7152544</v>
+        <v>7152575</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7408,22 +7417,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120086294</v>
+        <v>120086266</v>
       </c>
       <c r="B65" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7432,25 +7441,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7460,10 +7469,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>746310</v>
+        <v>746429</v>
       </c>
       <c r="R65" t="n">
-        <v>7152670</v>
+        <v>7152625</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7522,10 +7531,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120094855</v>
+        <v>120086275</v>
       </c>
       <c r="B66" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7534,41 +7543,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>746547</v>
+        <v>746370</v>
       </c>
       <c r="R66" t="n">
-        <v>7152471</v>
+        <v>7152601</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7609,7 +7615,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7628,7 +7633,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120094951</v>
+        <v>120086295</v>
       </c>
       <c r="B67" t="n">
         <v>91858</v>
@@ -7662,19 +7667,16 @@
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>746357</v>
+        <v>746365</v>
       </c>
       <c r="R67" t="n">
-        <v>7152686</v>
+        <v>7152695</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7715,7 +7717,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7734,10 +7735,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120080343</v>
+        <v>120080326</v>
       </c>
       <c r="B68" t="n">
-        <v>91858</v>
+        <v>89247</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7746,25 +7747,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>1596</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7774,10 +7775,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>746467</v>
+        <v>746543</v>
       </c>
       <c r="R68" t="n">
-        <v>7152466</v>
+        <v>7152437</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7836,7 +7837,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120094939</v>
+        <v>120094907</v>
       </c>
       <c r="B69" t="n">
         <v>91858</v>
@@ -7879,10 +7880,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>746413</v>
+        <v>746484</v>
       </c>
       <c r="R69" t="n">
-        <v>7152616</v>
+        <v>7152510</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7942,7 +7943,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120094869</v>
+        <v>120086294</v>
       </c>
       <c r="B70" t="n">
         <v>91858</v>
@@ -7976,19 +7977,16 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>746522</v>
+        <v>746310</v>
       </c>
       <c r="R70" t="n">
-        <v>7152453</v>
+        <v>7152670</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8029,7 +8027,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8048,7 +8045,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120080338</v>
+        <v>120086297</v>
       </c>
       <c r="B71" t="n">
         <v>91858</v>
@@ -8088,10 +8085,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>746455</v>
+        <v>746473</v>
       </c>
       <c r="R71" t="n">
-        <v>7152561</v>
+        <v>7152499</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8138,19 +8135,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120086275</v>
+        <v>120086276</v>
       </c>
       <c r="B72" t="n">
         <v>78542</v>
@@ -8190,10 +8187,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>746370</v>
+        <v>746304</v>
       </c>
       <c r="R72" t="n">
-        <v>7152601</v>
+        <v>7152657</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8252,10 +8249,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120086228</v>
+        <v>120080340</v>
       </c>
       <c r="B73" t="n">
-        <v>74654</v>
+        <v>91858</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8264,25 +8261,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8292,10 +8289,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>746357</v>
+        <v>746398</v>
       </c>
       <c r="R73" t="n">
-        <v>7152581</v>
+        <v>7152548</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8342,22 +8339,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120079805</v>
+        <v>120080349</v>
       </c>
       <c r="B74" t="n">
-        <v>92048</v>
+        <v>91858</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8366,25 +8363,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8394,13 +8391,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>746437</v>
+        <v>746540</v>
       </c>
       <c r="R74" t="n">
-        <v>7152508</v>
+        <v>7152444</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8444,22 +8441,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120094959</v>
+        <v>120086263</v>
       </c>
       <c r="B75" t="n">
-        <v>91858</v>
+        <v>92048</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8468,41 +8465,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>746300</v>
+        <v>746450</v>
       </c>
       <c r="R75" t="n">
-        <v>7152654</v>
+        <v>7152549</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8543,7 +8537,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8562,10 +8555,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120094901</v>
+        <v>120079809</v>
       </c>
       <c r="B76" t="n">
-        <v>91858</v>
+        <v>90730</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8574,25 +8567,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8605,13 +8598,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>746487</v>
+        <v>746368</v>
       </c>
       <c r="R76" t="n">
-        <v>7152494</v>
+        <v>7152599</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8656,22 +8649,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120080346</v>
+        <v>120086278</v>
       </c>
       <c r="B77" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8680,25 +8673,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8708,10 +8701,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>746461</v>
+        <v>746365</v>
       </c>
       <c r="R77" t="n">
-        <v>7152458</v>
+        <v>7152695</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8758,19 +8751,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120079812</v>
+        <v>120080343</v>
       </c>
       <c r="B78" t="n">
         <v>91858</v>
@@ -8810,13 +8803,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>746540</v>
+        <v>746467</v>
       </c>
       <c r="R78" t="n">
-        <v>7152434</v>
+        <v>7152466</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8854,29 +8847,28 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120080295</v>
+        <v>120086246</v>
       </c>
       <c r="B79" t="n">
-        <v>57473</v>
+        <v>91902</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8889,42 +8881,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103021</v>
+        <v>5449</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>746385</v>
+        <v>746475</v>
       </c>
       <c r="R79" t="n">
-        <v>7152570</v>
+        <v>7152487</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8971,19 +8955,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120080336</v>
+        <v>120094951</v>
       </c>
       <c r="B80" t="n">
         <v>91858</v>
@@ -9017,16 +9001,19 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>746545</v>
+        <v>746357</v>
       </c>
       <c r="R80" t="n">
-        <v>7152464</v>
+        <v>7152686</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9067,25 +9054,26 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120080348</v>
+        <v>120094886</v>
       </c>
       <c r="B81" t="n">
         <v>91858</v>
@@ -9119,16 +9107,19 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>746505</v>
+        <v>746500</v>
       </c>
       <c r="R81" t="n">
-        <v>7152451</v>
+        <v>7152466</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9169,28 +9160,29 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120086230</v>
+        <v>120094849</v>
       </c>
       <c r="B82" t="n">
-        <v>90545</v>
+        <v>91858</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9203,34 +9195,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>746412</v>
+        <v>746531</v>
       </c>
       <c r="R82" t="n">
-        <v>7152564</v>
+        <v>7152454</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9271,6 +9266,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9289,7 +9285,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120080342</v>
+        <v>120080338</v>
       </c>
       <c r="B83" t="n">
         <v>91858</v>
@@ -9329,10 +9325,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>746478</v>
+        <v>746455</v>
       </c>
       <c r="R83" t="n">
-        <v>7152487</v>
+        <v>7152561</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9391,10 +9387,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120094849</v>
+        <v>120086259</v>
       </c>
       <c r="B84" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9403,41 +9399,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>746531</v>
+        <v>746394</v>
       </c>
       <c r="R84" t="n">
-        <v>7152454</v>
+        <v>7152581</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9478,7 +9471,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9497,10 +9489,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120080337</v>
+        <v>120080295</v>
       </c>
       <c r="B85" t="n">
-        <v>91858</v>
+        <v>57473</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9509,38 +9501,46 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>746488</v>
+        <v>746385</v>
       </c>
       <c r="R85" t="n">
-        <v>7152500</v>
+        <v>7152570</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>

--- a/artfynd/A 41672-2024 artfynd.xlsx
+++ b/artfynd/A 41672-2024 artfynd.xlsx
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120067885</v>
+        <v>120068300</v>
       </c>
       <c r="B7" t="n">
-        <v>91902</v>
+        <v>91881</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>746399</v>
+        <v>746336</v>
       </c>
       <c r="R7" t="n">
-        <v>7152617</v>
+        <v>7152676</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120068300</v>
+        <v>120067885</v>
       </c>
       <c r="B8" t="n">
-        <v>91881</v>
+        <v>91902</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>746336</v>
+        <v>746399</v>
       </c>
       <c r="R8" t="n">
-        <v>7152676</v>
+        <v>7152617</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -4924,10 +4924,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120094901</v>
+        <v>120086277</v>
       </c>
       <c r="B41" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4936,41 +4936,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>746487</v>
+        <v>746302</v>
       </c>
       <c r="R41" t="n">
-        <v>7152494</v>
+        <v>7152670</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5011,7 +5008,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5030,10 +5026,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120086277</v>
+        <v>120094901</v>
       </c>
       <c r="B42" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5042,38 +5038,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>746302</v>
+        <v>746487</v>
       </c>
       <c r="R42" t="n">
-        <v>7152670</v>
+        <v>7152494</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5114,6 +5113,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41672-2024 artfynd.xlsx
+++ b/artfynd/A 41672-2024 artfynd.xlsx
@@ -2559,7 +2559,7 @@
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG18" t="b">
         <v>0</v>
@@ -8032,7 +8032,7 @@
         <v>0</v>
       </c>
       <c r="AE70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">

--- a/artfynd/A 41672-2024 artfynd.xlsx
+++ b/artfynd/A 41672-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY84"/>
+  <dimension ref="A1:AY74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120067979</v>
+        <v>120086272</v>
       </c>
       <c r="B2" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vintjärnsberget, Vintjärnsberget, Vb</t>
+          <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>746392</v>
+        <v>746357</v>
       </c>
       <c r="R2" t="n">
-        <v>7152615</v>
+        <v>7152581</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +743,9 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,65 +760,63 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120066631</v>
+        <v>120079809</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vintjärnsberget, Vintjärnsberget, Vb</t>
+          <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>746551</v>
+        <v>746368</v>
       </c>
       <c r="R3" t="n">
-        <v>7152434</v>
+        <v>7152599</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,92 +843,78 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120068080</v>
+        <v>120080326</v>
       </c>
       <c r="B4" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90674</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1596</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vintjärnsberget, Vintjärnsberget, Vb</t>
+          <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>746371</v>
+        <v>746543</v>
       </c>
       <c r="R4" t="n">
-        <v>7152632</v>
+        <v>7152437</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,19 +941,9 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,65 +958,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120067262</v>
+        <v>120079797</v>
       </c>
       <c r="B5" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vintjärnsberget, Vintjärnsberget, Vb</t>
+          <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>746520</v>
+        <v>746432</v>
       </c>
       <c r="R5" t="n">
-        <v>7152494</v>
+        <v>7152509</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,19 +1038,9 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,49 +1055,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120068383</v>
+        <v>120067430</v>
       </c>
       <c r="B6" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>746313</v>
+        <v>746505</v>
       </c>
       <c r="R6" t="n">
-        <v>7152706</v>
+        <v>7152499</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1198,7 +1137,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1147,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,37 +1174,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120067137</v>
+        <v>120067504</v>
       </c>
       <c r="B7" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1209,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>746520</v>
+        <v>746486</v>
       </c>
       <c r="R7" t="n">
-        <v>7152487</v>
+        <v>7152501</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1310,7 +1244,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1254,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,19 +1281,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120067430</v>
+        <v>120069457</v>
       </c>
       <c r="B8" t="n">
-        <v>91874</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1387,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>746505</v>
+        <v>746379</v>
       </c>
       <c r="R8" t="n">
-        <v>7152499</v>
+        <v>7152575</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1422,7 +1351,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1361,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,53 +1388,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120067841</v>
+        <v>120079805</v>
       </c>
       <c r="B9" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vintjärnsberget, Vintjärnsberget, Vb</t>
+          <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>746469</v>
+        <v>746437</v>
       </c>
       <c r="R9" t="n">
-        <v>7152569</v>
+        <v>7152508</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1532,19 +1456,9 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,65 +1473,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120068133</v>
+        <v>120080319</v>
       </c>
       <c r="B10" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vintjärnsberget, Vintjärnsberget, Vb</t>
+          <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>746333</v>
+        <v>746477</v>
       </c>
       <c r="R10" t="n">
-        <v>7152647</v>
+        <v>7152502</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1644,19 +1553,14 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:51</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:51</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På kolad tallstubbe</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1667,69 +1571,84 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Kolad tallstubbe</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Kolad tallstubbe</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120068255</v>
+        <v>120086263</v>
       </c>
       <c r="B11" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vintjärnsberget, Vintjärnsberget, Vb</t>
+          <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>746352</v>
+        <v>746450</v>
       </c>
       <c r="R11" t="n">
-        <v>7152686</v>
+        <v>7152549</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1756,19 +1675,9 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:56</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,49 +1692,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120069348</v>
+        <v>120069608</v>
       </c>
       <c r="B12" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1739,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>746382</v>
+        <v>746422</v>
       </c>
       <c r="R12" t="n">
-        <v>7152570</v>
+        <v>7152546</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1870,7 +1774,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1784,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,53 +1811,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120067568</v>
+        <v>120086259</v>
       </c>
       <c r="B13" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vintjärnsberget, Vintjärnsberget, Vb</t>
+          <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>746484</v>
+        <v>746394</v>
       </c>
       <c r="R13" t="n">
-        <v>7152500</v>
+        <v>7152581</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1980,19 +1879,9 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,49 +1896,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120067935</v>
+        <v>120067137</v>
       </c>
       <c r="B14" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>746381</v>
+        <v>746520</v>
       </c>
       <c r="R14" t="n">
-        <v>7152596</v>
+        <v>7152487</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2094,7 +1978,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +1988,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,15 +2015,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120069457</v>
+        <v>120066631</v>
       </c>
       <c r="B15" t="n">
-        <v>91874</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2147,21 +2026,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>746379</v>
+        <v>746551</v>
       </c>
       <c r="R15" t="n">
-        <v>7152575</v>
+        <v>7152434</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2206,7 +2085,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2095,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,19 +2122,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120068460</v>
+        <v>120067262</v>
       </c>
       <c r="B16" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2283,10 +2157,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>746312</v>
+        <v>746520</v>
       </c>
       <c r="R16" t="n">
-        <v>7152709</v>
+        <v>7152494</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2318,7 +2192,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2202,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,15 +2229,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120069608</v>
+        <v>120067568</v>
       </c>
       <c r="B17" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2371,21 +2240,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2264,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>746422</v>
+        <v>746484</v>
       </c>
       <c r="R17" t="n">
-        <v>7152546</v>
+        <v>7152500</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2430,7 +2299,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2309,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,37 +2336,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120068602</v>
+        <v>120067841</v>
       </c>
       <c r="B18" t="n">
-        <v>79652</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2371,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>746307</v>
+        <v>746469</v>
       </c>
       <c r="R18" t="n">
-        <v>7152647</v>
+        <v>7152569</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2542,7 +2406,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,14 +2416,14 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="b">
         <v>0</v>
@@ -2579,15 +2443,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120066896</v>
+        <v>120067935</v>
       </c>
       <c r="B19" t="n">
-        <v>91881</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,21 +2454,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2478,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>746537</v>
+        <v>746381</v>
       </c>
       <c r="R19" t="n">
-        <v>7152456</v>
+        <v>7152596</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2654,7 +2513,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2523,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,15 +2550,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120068300</v>
+        <v>120067979</v>
       </c>
       <c r="B20" t="n">
-        <v>91881</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2707,21 +2561,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2585,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>746336</v>
+        <v>746392</v>
       </c>
       <c r="R20" t="n">
-        <v>7152676</v>
+        <v>7152615</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2766,7 +2620,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2630,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,15 +2657,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120067504</v>
+        <v>120068080</v>
       </c>
       <c r="B21" t="n">
-        <v>91874</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2819,21 +2668,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,10 +2692,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>746486</v>
+        <v>746371</v>
       </c>
       <c r="R21" t="n">
-        <v>7152501</v>
+        <v>7152632</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2878,7 +2727,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2888,7 +2737,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,15 +2764,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120067885</v>
+        <v>120068133</v>
       </c>
       <c r="B22" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2931,21 +2775,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2955,10 +2799,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>746399</v>
+        <v>746333</v>
       </c>
       <c r="R22" t="n">
-        <v>7152617</v>
+        <v>7152647</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2990,7 +2834,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3000,7 +2844,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,19 +2871,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120068331</v>
+        <v>120068255</v>
       </c>
       <c r="B23" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3067,10 +2906,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>746318</v>
+        <v>746352</v>
       </c>
       <c r="R23" t="n">
-        <v>7152701</v>
+        <v>7152686</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3102,7 +2941,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3112,7 +2951,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,37 +2978,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120068346</v>
+        <v>120068331</v>
       </c>
       <c r="B24" t="n">
-        <v>91870</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,10 +3013,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>746324</v>
+        <v>746318</v>
       </c>
       <c r="R24" t="n">
-        <v>7152703</v>
+        <v>7152701</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3214,7 +3048,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3224,7 +3058,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3251,15 +3085,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120068365</v>
+        <v>120068383</v>
       </c>
       <c r="B25" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3267,21 +3096,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3291,10 +3120,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>746323</v>
+        <v>746313</v>
       </c>
       <c r="R25" t="n">
-        <v>7152700</v>
+        <v>7152706</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3326,7 +3155,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3336,7 +3165,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3363,19 +3192,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120086296</v>
+        <v>120068460</v>
       </c>
       <c r="B26" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3399,17 +3223,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Vintjärnskammen, Vb</t>
+          <t>Vintjärnsberget, Vintjärnsberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>746425</v>
+        <v>746312</v>
       </c>
       <c r="R26" t="n">
-        <v>7152621</v>
+        <v>7152709</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3436,9 +3260,19 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3453,31 +3287,26 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120080336</v>
+        <v>120069348</v>
       </c>
       <c r="B27" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3501,17 +3330,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Vintjärnskammen, Vb</t>
+          <t>Vintjärnsberget, Vintjärnsberget, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>746545</v>
+        <v>746382</v>
       </c>
       <c r="R27" t="n">
-        <v>7152464</v>
+        <v>7152570</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3538,9 +3367,19 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3555,31 +3394,26 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120080337</v>
+        <v>120079812</v>
       </c>
       <c r="B28" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3607,13 +3441,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>746488</v>
+        <v>746540</v>
       </c>
       <c r="R28" t="n">
-        <v>7152500</v>
+        <v>7152434</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3651,37 +3485,33 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120094959</v>
+        <v>120079813</v>
       </c>
       <c r="B29" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3703,22 +3533,19 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>746300</v>
+        <v>746517</v>
       </c>
       <c r="R29" t="n">
-        <v>7152654</v>
+        <v>7152485</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3756,38 +3583,32 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120080340</v>
+        <v>120080336</v>
       </c>
       <c r="B30" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3815,10 +3636,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>746398</v>
+        <v>746545</v>
       </c>
       <c r="R30" t="n">
-        <v>7152548</v>
+        <v>7152464</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3877,19 +3698,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120094849</v>
+        <v>120080337</v>
       </c>
       <c r="B31" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3911,19 +3727,16 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>746531</v>
+        <v>746488</v>
       </c>
       <c r="R31" t="n">
-        <v>7152454</v>
+        <v>7152500</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3964,34 +3777,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120079805</v>
+        <v>120080338</v>
       </c>
       <c r="B32" t="n">
-        <v>92048</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3999,21 +3806,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4023,13 +3830,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>746437</v>
+        <v>746455</v>
       </c>
       <c r="R32" t="n">
-        <v>7152508</v>
+        <v>7152561</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4073,31 +3880,26 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120080346</v>
+        <v>120080340</v>
       </c>
       <c r="B33" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4125,10 +3927,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>746461</v>
+        <v>746398</v>
       </c>
       <c r="R33" t="n">
-        <v>7152458</v>
+        <v>7152548</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4187,19 +3989,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120086294</v>
+        <v>120080341</v>
       </c>
       <c r="B34" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4227,10 +4024,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>746310</v>
+        <v>746384</v>
       </c>
       <c r="R34" t="n">
-        <v>7152670</v>
+        <v>7152544</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4277,27 +4074,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120086265</v>
+        <v>120080342</v>
       </c>
       <c r="B35" t="n">
-        <v>78279</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4305,21 +4097,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4329,10 +4121,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>746353</v>
+        <v>746478</v>
       </c>
       <c r="R35" t="n">
-        <v>7152592</v>
+        <v>7152487</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4379,27 +4171,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120086278</v>
+        <v>120080343</v>
       </c>
       <c r="B36" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4407,21 +4194,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4431,10 +4218,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>746365</v>
+        <v>746467</v>
       </c>
       <c r="R36" t="n">
-        <v>7152695</v>
+        <v>7152466</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4481,27 +4268,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120086274</v>
+        <v>120080345</v>
       </c>
       <c r="B37" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4509,21 +4291,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4533,10 +4315,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>746478</v>
+        <v>746459</v>
       </c>
       <c r="R37" t="n">
-        <v>7152496</v>
+        <v>7152465</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4583,31 +4365,26 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120094951</v>
+        <v>120080346</v>
       </c>
       <c r="B38" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4629,19 +4406,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>746357</v>
+        <v>746461</v>
       </c>
       <c r="R38" t="n">
-        <v>7152686</v>
+        <v>7152458</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4682,38 +4456,32 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120079813</v>
+        <v>120080348</v>
       </c>
       <c r="B39" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4741,13 +4509,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>746517</v>
+        <v>746505</v>
       </c>
       <c r="R39" t="n">
-        <v>7152485</v>
+        <v>7152451</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4791,27 +4559,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120094916</v>
+        <v>120080349</v>
       </c>
       <c r="B40" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4819,37 +4582,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>746490</v>
+        <v>746540</v>
       </c>
       <c r="R40" t="n">
-        <v>7152513</v>
+        <v>7152444</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4890,34 +4650,28 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120086277</v>
+        <v>120086294</v>
       </c>
       <c r="B41" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4925,21 +4679,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4949,7 +4703,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>746302</v>
+        <v>746310</v>
       </c>
       <c r="R41" t="n">
         <v>7152670</v>
@@ -5011,15 +4765,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120086280</v>
+        <v>120086295</v>
       </c>
       <c r="B42" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5027,21 +4776,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5051,10 +4800,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>746527</v>
+        <v>746365</v>
       </c>
       <c r="R42" t="n">
-        <v>7152434</v>
+        <v>7152695</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5113,19 +4862,14 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120080349</v>
+        <v>120086296</v>
       </c>
       <c r="B43" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -5153,10 +4897,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>746540</v>
+        <v>746425</v>
       </c>
       <c r="R43" t="n">
-        <v>7152444</v>
+        <v>7152621</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5203,27 +4947,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120094945</v>
+        <v>120086297</v>
       </c>
       <c r="B44" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5231,37 +4970,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>746417</v>
+        <v>746473</v>
       </c>
       <c r="R44" t="n">
-        <v>7152628</v>
+        <v>7152499</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5302,7 +5038,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5321,15 +5056,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120080307</v>
+        <v>120086298</v>
       </c>
       <c r="B45" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5337,21 +5067,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5361,10 +5091,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>746426</v>
+        <v>746527</v>
       </c>
       <c r="R45" t="n">
-        <v>7152510</v>
+        <v>7152434</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5411,31 +5141,26 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120086295</v>
+        <v>120094849</v>
       </c>
       <c r="B46" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -5457,16 +5182,19 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>746365</v>
+        <v>746531</v>
       </c>
       <c r="R46" t="n">
-        <v>7152695</v>
+        <v>7152454</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5507,6 +5235,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5525,19 +5254,14 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120080343</v>
+        <v>120094855</v>
       </c>
       <c r="B47" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5559,16 +5283,19 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>746467</v>
+        <v>746547</v>
       </c>
       <c r="R47" t="n">
-        <v>7152466</v>
+        <v>7152471</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5609,68 +5336,67 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120080326</v>
+        <v>120094869</v>
       </c>
       <c r="B48" t="n">
-        <v>89247</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1596</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>746543</v>
+        <v>746522</v>
       </c>
       <c r="R48" t="n">
-        <v>7152437</v>
+        <v>7152453</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5711,37 +5437,33 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120079812</v>
+        <v>120094886</v>
       </c>
       <c r="B49" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -5763,19 +5485,22 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>746540</v>
+        <v>746500</v>
       </c>
       <c r="R49" t="n">
-        <v>7152434</v>
+        <v>7152466</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5820,31 +5545,26 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120094939</v>
+        <v>120094897</v>
       </c>
       <c r="B50" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -5875,10 +5595,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>746413</v>
+        <v>746482</v>
       </c>
       <c r="R50" t="n">
-        <v>7152616</v>
+        <v>7152467</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5938,15 +5658,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120086263</v>
+        <v>120094901</v>
       </c>
       <c r="B51" t="n">
-        <v>92048</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5954,34 +5669,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>746450</v>
+        <v>746487</v>
       </c>
       <c r="R51" t="n">
-        <v>7152549</v>
+        <v>7152494</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6022,6 +5740,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6040,15 +5759,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120080295</v>
+        <v>120094907</v>
       </c>
       <c r="B52" t="n">
-        <v>57473</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6056,31 +5770,26 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6088,10 +5797,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>746385</v>
+        <v>746484</v>
       </c>
       <c r="R52" t="n">
-        <v>7152570</v>
+        <v>7152510</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6132,37 +5841,33 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120086297</v>
+        <v>120094932</v>
       </c>
       <c r="B53" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -6184,16 +5889,19 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>746473</v>
+        <v>746414</v>
       </c>
       <c r="R53" t="n">
-        <v>7152499</v>
+        <v>7152584</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6234,6 +5942,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6252,50 +5961,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120086272</v>
+        <v>120094939</v>
       </c>
       <c r="B54" t="n">
-        <v>74640</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>306</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>746357</v>
+        <v>746413</v>
       </c>
       <c r="R54" t="n">
-        <v>7152581</v>
+        <v>7152616</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6336,6 +6043,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6354,15 +6062,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120079797</v>
+        <v>120094951</v>
       </c>
       <c r="B55" t="n">
-        <v>89650</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6370,37 +6073,40 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>746432</v>
+        <v>746357</v>
       </c>
       <c r="R55" t="n">
-        <v>7152509</v>
+        <v>7152686</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6438,37 +6144,33 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120094907</v>
+        <v>120094959</v>
       </c>
       <c r="B56" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -6499,10 +6201,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>746484</v>
+        <v>746300</v>
       </c>
       <c r="R56" t="n">
-        <v>7152510</v>
+        <v>7152654</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6562,15 +6264,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120086228</v>
+        <v>120068346</v>
       </c>
       <c r="B57" t="n">
-        <v>74654</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6578,37 +6275,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6440</v>
+        <v>4366</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Vintjärnskammen, Vb</t>
+          <t>Vintjärnsberget, Vintjärnsberget, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>746357</v>
+        <v>746324</v>
       </c>
       <c r="R57" t="n">
-        <v>7152581</v>
+        <v>7152703</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6635,9 +6332,19 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6652,62 +6359,60 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120086230</v>
+        <v>120086269</v>
       </c>
       <c r="B58" t="n">
-        <v>90545</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90522</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5447</v>
+        <v>4962</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>746412</v>
+        <v>746365</v>
       </c>
       <c r="R58" t="n">
-        <v>7152564</v>
+        <v>7152575</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6742,12 +6447,18 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Inte ihålig men övriga karaktärer stämde.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6766,37 +6477,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120086275</v>
+        <v>120086230</v>
       </c>
       <c r="B59" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6806,10 +6512,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>746370</v>
+        <v>746412</v>
       </c>
       <c r="R59" t="n">
-        <v>7152601</v>
+        <v>7152564</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6868,15 +6574,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120086266</v>
+        <v>120066896</v>
       </c>
       <c r="B60" t="n">
-        <v>91881</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6904,17 +6605,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Vintjärnskammen, Vb</t>
+          <t>Vintjärnsberget, Vintjärnsberget, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>746429</v>
+        <v>746537</v>
       </c>
       <c r="R60" t="n">
-        <v>7152625</v>
+        <v>7152456</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6941,9 +6642,19 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6958,27 +6669,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120080319</v>
+        <v>120068300</v>
       </c>
       <c r="B61" t="n">
-        <v>92048</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6986,37 +6692,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2079</v>
+        <v>5966</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Vintjärnskammen, Vb</t>
+          <t>Vintjärnsberget, Vintjärnsberget, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>746477</v>
+        <v>746336</v>
       </c>
       <c r="R61" t="n">
-        <v>7152502</v>
+        <v>7152676</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7043,14 +6749,19 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>På kolad tallstubbe</t>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7061,89 +6772,61 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL61" t="inlineStr">
-        <is>
-          <t>Kolad tallstubbe</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Kolad tallstubbe</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120094886</v>
+        <v>120086266</v>
       </c>
       <c r="B62" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>746500</v>
+        <v>746429</v>
       </c>
       <c r="R62" t="n">
-        <v>7152466</v>
+        <v>7152625</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7184,7 +6867,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7203,37 +6885,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120080338</v>
+        <v>120086274</v>
       </c>
       <c r="B63" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7243,10 +6920,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>746455</v>
+        <v>746478</v>
       </c>
       <c r="R63" t="n">
-        <v>7152561</v>
+        <v>7152496</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7293,65 +6970,57 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120094869</v>
+        <v>120086275</v>
       </c>
       <c r="B64" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>746522</v>
+        <v>746370</v>
       </c>
       <c r="R64" t="n">
-        <v>7152453</v>
+        <v>7152601</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7392,7 +7061,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7411,53 +7079,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120094897</v>
+        <v>120086276</v>
       </c>
       <c r="B65" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>746482</v>
+        <v>746304</v>
       </c>
       <c r="R65" t="n">
-        <v>7152467</v>
+        <v>7152657</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7498,7 +7158,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7517,37 +7176,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120086246</v>
+        <v>120086277</v>
       </c>
       <c r="B66" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7557,10 +7211,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>746475</v>
+        <v>746302</v>
       </c>
       <c r="R66" t="n">
-        <v>7152487</v>
+        <v>7152670</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7619,58 +7273,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120086238</v>
+        <v>120086278</v>
       </c>
       <c r="B67" t="n">
-        <v>57473</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>746509</v>
+        <v>746365</v>
       </c>
       <c r="R67" t="n">
-        <v>7152434</v>
+        <v>7152695</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7703,11 +7344,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Två</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7734,53 +7370,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120094901</v>
+        <v>120086279</v>
       </c>
       <c r="B68" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>746487</v>
+        <v>746397</v>
       </c>
       <c r="R68" t="n">
-        <v>7152494</v>
+        <v>7152654</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7821,7 +7449,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7840,37 +7467,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120080345</v>
+        <v>120086280</v>
       </c>
       <c r="B69" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7880,10 +7502,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>746459</v>
+        <v>746527</v>
       </c>
       <c r="R69" t="n">
-        <v>7152465</v>
+        <v>7152434</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7930,27 +7552,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120086269</v>
+        <v>120086228</v>
       </c>
       <c r="B70" t="n">
-        <v>88170</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7958,37 +7575,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4962</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>746365</v>
+        <v>746357</v>
       </c>
       <c r="R70" t="n">
-        <v>7152575</v>
+        <v>7152581</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8023,18 +7637,12 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Inte ihålig men övriga karaktärer stämde.</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF70" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8053,53 +7661,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120086245</v>
+        <v>120068602</v>
       </c>
       <c r="B71" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5449</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Vintjärnskammen, Vb</t>
+          <t>Vintjärnsberget, Vintjärnsberget, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>746365</v>
+        <v>746307</v>
       </c>
       <c r="R71" t="n">
-        <v>7152575</v>
+        <v>7152647</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8126,16 +7729,26 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG71" t="b">
         <v>0</v>
@@ -8143,27 +7756,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120086259</v>
+        <v>120080295</v>
       </c>
       <c r="B72" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8171,34 +7779,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4361</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Vintjärnskammen, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>746394</v>
+        <v>746385</v>
       </c>
       <c r="R72" t="n">
-        <v>7152581</v>
+        <v>7152570</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8245,54 +7861,54 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120079809</v>
+        <v>120086238</v>
       </c>
       <c r="B73" t="n">
-        <v>90730</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1503</v>
+        <v>103021</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8300,13 +7916,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>746368</v>
+        <v>746509</v>
       </c>
       <c r="R73" t="n">
-        <v>7152599</v>
+        <v>7152434</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8338,40 +7954,39 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Två</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120086279</v>
+        <v>120086265</v>
       </c>
       <c r="B74" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8379,21 +7994,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8403,10 +8018,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>746397</v>
+        <v>746353</v>
       </c>
       <c r="R74" t="n">
-        <v>7152654</v>
+        <v>7152592</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8462,1038 +8077,6 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>120080348</v>
-      </c>
-      <c r="B75" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Vintjärnskammen, Vb</t>
-        </is>
-      </c>
-      <c r="Q75" t="n">
-        <v>746505</v>
-      </c>
-      <c r="R75" t="n">
-        <v>7152451</v>
-      </c>
-      <c r="S75" t="n">
-        <v>10</v>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>Burträsk</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AD75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT75" t="inlineStr"/>
-      <c r="AW75" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>120086298</v>
-      </c>
-      <c r="B76" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Vintjärnskammen, Vb</t>
-        </is>
-      </c>
-      <c r="Q76" t="n">
-        <v>746527</v>
-      </c>
-      <c r="R76" t="n">
-        <v>7152434</v>
-      </c>
-      <c r="S76" t="n">
-        <v>10</v>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>Burträsk</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AD76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT76" t="inlineStr"/>
-      <c r="AW76" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>120079802</v>
-      </c>
-      <c r="B77" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>5449</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>Vintjärnskammen, Vb</t>
-        </is>
-      </c>
-      <c r="Q77" t="n">
-        <v>746495</v>
-      </c>
-      <c r="R77" t="n">
-        <v>7152470</v>
-      </c>
-      <c r="S77" t="n">
-        <v>15</v>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>Burträsk</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AD77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT77" t="inlineStr"/>
-      <c r="AW77" t="inlineStr">
-        <is>
-          <t>Joakim Karlsson</t>
-        </is>
-      </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>Joakim Karlsson</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>120080341</v>
-      </c>
-      <c r="B78" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Vintjärnskammen, Vb</t>
-        </is>
-      </c>
-      <c r="Q78" t="n">
-        <v>746384</v>
-      </c>
-      <c r="R78" t="n">
-        <v>7152544</v>
-      </c>
-      <c r="S78" t="n">
-        <v>10</v>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>Burträsk</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AD78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT78" t="inlineStr"/>
-      <c r="AW78" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>120094922</v>
-      </c>
-      <c r="B79" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>5449</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>Vintjärnskammen, Vb</t>
-        </is>
-      </c>
-      <c r="Q79" t="n">
-        <v>746442</v>
-      </c>
-      <c r="R79" t="n">
-        <v>7152565</v>
-      </c>
-      <c r="S79" t="n">
-        <v>10</v>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>Burträsk</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AD79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF79" t="inlineStr"/>
-      <c r="AG79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT79" t="inlineStr"/>
-      <c r="AW79" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>120080306</v>
-      </c>
-      <c r="B80" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>5449</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>Vintjärnskammen, Vb</t>
-        </is>
-      </c>
-      <c r="Q80" t="n">
-        <v>746490</v>
-      </c>
-      <c r="R80" t="n">
-        <v>7152502</v>
-      </c>
-      <c r="S80" t="n">
-        <v>10</v>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>Burträsk</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AD80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT80" t="inlineStr"/>
-      <c r="AW80" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>120080342</v>
-      </c>
-      <c r="B81" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>Vintjärnskammen, Vb</t>
-        </is>
-      </c>
-      <c r="Q81" t="n">
-        <v>746478</v>
-      </c>
-      <c r="R81" t="n">
-        <v>7152487</v>
-      </c>
-      <c r="S81" t="n">
-        <v>10</v>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>Burträsk</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AD81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT81" t="inlineStr"/>
-      <c r="AW81" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>120094855</v>
-      </c>
-      <c r="B82" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Vintjärnskammen, Vb</t>
-        </is>
-      </c>
-      <c r="Q82" t="n">
-        <v>746547</v>
-      </c>
-      <c r="R82" t="n">
-        <v>7152471</v>
-      </c>
-      <c r="S82" t="n">
-        <v>10</v>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>Burträsk</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AD82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF82" t="inlineStr"/>
-      <c r="AG82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT82" t="inlineStr"/>
-      <c r="AW82" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>120086276</v>
-      </c>
-      <c r="B83" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>Vintjärnskammen, Vb</t>
-        </is>
-      </c>
-      <c r="Q83" t="n">
-        <v>746304</v>
-      </c>
-      <c r="R83" t="n">
-        <v>7152657</v>
-      </c>
-      <c r="S83" t="n">
-        <v>10</v>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>Burträsk</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AD83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT83" t="inlineStr"/>
-      <c r="AW83" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>120094932</v>
-      </c>
-      <c r="B84" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>Vintjärnskammen, Vb</t>
-        </is>
-      </c>
-      <c r="Q84" t="n">
-        <v>746414</v>
-      </c>
-      <c r="R84" t="n">
-        <v>7152584</v>
-      </c>
-      <c r="S84" t="n">
-        <v>10</v>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>Burträsk</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AD84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF84" t="inlineStr"/>
-      <c r="AG84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT84" t="inlineStr"/>
-      <c r="AW84" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41672-2024 artfynd.xlsx
+++ b/artfynd/A 41672-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY74"/>
+  <dimension ref="A1:AZ74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120086272</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120079809</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120080326</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120079797</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1171,6 +1196,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120067430</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120067504</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1385,6 +1420,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120069457</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1482,6 +1522,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120079805</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1604,6 +1649,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120080319</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1701,6 +1751,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120086263</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1808,6 +1863,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120069608</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1905,6 +1965,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120086259</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2012,6 +2077,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120067137</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2119,6 +2189,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120066631</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2226,6 +2301,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120067262</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2333,6 +2413,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120067568</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2440,6 +2525,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120067841</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2547,6 +2637,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120067935</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2654,6 +2749,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120067979</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2761,6 +2861,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120068080</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2868,6 +2973,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120068133</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2975,6 +3085,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120068255</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3082,6 +3197,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120068331</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3189,6 +3309,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120068383</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3296,6 +3421,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120068460</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3403,6 +3533,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120069348</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3501,6 +3636,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120079812</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3598,6 +3738,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120079813</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3695,6 +3840,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120080336</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3792,6 +3942,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120080337</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3889,6 +4044,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120080338</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3986,6 +4146,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120080340</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4083,6 +4248,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120080341</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4180,6 +4350,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120080342</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4277,6 +4452,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120080343</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4374,6 +4554,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120080345</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4471,6 +4656,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120080346</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4568,6 +4758,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120080348</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4665,6 +4860,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120080349</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4762,6 +4962,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120086294</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4859,6 +5064,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120086295</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4956,6 +5166,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120086296</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5053,6 +5268,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120086297</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5150,6 +5370,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120086298</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5251,6 +5476,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120094849</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5352,6 +5582,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120094855</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5453,6 +5688,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120094869</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5554,6 +5794,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120094886</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5655,6 +5900,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120094897</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5756,6 +6006,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120094901</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5857,6 +6112,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120094907</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5958,6 +6218,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120094932</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6059,6 +6324,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120094939</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6160,6 +6430,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120094951</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6261,6 +6536,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120094959</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6368,6 +6648,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120068346</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6474,6 +6759,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120086269</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6571,6 +6861,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120086230</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6678,6 +6973,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120066896</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6785,6 +7085,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120068300</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6882,6 +7187,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120086266</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6979,6 +7289,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120086274</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7076,6 +7391,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120086275</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7173,6 +7493,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120086276</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7270,6 +7595,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120086277</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7367,6 +7697,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120086278</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7464,6 +7799,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120086279</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7561,6 +7901,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120086280</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7658,6 +8003,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120086228</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7765,6 +8115,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120068602</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7870,6 +8225,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120080295</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7980,6 +8340,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120086238</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8077,8 +8442,88 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120086265</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>